--- a/피지컬팀 프로젝트 mk2 요구사항 정의서.xlsx
+++ b/피지컬팀 프로젝트 mk2 요구사항 정의서.xlsx
@@ -702,468 +702,468 @@
       <c r="O1" s="4" t="n"/>
     </row>
     <row r="2">
-      <c r="A2" s="10" t="inlineStr">
+      <c r="A2" s="44" t="inlineStr">
         <is>
           <t>HW-R-01</t>
         </is>
       </c>
-      <c r="B2" s="13" t="inlineStr">
+      <c r="B2" s="45" t="inlineStr">
         <is>
           <t>로봇</t>
         </is>
       </c>
-      <c r="C2" s="15" t="inlineStr">
+      <c r="C2" s="46" t="inlineStr">
         <is>
           <t>로봇 내부 데이터 전달(온보드)</t>
         </is>
       </c>
-      <c r="D2" s="15" t="inlineStr">
+      <c r="D2" s="46" t="inlineStr">
         <is>
           <t>로봇 제어기(구동부)가 배터리 잔량, 위치(좌표), 속도, 동작 모드, 온디바이스 인식 결과 등 자신의 데이터를 온보드 라즈베리파이로 전달한다. 외부 통신(MQTT)·버퍼링·중계 역할을 온보드 라즈베리파이에 위임하여 로봇 제어기는 주행·임무 수행에 연산 자원을 집중하도록 역할을 분리하기 위해 정의한다.</t>
         </is>
       </c>
-      <c r="E2" s="15" t="inlineStr">
+      <c r="E2" s="46" t="inlineStr">
         <is>
           <t>로봇→로봇 온보드 라즈베리파이</t>
         </is>
       </c>
-      <c r="F2" s="10" t="inlineStr">
+      <c r="F2" s="44" t="inlineStr">
         <is>
           <t>0.1초 1회(유선 인터페이스)</t>
         </is>
       </c>
-      <c r="G2" s="15" t="inlineStr">
+      <c r="G2" s="46" t="inlineStr">
         <is>
           <t>1초 주기도 존재하나 유선전달 구간은 대역폭 부담이 거의 없고, 제어기 상태를 온보드에서 촘촘히 확보해야 외부 보고 주기를 상황별로 조절할 수 있음. 내부는 고주기(0.1초), 외부 보고는 저주기로 이원화하는 것이 가장 효율적이라 선정.</t>
         </is>
       </c>
-      <c r="H2" s="15" t="inlineStr">
+      <c r="H2" s="46" t="inlineStr">
         <is>
           <t>백엔드 엣지노드</t>
         </is>
       </c>
-      <c r="I2" s="15" t="inlineStr">
+      <c r="I2" s="46" t="inlineStr">
         <is>
           <t>온보드 라즈베리파이가 엣지노드로 보고하는 모든 데이터(HW-R-02~04)의 원천 입력이 됨</t>
         </is>
       </c>
-      <c r="J2" s="10" t="inlineStr">
+      <c r="J2" s="44" t="inlineStr">
         <is>
           <t>조병현</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="10" t="inlineStr">
+      <c r="A3" s="44" t="inlineStr">
         <is>
           <t>HW-R-02</t>
         </is>
       </c>
-      <c r="B3" s="13" t="inlineStr">
+      <c r="B3" s="45" t="inlineStr">
         <is>
           <t>로봇</t>
         </is>
       </c>
-      <c r="C3" s="15" t="inlineStr">
+      <c r="C3" s="46" t="inlineStr">
         <is>
           <t>하트비트 전송</t>
         </is>
       </c>
-      <c r="D3" s="15" t="inlineStr">
+      <c r="D3" s="46" t="inlineStr">
         <is>
           <t>로봇 온보드 라즈베리파이가 로봇의 생존(접속) 상태를 주기적으로 엣지노드에 전송한다. 단, 임무 수행 중에는 상태 데이터(HW-R-03)가 하트비트를 겸하므로 별도 하트비트는 대기 상태에서만 전송한다.</t>
         </is>
       </c>
-      <c r="E3" s="15" t="inlineStr">
+      <c r="E3" s="46" t="inlineStr">
         <is>
           <t>로봇 온보드 라즈베리파이→구역 엣지노드</t>
         </is>
       </c>
-      <c r="F3" s="10" t="inlineStr">
+      <c r="F3" s="44" t="inlineStr">
         <is>
           <t>대기 중 1초 1회(임무 중에는 상태 데이터가 겸함)</t>
         </is>
       </c>
-      <c r="G3" s="15" t="inlineStr">
+      <c r="G3" s="46" t="inlineStr">
         <is>
           <t>5초 이상은 이동체 장애 감지가 늦어 골든타임 대응에 불리하고, 0.1초는 너무 반복적인 전달로 인한 낭비가 발생한다. 하트비트 1건은 약 100바이트로 구역당 로봇 수(수 대~수십 대)에서 1초 주기 부하는 미미하며, 국가 단위 확장 시에도 엣지노드가 구역별로 증설되어 엣지 1대당 장치 수는 일정함. 임무 중 상태 데이터와의 중복만 제거하면 1초가 가장 효율적이라 선정.</t>
         </is>
       </c>
-      <c r="H3" s="15" t="inlineStr">
+      <c r="H3" s="46" t="inlineStr">
         <is>
           <t>백엔드 엣지노드, 가시화</t>
         </is>
       </c>
-      <c r="I3" s="15" t="inlineStr">
+      <c r="I3" s="46" t="inlineStr">
         <is>
           <t>엣지노드가 하트비트를 수신·집계하여 온라인 상태를 관리하고, 가시화 대시보드에서 구역별 로봇 온라인/오프라인을 표시</t>
         </is>
       </c>
-      <c r="J3" s="10" t="inlineStr">
+      <c r="J3" s="44" t="inlineStr">
         <is>
           <t>조병현</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="10" t="inlineStr">
+      <c r="A4" s="44" t="inlineStr">
         <is>
           <t>HW-R-03</t>
         </is>
       </c>
-      <c r="B4" s="13" t="inlineStr">
+      <c r="B4" s="45" t="inlineStr">
         <is>
           <t>로봇</t>
         </is>
       </c>
-      <c r="C4" s="15" t="inlineStr">
+      <c r="C4" s="46" t="inlineStr">
         <is>
           <t>상태 데이터 전달</t>
         </is>
       </c>
-      <c r="D4" s="15" t="inlineStr">
+      <c r="D4" s="46" t="inlineStr">
         <is>
           <t>로봇 온보드 라즈베리파이가 내부(HW-R-01)에서 수집한 로봇 상태(배터리, 위치, 속도, 동작 모드)를 엣지노드로 전송한다. 관제(모니터링) 시스템이 로봇의 현재 상황을 실시간으로 파악하고, 임무 할당·이상 판단의 기초 데이터로 사용하기 위해 정의한다.</t>
         </is>
       </c>
-      <c r="E4" s="15" t="inlineStr">
+      <c r="E4" s="46" t="inlineStr">
         <is>
           <t>로봇 온보드 라즈베리파이→엣지노드</t>
         </is>
       </c>
-      <c r="F4" s="10" t="inlineStr">
+      <c r="F4" s="44" t="inlineStr">
         <is>
           <t>임무 수행 중 50ms / 대기 중 5초 1회</t>
         </is>
       </c>
-      <c r="G4" s="15" t="inlineStr">
+      <c r="G4" s="46" t="inlineStr">
         <is>
           <t>1초 주기도 존재하나 이동체 추적에는 틱당 이동거리가 커서 거칠고, 엣지노드 단의 디지털 트윈 동기화·이상 감지의 실시간성이 부족함. 50ms(20Hz)는 구역 내 무선 구간에서 처리 가능한 수준이면서 트윈 갱신이 사실상 연속으로 보이는 주기이고, 그 이하는 무선 지터(수십 ms)에 묻혀 정보 이득이 없음. 대기 중에는 변화가 없어 5초로 완화하는 이원화가 실시간성과 낭비 최소화의 균형이 가장 좋아 선정.</t>
         </is>
       </c>
-      <c r="H4" s="15" t="inlineStr">
+      <c r="H4" s="46" t="inlineStr">
         <is>
           <t>백엔드 서버, 가시화, 엣지노드</t>
         </is>
       </c>
-      <c r="I4" s="15" t="inlineStr">
+      <c r="I4" s="46" t="inlineStr">
         <is>
           <t>백엔드 서버가 상태 이력을 저장·관리하고, 가시화에서 로봇 위치·배터리를 대시보드로 표시, 엣지노드의 경우 로봇의 정보를 전달 받고 명령을 내림</t>
         </is>
       </c>
-      <c r="J4" s="10" t="inlineStr">
+      <c r="J4" s="44" t="inlineStr">
         <is>
           <t>조병현</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="10" t="inlineStr">
+      <c r="A5" s="44" t="inlineStr">
         <is>
           <t>HW-R-04</t>
         </is>
       </c>
-      <c r="B5" s="13" t="inlineStr">
+      <c r="B5" s="45" t="inlineStr">
         <is>
           <t>로봇</t>
         </is>
       </c>
-      <c r="C5" s="15" t="inlineStr">
+      <c r="C5" s="46" t="inlineStr">
         <is>
           <t>환경인식용 이미지 및 온디바이스 인식</t>
         </is>
       </c>
-      <c r="D5" s="15" t="inlineStr">
+      <c r="D5" s="46" t="inlineStr">
         <is>
           <t>로봇 탑재 카메라에서 획득한 이미지(프레임)는 로봇 온디바이스에 배포된 경량 인지 모델의 입력으로 사용한다. 로봇은 온디바이스에서 객체·환경을 인식하고 해당 인식 결과를 상태 데이터와 함께 전달한다. 필요 시 원본 이미지 또는 영상 프레임을 엣지노드로 전달하여 디지털 트윈 동기화, 추가 분석 및 관제에 활용할 수 있어야 한다.</t>
         </is>
       </c>
-      <c r="E5" s="15" t="inlineStr">
+      <c r="E5" s="46" t="inlineStr">
         <is>
           <t>카메라→로봇 온디바이스 AI</t>
         </is>
       </c>
-      <c r="F5" s="10" t="inlineStr">
+      <c r="F5" s="44" t="inlineStr">
         <is>
           <t>온디바이스 추론 주기는 AI 파트 기준</t>
         </is>
       </c>
-      <c r="G5" s="15" t="inlineStr">
+      <c r="G5" s="46" t="inlineStr">
         <is>
           <t>온디바이스 추론 속도는 적용 모델의 연산량, 로봇 탑재 연산 자원 및 요구 인식 성능에 따라 달라지므로 하드웨어 파트에서 임의의 고정 주기를 설정하지 않는다. AI 파트에서 실제 경량 모델을 기준으로 목표 추론 주기를 결정하고, 하드웨어는 해당 카메라 입력 및 처리 속도를 지원하도록 구성한다.</t>
         </is>
       </c>
-      <c r="H5" s="15" t="inlineStr">
+      <c r="H5" s="46" t="inlineStr">
         <is>
           <t>AI, 백엔드 엣지노드, 가시화</t>
         </is>
       </c>
-      <c r="I5" s="15" t="inlineStr">
+      <c r="I5" s="46" t="inlineStr">
         <is>
           <t>AI-P-01의 경량 온디바이스 인지 모델이 로봇 카메라 영상을 기반으로 객체·환경을 인식하고, AI-R-03의 구역별 특화 모델 배포를 통해 현재 구역에 적합한 온디바이스 인식을 수행한다. 인식 결과는 HW-R-01의 상태 데이터와 연계하여 엣지노드·디지털 트윈·가시화에 활용한다.</t>
         </is>
       </c>
-      <c r="J5" s="10" t="inlineStr">
+      <c r="J5" s="44" t="inlineStr">
         <is>
           <t>조병현</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="10" t="inlineStr">
+      <c r="A6" s="44" t="inlineStr">
         <is>
           <t>HW-R-05</t>
         </is>
       </c>
-      <c r="B6" s="13" t="inlineStr">
+      <c r="B6" s="45" t="inlineStr">
         <is>
           <t>로봇</t>
         </is>
       </c>
-      <c r="C6" s="15" t="inlineStr">
+      <c r="C6" s="46" t="inlineStr">
         <is>
           <t>임무(서브태스크) 수신</t>
         </is>
       </c>
-      <c r="D6" s="15" t="inlineStr">
+      <c r="D6" s="46" t="inlineStr">
         <is>
           <t>메인서버가 하달한 임무(예: '구역1 비전센서 1번 위치로 이동')를 엣지노드가 해당 내용으로 서브테스크를 생성하며 로봇 온보드 라즈베리파이에 전달하고, 온보드가 이를 수신·검증한다. 수행 시작/완료/실패 보고는 상태 데이터(HW-R-03)에 포함하여 회신한다. 서브태스크 단위 검증·디버깅(어느 단계에서 실패했는지 판별)을 가능하게 하기 위해 정의한다.</t>
         </is>
       </c>
-      <c r="E6" s="15" t="inlineStr">
+      <c r="E6" s="46" t="inlineStr">
         <is>
           <t>엣지노드→로봇 온보드 라즈베리파이</t>
         </is>
       </c>
-      <c r="F6" s="10" t="inlineStr">
+      <c r="F6" s="44" t="inlineStr">
         <is>
           <t>이벤트 기반(임무 하달 시 즉시, 비주기)</t>
         </is>
       </c>
-      <c r="G6" s="15" t="inlineStr">
+      <c r="G6" s="46" t="inlineStr">
         <is>
           <t>주기적 폴링(로봇이 임무 유무를 반복 조회) 방식도 존재하나 임무가 없는 구간의 조회가 전부 낭비이며 하달 지연도 발생함. 엣지노드가 하달 시점에 즉시 푸시하는 이벤트 방식이 지연·낭비 모두 가장 적어 선정.</t>
         </is>
       </c>
-      <c r="H6" s="15" t="inlineStr">
+      <c r="H6" s="46" t="inlineStr">
         <is>
           <t>AI, 백엔드 서버, 가시화</t>
         </is>
       </c>
-      <c r="I6" s="15" t="inlineStr">
+      <c r="I6" s="46" t="inlineStr">
         <is>
           <t>AI(LLM)가 생성한 서브태스크를 수신 대상으로 하고, 백엔드가 하달 이력을 저장하며, 가시화에서 서브태스크 수행 여부를 노드 형태로 표시·디버깅</t>
         </is>
       </c>
-      <c r="J6" s="10" t="inlineStr">
+      <c r="J6" s="44" t="inlineStr">
         <is>
           <t>조병현</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="10" t="inlineStr">
+      <c r="A7" s="44" t="inlineStr">
         <is>
           <t>HW-R-06</t>
         </is>
       </c>
-      <c r="B7" s="13" t="inlineStr">
+      <c r="B7" s="45" t="inlineStr">
         <is>
           <t>로봇</t>
         </is>
       </c>
-      <c r="C7" s="15" t="inlineStr">
+      <c r="C7" s="46" t="inlineStr">
         <is>
           <t>제어 명령 내부 전달(온보드)</t>
         </is>
       </c>
-      <c r="D7" s="15" t="inlineStr">
+      <c r="D7" s="46" t="inlineStr">
         <is>
           <t>로봇 온보드 라즈베리파이가 수신한 서브태스크·제어 명령을 로봇 제어기(구동부)가 실행할 수 있는 명령 형태로 변환하여 전달한다. 외부 프로토콜(MQTT)과 로봇 구동 인터페이스를 온보드에서 변환·격리함으로써, 통신 장애가 구동 로직에 직접 영향을 주지 않도록 하기 위해 정의한다.</t>
         </is>
       </c>
-      <c r="E7" s="15" t="inlineStr">
+      <c r="E7" s="46" t="inlineStr">
         <is>
           <t>로봇 온보드 라즈베리파이→로봇</t>
         </is>
       </c>
-      <c r="F7" s="10" t="inlineStr">
+      <c r="F7" s="44" t="inlineStr">
         <is>
           <t>이벤트 기반(명령 수신 시 즉시)</t>
         </is>
       </c>
-      <c r="G7" s="15" t="inlineStr">
+      <c r="G7" s="46" t="inlineStr">
         <is>
           <t>명령을 모아 일괄 전달하는 방식도 존재하나 이동 제어 특성상 지연이 곧 오동작으로 이어짐. 내부 유선 구간은 부하 부담이 없으므로 수신 즉시 전달하는 이벤트 방식이 가장 안전하고 효율적이라 선정. 각각의 서브테스크들을 하나씩 풀어서 로봇에게 전달하고 해결 불가한 사항을 대면할 경우 위쪽에 다시 전달(어디에서 어떤 문제로 해당 작업 수행 불가인지)</t>
         </is>
       </c>
-      <c r="H7" s="15" t="inlineStr">
+      <c r="H7" s="46" t="inlineStr">
         <is>
           <t>백엔드 엣지노드</t>
         </is>
       </c>
-      <c r="I7" s="15" t="inlineStr">
+      <c r="I7" s="46" t="inlineStr">
         <is>
           <t>엣지노드가 내려준 서브태스크가 실제 구동으로 이어지는 마지막 구간으로, 명령 체계(HW-C-06 ACK)와 연동</t>
         </is>
       </c>
-      <c r="J7" s="10" t="inlineStr">
+      <c r="J7" s="44" t="inlineStr">
         <is>
           <t>조병현</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="10" t="inlineStr">
+      <c r="A8" s="44" t="inlineStr">
         <is>
           <t>HW-R-07</t>
         </is>
       </c>
-      <c r="B8" s="13" t="inlineStr">
+      <c r="B8" s="45" t="inlineStr">
         <is>
           <t>로봇</t>
         </is>
       </c>
-      <c r="C8" s="15" t="inlineStr">
+      <c r="C8" s="46" t="inlineStr">
         <is>
           <t>관제용 고해상도 영상 스트림(온디맨드)</t>
         </is>
       </c>
-      <c r="D8" s="15" t="inlineStr">
+      <c r="D8" s="46" t="inlineStr">
         <is>
           <t>관제사(사람)가 로봇 시점 영상을 직접 확인해야 할 때(사각지대 확인, 원격 상황 판단, 기록·증거 확보), 로봇 탑재 카메라의 고해상도 원본 스트림을 온보드 라즈베리파이가 엣지노드로 전송한다. 환경인식용 프레임(HW-R-04)이 AI 추론이 소비하는 다운스케일(640급) 이미지인 것과 달리, 본 항목은 사람이 소비하는 원본 해상도 영상이며 관제 요청 시에만 스트림을 열어 무선 대역폭 소모를 최소화한다.</t>
         </is>
       </c>
-      <c r="E8" s="15" t="inlineStr">
+      <c r="E8" s="46" t="inlineStr">
         <is>
           <t>로봇 온보드 라즈베리파이→엣지노드</t>
         </is>
       </c>
-      <c r="F8" s="10" t="inlineStr">
+      <c r="F8" s="44" t="inlineStr">
         <is>
           <t>요청 시에만 전송(온디맨드), 전송 중 15fps 고해상도, HW-R-04에 편입 가능시 제외</t>
         </is>
       </c>
-      <c r="G8" s="15" t="inlineStr">
+      <c r="G8" s="46" t="inlineStr">
         <is>
           <t>상시 고해상도 스트리밍도 존재하나 무선 구간 대역폭을 상시 점유하여 낭비가 극심하고, AI 추론용 프레임(HW-R-04)으로 평시 관측은 이미 충족됨. 사람 시청 목적의 프레임레이트는 관제 업계 표준인 15fps로 충분하며 30fps는 개선이 미미한데 대역폭이 2배임(IPVM 가이드). 요청 기반 15fps 고해상도가 시청 품질과 대역폭의 균형이 가장 좋아 선정. 만약 필요하다면 HW-R-04에 편입되어 해상도를 조정할 예정</t>
         </is>
       </c>
-      <c r="H8" s="15" t="inlineStr">
+      <c r="H8" s="46" t="inlineStr">
         <is>
           <t>가시화, 백엔드 엣지노드</t>
         </is>
       </c>
-      <c r="I8" s="15" t="inlineStr">
+      <c r="I8" s="46" t="inlineStr">
         <is>
           <t>가시화 파트의 관제 화면(로봇 시점 실시간 뷰)에 표시되고, 엣지노드가 스트림 요청·중계를 담당</t>
         </is>
       </c>
-      <c r="J8" s="10" t="inlineStr">
+      <c r="J8" s="44" t="inlineStr">
         <is>
           <t>조병현</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="10" t="inlineStr">
+      <c r="A9" s="44" t="inlineStr">
         <is>
           <t>HW-R-08</t>
         </is>
       </c>
-      <c r="B9" s="13" t="inlineStr">
+      <c r="B9" s="45" t="inlineStr">
         <is>
           <t>로봇</t>
         </is>
       </c>
-      <c r="C9" s="15" t="inlineStr">
+      <c r="C9" s="46" t="inlineStr">
         <is>
           <t>구역 사전 정보(맵·경로) 수신</t>
         </is>
       </c>
-      <c r="D9" s="15" t="inlineStr">
+      <c r="D9" s="46" t="inlineStr">
         <is>
           <t>로봇이 특정 구역 진입 시 해당 구역 엣지노드로부터 구역 맵, 경로 계획(패스플랜), 주변 환경 정보 등 사전 정보 전체를 온보드 라즈베리파이가 수신하고, 이후 구역 내 환경 변화(신규 장애물, 통로 폐쇄, 이벤트 상황 등)가 발생하면 엣지노드가 변경분(델타)만 즉시 푸시하여 로봇이 보유한 사전 정보를 최신으로 유지한다. 구역의 CCTV 탐지·센서 이벤트가 모두 엣지노드로 모이므로 변화 감지·갱신 배포의 주체는 엣지노드로 한다. 객체 탐지는 엣지·서버가 수행하므로 로봇에는 모델이 아닌 주행·임무 수행에 필요한 환경 정보만 전달하여 로봇 측 연산 부담을 최소화한다.</t>
         </is>
       </c>
-      <c r="E9" s="15" t="inlineStr">
+      <c r="E9" s="46" t="inlineStr">
         <is>
           <t>엣지노드→로봇 온보드 라즈베리파이</t>
         </is>
       </c>
-      <c r="F9" s="10" t="inlineStr">
+      <c r="F9" s="44" t="inlineStr">
         <is>
           <t>구역 진입 시 1회 전체 수신 + 변경 이벤트 발생 시 델타 즉시 푸시</t>
         </is>
       </c>
-      <c r="G9" s="15" t="inlineStr">
+      <c r="G9" s="46" t="inlineStr">
         <is>
           <t>주기적 재전송 방식은 변화가 없는 구간의 반복 전송이 전부 낭비이고, 진입 시 1회만 수신하는 방식은 재난 등 동적 환경의 변화를 반영하지 못해 로봇이 낡은 정보로 주행하는 위험이 있음. 진입 시 1회 전체 + 변경 감지 시 변경분만 푸시하는 이벤트 기반 델타 갱신이 환경이 계속 변해도 최신성을 유지하면서 변화가 없으면 트래픽이 발생하지 않아 가장 효율적이라 선정.</t>
         </is>
       </c>
-      <c r="H9" s="15" t="inlineStr">
+      <c r="H9" s="46" t="inlineStr">
         <is>
           <t>AI, 백엔드 엣지노드</t>
         </is>
       </c>
-      <c r="I9" s="15" t="inlineStr">
+      <c r="I9" s="46" t="inlineStr">
         <is>
           <t>엣지노드가 구역별 환경 정보의 관리·배포 주체가 되고, AI가 생성한 서브태스크·경로 계획 결과가 이 사전 정보에 포함되어 전달됨</t>
         </is>
       </c>
-      <c r="J9" s="10" t="inlineStr">
+      <c r="J9" s="44" t="inlineStr">
         <is>
           <t>조병현</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="10" t="inlineStr">
+      <c r="A10" s="44" t="inlineStr">
         <is>
           <t>HW-R-09</t>
         </is>
       </c>
-      <c r="B10" s="13" t="inlineStr">
+      <c r="B10" s="45" t="inlineStr">
         <is>
           <t>로봇</t>
         </is>
       </c>
-      <c r="C10" s="15" t="inlineStr">
+      <c r="C10" s="46" t="inlineStr">
         <is>
           <t>통신 두절 시 버퍼링·재전송</t>
         </is>
       </c>
-      <c r="D10" s="15" t="inlineStr">
+      <c r="D10" s="46" t="inlineStr">
         <is>
           <t>엣지노드와의 통신이 끊긴 경우 로봇 온보드 라즈베리파이가 상태·인식 데이터를 로컬에 버퍼링하고, 전송 경로가 재연결되면 미전송분을 재전송한다. 재전송 시 원래 측정 시각의 타임스탬프를 유지하여 데이터 순서를 복원할 수 있어야 한다.</t>
         </is>
       </c>
-      <c r="E10" s="15" t="inlineStr">
+      <c r="E10" s="46" t="inlineStr">
         <is>
           <t>로봇 온보드 라즈베리파이→엣지노드</t>
         </is>
       </c>
-      <c r="F10" s="10" t="inlineStr">
+      <c r="F10" s="44" t="inlineStr">
         <is>
           <t>재연결 시 즉시 일괄 전송(이벤트 기반)</t>
         </is>
       </c>
-      <c r="G10" s="15" t="inlineStr">
+      <c r="G10" s="46" t="inlineStr">
         <is>
           <t>통신 두절 구간의 데이터를 유실하면 임무 분석·디버깅·디지털 트윈 최신성에 공백이 발생한다. 따라서 로컬 버퍼를 두고 재연결 시 미전송 데이터를 복구하는 구조를 기본으로 한다. 구체적인 전달 보장 방식(QoS, 재시도, 세션 유지 등)은 백엔드 파트에서 최종 확정한 전송 프로토콜의 기능을 따른다.</t>
         </is>
       </c>
-      <c r="H10" s="15" t="inlineStr">
+      <c r="H10" s="46" t="inlineStr">
         <is>
           <t>백엔드 엣지노드, 백엔드 서버</t>
         </is>
       </c>
-      <c r="I10" s="15" t="inlineStr">
+      <c r="I10" s="46" t="inlineStr">
         <is>
           <t>엣지노드의 브로커 재연결 처리와 백엔드 서버의 데이터 정합성(타임스탬프 기준 정렬) 처리에 연관</t>
         </is>
       </c>
-      <c r="J10" s="10" t="inlineStr">
+      <c r="J10" s="44" t="inlineStr">
         <is>
           <t>조병현</t>
         </is>
@@ -1175,7 +1175,7 @@
           <t>HW-R-10</t>
         </is>
       </c>
-      <c r="B11" s="13" t="inlineStr">
+      <c r="B11" s="45" t="inlineStr">
         <is>
           <t>로봇</t>
         </is>
@@ -1222,7 +1222,7 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="10" t="inlineStr">
+      <c r="A12" s="44" t="inlineStr">
         <is>
           <t>HW-S-01</t>
         </is>
@@ -1232,49 +1232,49 @@
           <t>센서</t>
         </is>
       </c>
-      <c r="C12" s="15" t="inlineStr">
+      <c r="C12" s="46" t="inlineStr">
         <is>
           <t>계측값 수집(센서→센서노드)</t>
         </is>
       </c>
-      <c r="D12" s="15" t="inlineStr">
+      <c r="D12" s="46" t="inlineStr">
         <is>
           <t>수위·온도·습도 등 환경 센서가 측정한 원시 계측값을 센서노드(라즈베리파이)가 센서가 낼 수 있는 최대 속도(샘플링 해상도 한계)로 상시 수집한다. 어떤 값을 얼마나 자주 밖으로 내보낼지의 취사선택(필터링·다운샘플링)은 원본을 전부 쥔 라즈베리파이가 담당하며, 수집값에는 측정 시각 타임스탬프와 장치ID를 부여한다.</t>
         </is>
       </c>
-      <c r="E12" s="15" t="inlineStr">
+      <c r="E12" s="46" t="inlineStr">
         <is>
           <t>센서→라즈베리파이</t>
         </is>
       </c>
-      <c r="F12" s="10" t="inlineStr">
+      <c r="F12" s="44" t="inlineStr">
         <is>
           <t>센서 최대 샘플링 속도로 상시 수집(해상도 한계까지)</t>
         </is>
       </c>
-      <c r="G12" s="15" t="inlineStr">
+      <c r="G12" s="46" t="inlineStr">
         <is>
           <t>수집 주기를 보고 주기에 맞춰 낮추는 방식도 존재하나, 유선 직결인 센서→라즈베리파이 구간은 전송 비용이 사실상 없고, 수집을 낮춰 버리면 이벤트 발생 시 고주기 보고로 전환해도 그 사이 데이터가 존재하지 않아 복원이 불가능함. 내부는 최대로 수집하고 외부 보고에서 조절하는 방식이 정보 손실 없이 낭비도 없는 유일한 구조라 선정.</t>
         </is>
       </c>
-      <c r="H12" s="15" t="inlineStr">
+      <c r="H12" s="46" t="inlineStr">
         <is>
           <t>백엔드 엣지노드</t>
         </is>
       </c>
-      <c r="I12" s="15" t="inlineStr">
+      <c r="I12" s="46" t="inlineStr">
         <is>
           <t>센서노드가 엣지노드로 보고하는 데이터(HW-S-02~03)의 원천 입력이 됨</t>
         </is>
       </c>
-      <c r="J12" s="10" t="inlineStr">
+      <c r="J12" s="44" t="inlineStr">
         <is>
           <t>조병현</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="10" t="inlineStr">
+      <c r="A13" s="44" t="inlineStr">
         <is>
           <t>HW-S-02</t>
         </is>
@@ -1284,49 +1284,49 @@
           <t>센서</t>
         </is>
       </c>
-      <c r="C13" s="15" t="inlineStr">
+      <c r="C13" s="46" t="inlineStr">
         <is>
           <t>계측 데이터 전달(평시)</t>
         </is>
       </c>
-      <c r="D13" s="15" t="inlineStr">
+      <c r="D13" s="46" t="inlineStr">
         <is>
           <t>센서노드(라즈베리파이)에 상시 상주하는 기본 수집 컨테이너가 계측값을 구역 엣지노드로 저주기 전달한다. 단, 라즈베리파이는 센서 값을 최대 속도로 상시 수집하고 있으므로(HW-S-01) 임계값 초과·급변(변화율 초과)은 로컬에서 즉시 감지하여 보고 주기와 무관하게 이벤트 메시지를 즉시 발행한다(report-by-exception, SCADA 표준 패턴). 즉 1분 주기는 '정상 범위' 정기 확인용이고, 위험 징후 감지는 주기에 얹히지 않아 지연이 없다. 기본 컨테이너는 하트비트(HW-S-06)와 함께 항상 유지된다(고주기 연속 보고는 HW-S-03의 별도 컨테이너가 담당).</t>
         </is>
       </c>
-      <c r="E13" s="15" t="inlineStr">
+      <c r="E13" s="46" t="inlineStr">
         <is>
           <t>라즈베리파이→엣지노드</t>
         </is>
       </c>
-      <c r="F13" s="10" t="inlineStr">
+      <c r="F13" s="44" t="inlineStr">
         <is>
           <t>평시 1분 1회 + 임계값 초과·급변 시 주기 무관 즉시 발행</t>
         </is>
       </c>
-      <c r="G13" s="15" t="inlineStr">
+      <c r="G13" s="46" t="inlineStr">
         <is>
           <t>1초 1회 등 고주기도 존재하나 평시에는 동일 값 반복 전송으로 네트워크·저장 낭비가 큼. 국가 홍수관제(한강홍수통제소)의 공식 수위 관측 제공 주기가 10분 단위인 것과 비교하면 평시 1분은 이미 10배 조밀한 수준임. 위험 감지 지연은 주기가 아니라 로컬 임계값 감시의 즉시 발행이 담당하므로, 평시 1분 + 예외 즉시 보고 조합이 감지 지연 없이 낭비가 가장 적어 선정.</t>
         </is>
       </c>
-      <c r="H13" s="15" t="inlineStr">
+      <c r="H13" s="46" t="inlineStr">
         <is>
           <t>백엔드 엣지노드, 백엔드 서버</t>
         </is>
       </c>
-      <c r="I13" s="15" t="inlineStr">
+      <c r="I13" s="46" t="inlineStr">
         <is>
           <t>엣지노드가 구역 내 센서 데이터를 취합하는 입력이 되고, 백엔드 서버의 시계열 저장·이력 조회 대상이 됨</t>
         </is>
       </c>
-      <c r="J13" s="10" t="inlineStr">
+      <c r="J13" s="44" t="inlineStr">
         <is>
           <t>조병현</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="10" t="inlineStr">
+      <c r="A14" s="44" t="inlineStr">
         <is>
           <t>HW-S-03</t>
         </is>
@@ -1336,49 +1336,49 @@
           <t>센서</t>
         </is>
       </c>
-      <c r="C14" s="15" t="inlineStr">
+      <c r="C14" s="46" t="inlineStr">
         <is>
           <t>이벤트 모드 고주기 보고</t>
         </is>
       </c>
-      <c r="D14" s="15" t="inlineStr">
+      <c r="D14" s="46" t="inlineStr">
         <is>
           <t>강우 감지·수위 임계값 초과 등 이벤트 발생 시, 엣지노드의 쿠버네티스가 센서노드에 고주기 모니터링 컨테이너를 배포하여 1초 주기 보고로 전환한다. 홍수 등 재난 상황에서는 대응 골든타임이 존재하므로, 상황 발생 시 실시간성에 준하는 데이터 갱신이 필요하여 정의한다. 상황 종료 시 해당 컨테이너는 제거되어 평시(기본 컨테이너 저주기 보고)로 복귀한다.</t>
         </is>
       </c>
-      <c r="E14" s="15" t="inlineStr">
+      <c r="E14" s="46" t="inlineStr">
         <is>
           <t>라즈베리파이→엣지노드</t>
         </is>
       </c>
-      <c r="F14" s="10" t="inlineStr">
+      <c r="F14" s="44" t="inlineStr">
         <is>
           <t>이벤트 발생 시 1초 1회로 전환</t>
         </is>
       </c>
-      <c r="G14" s="15" t="inlineStr">
+      <c r="G14" s="46" t="inlineStr">
         <is>
           <t>이벤트 시에도 평시 주기(1분)를 유지하는 방식은 골든타임 내 대응이 불가능하고, 1초 미만 주기는 센서 해상도를 초과하여 의미가 없음. 1초 주기가 골든타임 대응과 유효 데이터 생산의 접점이라 선정.</t>
         </is>
       </c>
-      <c r="H14" s="15" t="inlineStr">
+      <c r="H14" s="46" t="inlineStr">
         <is>
           <t>백엔드 서버, 가시화, AI</t>
         </is>
       </c>
-      <c r="I14" s="15" t="inlineStr">
+      <c r="I14" s="46" t="inlineStr">
         <is>
           <t>서버가 임계값 판단·알림을 발행하고, 가시화가 실시간 수위 그래프를 갱신하며, AI가 상황 인지·예측의 입력으로 사용</t>
         </is>
       </c>
-      <c r="J14" s="10" t="inlineStr">
+      <c r="J14" s="44" t="inlineStr">
         <is>
           <t>조병현</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="10" t="inlineStr">
+      <c r="A15" s="44" t="inlineStr">
         <is>
           <t>HW-S-04</t>
         </is>
@@ -1388,49 +1388,49 @@
           <t>센서</t>
         </is>
       </c>
-      <c r="C15" s="15" t="inlineStr">
+      <c r="C15" s="46" t="inlineStr">
         <is>
           <t>적응형 주기 전환 명령 수신</t>
         </is>
       </c>
-      <c r="D15" s="15" t="inlineStr">
+      <c r="D15" s="46" t="inlineStr">
         <is>
           <t>엣지노드가 상황 판단(강우 시작·종료 등)에 따라 센서노드의 모니터링 모드를 전환한다. 전환의 실체는 쿠버네티스를 통한 컨테이너 배포/제거이다: 강우 시작 시 고주기 모니터링 컨테이너를 배포하고, 종료 시 제거하여 평시로 복귀한다. 평시↔이벤트 모드 전환을 센서 단독 판단이 아닌 엣지노드 주도로 제어하여 구역 단위 일관성을 확보하기 위해 정의한다.</t>
         </is>
       </c>
-      <c r="E15" s="15" t="inlineStr">
+      <c r="E15" s="46" t="inlineStr">
         <is>
           <t>엣지노드→라즈베리파이</t>
         </is>
       </c>
-      <c r="F15" s="10" t="inlineStr">
+      <c r="F15" s="44" t="inlineStr">
         <is>
           <t>이벤트 기반(상황 변화 시 즉시)</t>
         </is>
       </c>
-      <c r="G15" s="15" t="inlineStr">
+      <c r="G15" s="46" t="inlineStr">
         <is>
           <t>센서노드가 자체 판단으로 전환하는 방식도 존재하나 구역 전체 상황(주변 센서·기상 정보)을 모르는 채 판단하면 오전환이 발생함. 구역 상황을 종합하는 엣지노드가 쿠버네티스 배포/제거로 전환하는 방식이 가장 정확하고, 전환 이력이 쿠버네티스에 선언적으로 남아 검증·디버깅에도 유리하여 선정.</t>
         </is>
       </c>
-      <c r="H15" s="15" t="inlineStr">
+      <c r="H15" s="46" t="inlineStr">
         <is>
           <t>백엔드 엣지노드</t>
         </is>
       </c>
-      <c r="I15" s="15" t="inlineStr">
+      <c r="I15" s="46" t="inlineStr">
         <is>
           <t>엣지노드의 구역 상황 판단 로직 및 프로세스 제어(기동/종료) 기능과 직접 연동</t>
         </is>
       </c>
-      <c r="J15" s="10" t="inlineStr">
+      <c r="J15" s="44" t="inlineStr">
         <is>
           <t>조병현</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="10" t="inlineStr">
+      <c r="A16" s="44" t="inlineStr">
         <is>
           <t>HW-S-05</t>
         </is>
@@ -1440,49 +1440,49 @@
           <t>센서</t>
         </is>
       </c>
-      <c r="C16" s="15" t="inlineStr">
+      <c r="C16" s="46" t="inlineStr">
         <is>
           <t>센서노드(라즈베리파이) 하트비트</t>
         </is>
       </c>
-      <c r="D16" s="15" t="inlineStr">
+      <c r="D16" s="46" t="inlineStr">
         <is>
           <t>센서를 담당하는 라즈베리파이(항상 켜져 있는 상시 노드)가 자신의 생존 상태를 엣지노드로 주기 전송한다. 하트비트는 노드(라즈베리파이) 수준의 생존 확인용이며, 노드 위에서 올렸다 내렸다 하는 개별 기능(계측·보고 컨테이너)의 생존은 엣지노드의 쿠버네티스가 liveness probe·파드 상태로 감시하고 비정상 종료 시 자동 재기동한다. 센서 값이 오지 않는 상황이 '센서 값 무변화'인지 '노드 장애'인지 '컨테이너 장애'인지 구분하기 위해 계측 데이터와 별도 채널의 생존 확인이 필요하여 정의한다.</t>
         </is>
       </c>
-      <c r="E16" s="15" t="inlineStr">
+      <c r="E16" s="46" t="inlineStr">
         <is>
           <t>라즈베리파이→엣지노드</t>
         </is>
       </c>
-      <c r="F16" s="10" t="inlineStr">
+      <c r="F16" s="44" t="inlineStr">
         <is>
           <t>5초 1회</t>
         </is>
       </c>
-      <c r="G16" s="15" t="inlineStr">
+      <c r="G16" s="46" t="inlineStr">
         <is>
           <t>1초 주기도 존재하나 센서노드는 고정 설치에 수량이 많아(구역당 수백 대 가능) 국가 단위에서는 누적 트래픽 낭비가 크고, 급사 감지는 LWT가 담당하므로 1초의 이득이 작음. 1분은 행(hang) 상태 감지가 평시 보고 주기와 겹쳐 무의미함. 5초가 장애 감지 지연과 대규모 확장 시 부하의 균형이 가장 좋아 선정.</t>
         </is>
       </c>
-      <c r="H16" s="15" t="inlineStr">
+      <c r="H16" s="46" t="inlineStr">
         <is>
           <t>백엔드 엣지노드, 가시화</t>
         </is>
       </c>
-      <c r="I16" s="15" t="inlineStr">
+      <c r="I16" s="46" t="inlineStr">
         <is>
           <t>엣지노드의 노드 생존 관리 및 가시화의 구역별 센서노드 온라인/오프라인 표시와 연동</t>
         </is>
       </c>
-      <c r="J16" s="10" t="inlineStr">
+      <c r="J16" s="44" t="inlineStr">
         <is>
           <t>조병현</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="10" t="inlineStr">
+      <c r="A17" s="44" t="inlineStr">
         <is>
           <t>HW-S-06</t>
         </is>
@@ -1492,49 +1492,49 @@
           <t>센서</t>
         </is>
       </c>
-      <c r="C17" s="15" t="inlineStr">
+      <c r="C17" s="46" t="inlineStr">
         <is>
           <t>고정 비전센서(CCTV) 영상 전달</t>
         </is>
       </c>
-      <c r="D17" s="15" t="inlineStr">
+      <c r="D17" s="46" t="inlineStr">
         <is>
           <t>구역에 고정 설치된 비전 센서(웹캠·CCTV·360도 카메라)의 영상 스트림을 엣지노드로 상시 전달한다. 객체 탐지는 로봇 카메라와 동일하게 엣지노드·메인서버가 수행하며(HW-R-04와 동일 원칙), 카메라는 촬영·전달만 담당한다. 위치가 고정되어 상대 거리 산출이 용이하므로 이 영상이 디지털 트윈의 1차 구성·동기화와 신규 객체 출현 감지의 기준 입력이 된다.</t>
         </is>
       </c>
-      <c r="E17" s="15" t="inlineStr">
+      <c r="E17" s="46" t="inlineStr">
         <is>
           <t>센서(고정 카메라)→엣지노드</t>
         </is>
       </c>
-      <c r="F17" s="10" t="inlineStr">
+      <c r="F17" s="44" t="inlineStr">
         <is>
           <t>상시 15fps 스트림</t>
         </is>
       </c>
-      <c r="G17" s="15" t="inlineStr">
+      <c r="G17" s="46" t="inlineStr">
         <is>
           <t>카메라가 고정이어도 관측 대상(사람·수위·로봇)은 이동체이므로 이동체 포착 기준인 업계 평균 15fps가 그대로 적용됨(IPVM 가이드: 1fps는 보행자가 프레임 간 약 1.2m 이동해 부족, 30fps는 개선 미미에 비용 2배). 고정 카메라 구간은 유선(구내망) 직결이라 무선 대역폭 제약도 없음. 실제 병목은 전송이 아닌 엣지 추론 용량이므로, 엣지노드가 채널별 15fps 입력 중 추론 용량에 맞춰 프레임을 선별 처리하는 구조가 가장 효율적이라 선정.</t>
         </is>
       </c>
-      <c r="H17" s="15" t="inlineStr">
+      <c r="H17" s="46" t="inlineStr">
         <is>
           <t>AI, 가시화, 백엔드 서버</t>
         </is>
       </c>
-      <c r="I17" s="15" t="inlineStr">
+      <c r="I17" s="46" t="inlineStr">
         <is>
           <t>AI의 디지털 트윈 1차 동기화·신규 객체 인식 입력이 되고, 가시화의 트윈 맵 갱신과 서버 저장에 연관</t>
         </is>
       </c>
-      <c r="J17" s="10" t="inlineStr">
+      <c r="J17" s="44" t="inlineStr">
         <is>
           <t>조병현</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="10" t="inlineStr">
+      <c r="A18" s="44" t="inlineStr">
         <is>
           <t>HW-S-07</t>
         </is>
@@ -1544,49 +1544,49 @@
           <t>센서</t>
         </is>
       </c>
-      <c r="C18" s="15" t="inlineStr">
+      <c r="C18" s="46" t="inlineStr">
         <is>
           <t>오프라인 감지 및 상태 반영</t>
         </is>
       </c>
-      <c r="D18" s="15" t="inlineStr">
+      <c r="D18" s="46" t="inlineStr">
         <is>
           <t>센서노드가 비정상 종료·전원 차단 또는 통신 두절된 경우 엣지노드가 오프라인 상태를 감지하여 메인서버에 반영해야 한다. 구체적인 단절 감지 방식은 백엔드 파트에서 최종 확정한 전송 프로토콜의 세션 단절 감지 기능을 우선 활용하고, 해당 기능이 없는 경우 HW-S-05 하트비트 타임아웃을 사용한다.</t>
         </is>
       </c>
-      <c r="E18" s="15" t="inlineStr">
+      <c r="E18" s="46" t="inlineStr">
         <is>
           <t>엣지노드→메인서버</t>
         </is>
       </c>
-      <c r="F18" s="10" t="inlineStr">
+      <c r="F18" s="44" t="inlineStr">
         <is>
           <t>연결 단절 시 즉시(이벤트 기반)</t>
         </is>
       </c>
-      <c r="G18" s="15" t="inlineStr">
+      <c r="G18" s="46" t="inlineStr">
         <is>
           <t>하트비트만으로 장애를 판단하면 타임아웃만큼 감지 지연이 발생할 수 있으므로, 최종 전송 프로토콜이 연결 단절 이벤트를 제공하는 경우 이를 우선 활용한다. 프로토콜이 해당 기능을 제공하지 않으면 HW-S-05의 5초 하트비트를 기준으로 연속 미수신 횟수를 정해 오프라인을 판정한다.</t>
         </is>
       </c>
-      <c r="H18" s="15" t="inlineStr">
+      <c r="H18" s="46" t="inlineStr">
         <is>
           <t>백엔드 서버, 가시화</t>
         </is>
       </c>
-      <c r="I18" s="15" t="inlineStr">
+      <c r="I18" s="46" t="inlineStr">
         <is>
           <t>서버의 장치 상태 테이블 갱신과 가시화의 오프라인 상태 표시(끊김 조회) 기능에 직접 연관</t>
         </is>
       </c>
-      <c r="J18" s="10" t="inlineStr">
+      <c r="J18" s="44" t="inlineStr">
         <is>
           <t>조병현</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="10" t="inlineStr">
+      <c r="A19" s="44" t="inlineStr">
         <is>
           <t>HW-S-08</t>
         </is>
@@ -1596,42 +1596,42 @@
           <t>센서</t>
         </is>
       </c>
-      <c r="C19" s="15" t="inlineStr">
+      <c r="C19" s="46" t="inlineStr">
         <is>
           <t>시각 동기화(타임스탬프)</t>
         </is>
       </c>
-      <c r="D19" s="15" t="inlineStr">
+      <c r="D19" s="46" t="inlineStr">
         <is>
           <t>모든 센서노드(로봇 온보드 라즈베리파이 포함)는 NTP로 시각을 동기화하고, 모든 계측 데이터에 측정 시각 타임스탬프를 포함하여 전달한다. 구역·장치별로 수집된 데이터를 서버에서 병합·정렬하고 디지털 트윈의 시의성(최신성)을 판단하기 위해 정의한다.</t>
         </is>
       </c>
-      <c r="E19" s="15" t="inlineStr">
+      <c r="E19" s="46" t="inlineStr">
         <is>
           <t>메인서버→라즈베리파이</t>
         </is>
       </c>
-      <c r="F19" s="10" t="inlineStr">
+      <c r="F19" s="44" t="inlineStr">
         <is>
           <t>NTP 동기화 1시간 1회, 타임스탬프는 매 데이터 포함</t>
         </is>
       </c>
-      <c r="G19" s="15" t="inlineStr">
+      <c r="G19" s="46" t="inlineStr">
         <is>
           <t>동기화 없이 서버 수신 시각을 사용하는 방식도 존재하나 버퍼링·재전송 시 실제 측정 시각과 어긋나 정합성이 깨짐. 1시간 주기 NTP 동기화가 라즈베리파이 시계 오차(드리프트)를 충분히 보정하면서 부하가 가장 적어 선정.</t>
         </is>
       </c>
-      <c r="H19" s="15" t="inlineStr">
+      <c r="H19" s="46" t="inlineStr">
         <is>
           <t>백엔드 서버, AI</t>
         </is>
       </c>
-      <c r="I19" s="15" t="inlineStr">
+      <c r="I19" s="46" t="inlineStr">
         <is>
           <t>서버의 시계열 병합·정렬 처리와 AI의 시간 기반 학습 데이터 구성(최신성 판단)에 연관</t>
         </is>
       </c>
-      <c r="J19" s="10" t="inlineStr">
+      <c r="J19" s="44" t="inlineStr">
         <is>
           <t>조병현</t>
         </is>
@@ -1653,44 +1653,44 @@
           <t>하드웨어-엣지노드 전송 인터페이스(백엔드 확정 예정)</t>
         </is>
       </c>
-      <c r="D20" s="15" t="inlineStr">
+      <c r="D20" s="46" t="inlineStr">
         <is>
           <t>하드웨어와 엣지노드 사이의 상태·센서·제어·영상 데이터는 백엔드 파트에서 최종 확정한 전송 인터페이스 및 프로토콜을 따라 송수신해야 한다. 현재 MQTT 등은 후보 기술 또는 구현 예시로만 두며, 최종 프로토콜이 확정되면 하드웨어 파트의 전송 규격과 세부 기능을 해당 방식에 맞춰 일치시킨다.</t>
         </is>
       </c>
-      <c r="E20" s="15" t="inlineStr">
+      <c r="E20" s="46" t="inlineStr">
         <is>
           <t>하드웨어 장치↔엣지노드</t>
         </is>
       </c>
-      <c r="F20" s="10" t="inlineStr">
+      <c r="F20" s="44" t="inlineStr">
         <is>
           <t>상시 적용(전송 규격)</t>
         </is>
       </c>
-      <c r="G20" s="15" t="inlineStr">
+      <c r="G20" s="46" t="inlineStr">
         <is>
           <t>전송 프로토콜을 하드웨어 파트에서 선확정하면 백엔드 아키텍처 변경 시 파트 간 인터페이스 불일치가 발생할 수 있다. 따라서 하드웨어 요구사항에서는 필요한 기능과 데이터 흐름을 우선 정의하고, 실제 프로토콜·전달 보장·세션 관리 방식은 백엔드 확정 사항을 따른다.</t>
         </is>
       </c>
-      <c r="H20" s="15" t="inlineStr">
+      <c r="H20" s="46" t="inlineStr">
         <is>
           <t>백엔드 서버, 백엔드 엣지노드, AI, 가시화</t>
         </is>
       </c>
-      <c r="I20" s="15" t="inlineStr">
+      <c r="I20" s="46" t="inlineStr">
         <is>
           <t>전 파트가 동일한 최종 전송 인터페이스를 사용하도록 백엔드 확정 사항을 하드웨어 요구사항에 반영</t>
         </is>
       </c>
-      <c r="J20" s="10" t="inlineStr">
+      <c r="J20" s="44" t="inlineStr">
         <is>
           <t>조병현</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="10" t="inlineStr">
+      <c r="A21" s="44" t="inlineStr">
         <is>
           <t>HW-C-02</t>
         </is>
@@ -1700,49 +1700,49 @@
           <t>공통</t>
         </is>
       </c>
-      <c r="C21" s="15" t="inlineStr">
+      <c r="C21" s="46" t="inlineStr">
         <is>
           <t>표준 메시지 규격·채널/토픽 체계</t>
         </is>
       </c>
-      <c r="D21" s="15" t="inlineStr">
+      <c r="D21" s="46" t="inlineStr">
         <is>
           <t>모든 장치는 합의된 데이터 채널 구조와 공통 메시지 스키마(장치ID, 타임스탬프, 값, 상태코드, 스키마 버전 등)를 따라야 한다. 채널·토픽의 실제 표현 방식은 백엔드에서 최종 선택한 전송 프로토콜의 주소·채널 체계에 맞춰 정의한다.</t>
         </is>
       </c>
-      <c r="E21" s="15" t="inlineStr">
+      <c r="E21" s="46" t="inlineStr">
         <is>
           <t>하드웨어 장치→엣지노드</t>
         </is>
       </c>
-      <c r="F21" s="10" t="inlineStr">
+      <c r="F21" s="44" t="inlineStr">
         <is>
           <t>상시 적용(규격), 스키마 변경 시 버전 관리</t>
         </is>
       </c>
-      <c r="G21" s="15" t="inlineStr">
+      <c r="G21" s="46" t="inlineStr">
         <is>
           <t>전송 기술이 변경되더라도 파트 간 데이터 의미와 필드 구조가 유지되어야 하므로 공통 스키마와 버전 관리는 별도로 고정한다. 채널·토픽 명명 규칙만 최종 프로토콜에 맞추어 조정하면 하드웨어·AI·가시화 파트의 재작업을 줄일 수 있다.</t>
         </is>
       </c>
-      <c r="H21" s="15" t="inlineStr">
+      <c r="H21" s="46" t="inlineStr">
         <is>
           <t>AI, 가시화, 백엔드 서버, 백엔드 엣지노드</t>
         </is>
       </c>
-      <c r="I21" s="15" t="inlineStr">
+      <c r="I21" s="46" t="inlineStr">
         <is>
           <t>전 파트가 이 스키마를 기준으로 파싱·저장·시각화하므로 모든 인터페이스 정의의 기준 문서가 됨</t>
         </is>
       </c>
-      <c r="J21" s="10" t="inlineStr">
+      <c r="J21" s="44" t="inlineStr">
         <is>
           <t>조병현</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="10" t="inlineStr">
+      <c r="A22" s="44" t="inlineStr">
         <is>
           <t>HW-C-03</t>
         </is>
@@ -1752,49 +1752,49 @@
           <t>공통</t>
         </is>
       </c>
-      <c r="C22" s="15" t="inlineStr">
+      <c r="C22" s="46" t="inlineStr">
         <is>
           <t>컨테이너 기반 구조(쿠버네티스 배포·제거)</t>
         </is>
       </c>
-      <c r="D22" s="15" t="inlineStr">
+      <c r="D22" s="46" t="inlineStr">
         <is>
           <t>장치 내 수집·보고·모니터링 기능은 기능 단위의 도커 컨테이너로 패키징하고, 구역 엣지노드의 쿠버네티스(라즈베리파이 환경 특성상 경량판 K3s)가 센서노드·로봇 온보드 라즈베리파이를 워커 노드로 편입하여 상황에 따라 컨테이너를 배포(기동)/제거(종료)한다. 예: 수위 고주기 모니터링 컨테이너는 강우 시작 시 배포되고 강우 종료 시 내려간다. 필요 시에만 컨테이너를 띄워 저사양 장치의 자원을 절약하고, 기능별 장애 격리와 비정상 종료 시 자동 재기동(쿠버네티스 셀프힐링)을 확보하기 위해 정의한다.</t>
         </is>
       </c>
-      <c r="E22" s="15" t="inlineStr">
+      <c r="E22" s="46" t="inlineStr">
         <is>
           <t>엣지노드→하드웨어 장치</t>
         </is>
       </c>
-      <c r="F22" s="10" t="inlineStr">
+      <c r="F22" s="44" t="inlineStr">
         <is>
           <t>이벤트 기반(상황 발생·해제 시 기동/종료)</t>
         </is>
       </c>
-      <c r="G22" s="15" t="inlineStr">
+      <c r="G22" s="46" t="inlineStr">
         <is>
           <t>단일 상주 프로세스+스레드 제어 방식은 미사용 기능이 상시 자원을 점유하고 오류 전파 위험이 크며, systemd 등 개별 프로세스 관리 방식은 다수 구역·다수 노드에 동일 구성을 배포·갱신하기 어려움. 쿠버네티스는 CNCF 표준이며 K3s는 CNCF 인증 경량 배포판으로 라즈베리파이급 엣지 장치를 공식 지원함. 선언적 상태 관리, 죽은 컨테이너 자동 재기동, 버전 롤백을 제공하여 국가 단위 다수 노드 운영에서 관리 비용이 가장 낮아 선정.</t>
         </is>
       </c>
-      <c r="H22" s="15" t="inlineStr">
+      <c r="H22" s="46" t="inlineStr">
         <is>
           <t>백엔드 엣지노드</t>
         </is>
       </c>
-      <c r="I22" s="15" t="inlineStr">
+      <c r="I22" s="46" t="inlineStr">
         <is>
           <t>엣지노드의 장치 제어 명령 체계와 상태 다이어그램(프로세스 기동/종료 상태) 설계에 직접 연관</t>
         </is>
       </c>
-      <c r="J22" s="10" t="inlineStr">
+      <c r="J22" s="44" t="inlineStr">
         <is>
           <t>조병현</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="10" t="inlineStr">
+      <c r="A23" s="44" t="inlineStr">
         <is>
           <t>HW-C-04</t>
         </is>
@@ -1804,42 +1804,42 @@
           <t>공통</t>
         </is>
       </c>
-      <c r="C23" s="15" t="inlineStr">
+      <c r="C23" s="46" t="inlineStr">
         <is>
           <t>장치 상태·구역 등록 관리</t>
         </is>
       </c>
-      <c r="D23" s="15" t="inlineStr">
+      <c r="D23" s="46" t="inlineStr">
         <is>
           <t>모든 하드웨어 장치는 최초 접속 시 자신이 속한 구역과 장치 정보를 엣지노드에 등록하고, 엣지노드는 구역 단위 장치 목록과 온라인/오프라인 상태를 유지한다. '접속 시 등록(Birth) → 단절 시 즉시 반영(Death)' 구조는 산업 IoT 표준 Eclipse Sparkplug의 Birth/Death Certificate 패턴과 동일하다. '해당 로봇이 어느 구역에서 온라인 중이다'를 관제 화면에 표시하기 위해 정의한다.</t>
         </is>
       </c>
-      <c r="E23" s="15" t="inlineStr">
+      <c r="E23" s="46" t="inlineStr">
         <is>
           <t>하드웨어 장치→엣지노드</t>
         </is>
       </c>
-      <c r="F23" s="10" t="inlineStr">
+      <c r="F23" s="44" t="inlineStr">
         <is>
           <t>등록은 접속 시 1회, 상태 요약 갱신은 5초 1회</t>
         </is>
       </c>
-      <c r="G23" s="15" t="inlineStr">
+      <c r="G23" s="46" t="inlineStr">
         <is>
           <t>매 하트비트를 서버까지 그대로 중계하는 방식도 존재하나 국가 단위에서는 장치 수에 비례해 서버 트래픽이 폭증함. 하트비트는 구역 엣지노드에서 소비·집계하고 서버에는 5초 주기 요약(또는 상태 변화 시에만)만 올리는 방식이 서버 부하를 장치 수와 무관하게 구역 수에만 비례하도록 만들어 확장성이 가장 좋아 선정.</t>
         </is>
       </c>
-      <c r="H23" s="15" t="inlineStr">
+      <c r="H23" s="46" t="inlineStr">
         <is>
           <t>백엔드 서버, 가시화</t>
         </is>
       </c>
-      <c r="I23" s="15" t="inlineStr">
+      <c r="I23" s="46" t="inlineStr">
         <is>
           <t>서버의 장치 관리 테이블과 가시화의 구역별 장치 현황판(온라인 상태 조회)에 직접 연관</t>
         </is>
       </c>
-      <c r="J23" s="10" t="inlineStr">
+      <c r="J23" s="44" t="inlineStr">
         <is>
           <t>조병현</t>
         </is>
@@ -1861,44 +1861,44 @@
           <t>관측 데이터(OpenTelemetry) 계측(정해지면 사용)</t>
         </is>
       </c>
-      <c r="D24" s="15" t="inlineStr">
+      <c r="D24" s="46" t="inlineStr">
         <is>
           <t>각 하드웨어 노드(센서노드·로봇 온보드 라즈베리파이)는 CPU/메모리 사용률, 전송 성공·실패 횟수, 지연 시간 등 시스템 관측 지표를 OpenTelemetry 규격으로 계측하여 엣지노드의 Collector에 전달한다. 데이터 전달(MQTT)과 시스템 관측(OTel)의 역할을 분리하여 장애 원인 추적을 가능하게 하기 위해 정의한다.</t>
         </is>
       </c>
-      <c r="E24" s="15" t="inlineStr">
+      <c r="E24" s="46" t="inlineStr">
         <is>
           <t>하드웨어 장치→엣지노드</t>
         </is>
       </c>
-      <c r="F24" s="10" t="inlineStr">
+      <c r="F24" s="44" t="inlineStr">
         <is>
           <t>지표 수집 15초 1회</t>
         </is>
       </c>
-      <c r="G24" s="15" t="inlineStr">
+      <c r="G24" s="46" t="inlineStr">
         <is>
           <t>1초 수집은 관측 데이터 자체가 부하가 되고, 1분 수집은 순간 장애의 원인 구간 특정이 어려움. 15초는 관측 업계의 사실상 표준인 Prometheus의 기본 스크레이프 주기로, 관측 오버헤드와 장애 추적 해상도의 균형점으로 업계에서 검증된 값이라 선정.</t>
         </is>
       </c>
-      <c r="H24" s="15" t="inlineStr">
+      <c r="H24" s="46" t="inlineStr">
         <is>
           <t>백엔드 서버, 백엔드 엣지노드, 가시화</t>
         </is>
       </c>
-      <c r="I24" s="15" t="inlineStr">
+      <c r="I24" s="46" t="inlineStr">
         <is>
           <t>백엔드의 관측 파이프라인(Collector·저장소) 구성과 가시화의 시스템 상태 대시보드에 연관되며, 업무 데이터 전송 계층과 관측 계층의 역할을 분리</t>
         </is>
       </c>
-      <c r="J24" s="10" t="inlineStr">
+      <c r="J24" s="44" t="inlineStr">
         <is>
           <t>조병현</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="10" t="inlineStr">
+      <c r="A25" s="44" t="inlineStr">
         <is>
           <t>HW-C-06</t>
         </is>
@@ -1908,42 +1908,42 @@
           <t>공통</t>
         </is>
       </c>
-      <c r="C25" s="15" t="inlineStr">
+      <c r="C25" s="46" t="inlineStr">
         <is>
           <t>제어 명령 수신 및 ACK 응답</t>
         </is>
       </c>
-      <c r="D25" s="15" t="inlineStr">
+      <c r="D25" s="46" t="inlineStr">
         <is>
           <t>엣지노드가 하달하는 제어 명령(주기 변경, 프로세스 기동/종료, 임무 하달, 모터 구동 등)에 대해 장치는 수신 확인(ACK)과 수행 결과를 응답한다. 특히 모터 구동처럼 되돌리기 어려운 명령은 '명령 하달→수신 확인→수행 결과 확인'까지를 하나의 절차로 보장하기 위해 정의한다.</t>
         </is>
       </c>
-      <c r="E25" s="15" t="inlineStr">
+      <c r="E25" s="46" t="inlineStr">
         <is>
           <t>엣지노드→하드웨어 장치</t>
         </is>
       </c>
-      <c r="F25" s="10" t="inlineStr">
+      <c r="F25" s="44" t="inlineStr">
         <is>
           <t>이벤트 기반, ACK는 수신 즉시·결과는 수행 완료 시</t>
         </is>
       </c>
-      <c r="G25" s="15" t="inlineStr">
+      <c r="G25" s="46" t="inlineStr">
         <is>
           <t>ACK 없이 단방향 명령만 전달하면 명령 유실 시 수행 여부를 확인하기 어렵다. 따라서 수신 확인과 실제 수행 결과를 분리하여 관리하고, 재전송·중복 방지·전달 보장 방식은 백엔드에서 최종 확정한 전송 프로토콜의 기능을 따른다.</t>
         </is>
       </c>
-      <c r="H25" s="15" t="inlineStr">
+      <c r="H25" s="46" t="inlineStr">
         <is>
           <t>백엔드 서버, 백엔드 엣지노드, 가시화</t>
         </is>
       </c>
-      <c r="I25" s="15" t="inlineStr">
+      <c r="I25" s="46" t="inlineStr">
         <is>
           <t>서버의 명령 발행·이력 관리, 엣지노드의 명령 중계, 가시화의 명령 수행 상태(성공/실패) 표시와 연관</t>
         </is>
       </c>
-      <c r="J25" s="10" t="inlineStr">
+      <c r="J25" s="44" t="inlineStr">
         <is>
           <t>조병현</t>
         </is>
@@ -4947,7 +4947,7 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O29"/>
+  <dimension ref="A1:O33"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="12.63" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
     <col width="10" customWidth="1" style="43" min="1" max="1"/>
@@ -5065,7 +5065,7 @@
           <t>HW-R-02, HW-R-03, HW-S-02, HW-S-07, HW-C-01, HW-C-02</t>
         </is>
       </c>
-      <c r="J2" s="47" t="inlineStr">
+      <c r="J2" s="44" t="inlineStr">
         <is>
           <t>김현우</t>
         </is>
@@ -5117,7 +5117,7 @@
           <t>HW-R-03, HW-S-02, HW-C-04</t>
         </is>
       </c>
-      <c r="J3" s="47" t="inlineStr">
+      <c r="J3" s="44" t="inlineStr">
         <is>
           <t>김현우</t>
         </is>
@@ -5169,7 +5169,7 @@
           <t>HW-C-04, HW-C-07, RS-01, RS-04</t>
         </is>
       </c>
-      <c r="J4" s="47" t="inlineStr">
+      <c r="J4" s="44" t="inlineStr">
         <is>
           <t>김현우</t>
         </is>
@@ -5221,7 +5221,7 @@
           <t>HW-C-05, HW-S-03, OB-01</t>
         </is>
       </c>
-      <c r="J5" s="47" t="inlineStr">
+      <c r="J5" s="44" t="inlineStr">
         <is>
           <t>김현우</t>
         </is>
@@ -5273,7 +5273,7 @@
           <t>HW-C-06, RK-03</t>
         </is>
       </c>
-      <c r="J6" s="47" t="inlineStr">
+      <c r="J6" s="44" t="inlineStr">
         <is>
           <t>김현우</t>
         </is>
@@ -5325,7 +5325,7 @@
           <t>HW-R-07, HW-S-06</t>
         </is>
       </c>
-      <c r="J7" s="47" t="inlineStr">
+      <c r="J7" s="44" t="inlineStr">
         <is>
           <t>김현우</t>
         </is>
@@ -5377,7 +5377,7 @@
           <t>HW-R-04, OD-01, EG-02, EG-03, GN-03</t>
         </is>
       </c>
-      <c r="J8" s="47" t="inlineStr">
+      <c r="J8" s="44" t="inlineStr">
         <is>
           <t>김현우</t>
         </is>
@@ -5429,7 +5429,7 @@
           <t>RK-01, RK-02, RK-03, HW-S-03</t>
         </is>
       </c>
-      <c r="J9" s="47" t="inlineStr">
+      <c r="J9" s="44" t="inlineStr">
         <is>
           <t>김현우</t>
         </is>
@@ -5481,7 +5481,7 @@
           <t>PR-01, PR-02, PR-04, PR-03(선택적 확장)</t>
         </is>
       </c>
-      <c r="J10" s="47" t="inlineStr">
+      <c r="J10" s="44" t="inlineStr">
         <is>
           <t>김현우</t>
         </is>
@@ -5533,7 +5533,7 @@
           <t>OB-02, OB-01</t>
         </is>
       </c>
-      <c r="J11" s="47" t="inlineStr">
+      <c r="J11" s="44" t="inlineStr">
         <is>
           <t>김현우</t>
         </is>
@@ -5542,50 +5542,50 @@
     <row r="12" ht="66.75" customHeight="1" s="43">
       <c r="A12" s="44" t="inlineStr">
         <is>
-          <t>VZ-O-01</t>
+          <t>VZ-I-11</t>
         </is>
       </c>
       <c r="B12" s="45" t="inlineStr">
         <is>
-          <t>송신</t>
+          <t>수신</t>
         </is>
       </c>
       <c r="C12" s="46" t="inlineStr">
         <is>
-          <t>제어 명령 발행</t>
+          <t>구독 범위(관심 영역) 한정 — 자리 확보</t>
         </is>
       </c>
       <c r="D12" s="46" t="inlineStr">
         <is>
-          <t>사용자 조작을 추상 action+params 형태로 백엔드에 발행한다. 명령 식별자(전 파트 단일 상관 키)와 만료 시각(만료 후 실행 금지)을 포함하며, 디바이스 명령으로의 번역은 백엔드가 도메인 어휘집으로 수행한다. 브라우저가 브로커에 직접 쓰지 않고 백엔드를 경유한다.</t>
+          <t>구독 요청에 관심 영역(보고 있는 구역·계층·화면 범위)을 한정하는 범위 파라미터 자리를 계약에 둔다. 대상 수가 늘어나면 화면이 보고 있는 범위만 개별 구독하고 나머지는 집약 스트림으로 대체해야 하므로, 그 전환을 나중에 끼울 수 있도록 구독 요청 형식에 자리를 남긴다. 캡스톤 시연 규모에서는 전체 구독으로 충분하므로 이번 단계에서는 사용하지 않는다.</t>
         </is>
       </c>
       <c r="E12" s="46" t="inlineStr">
         <is>
-          <t>가시화→백엔드 WS 게이트웨이→디바이스</t>
+          <t>가시화→백엔드 WS 게이트웨이(구독 요청)</t>
         </is>
       </c>
       <c r="F12" s="44" t="inlineStr">
         <is>
-          <t>이벤트 기반(사용자 조작 시 즉시)</t>
+          <t>해당 없음(계약 자리만 확보, 현 단계 미사용)</t>
         </is>
       </c>
       <c r="G12" s="46" t="inlineStr">
         <is>
-          <t>사용자 조작은 본질적으로 비주기다. 명령을 모아 일괄 발행하는 방식도 있으나 긴급 제어가 지연되고 만료 시각(만료 후 실행 금지)의 의미가 사라진다. 발생 즉시 발행이 지연·안전 양쪽에서 유리해 선정.</t>
+          <t>지금은 구역 하나에 장치 수십 개라 전체를 구독해도 문제가 없다. 그러나 다지점·다구역으로 확장되면 전량 구독이 브라우저 수신 대역과 초기 스냅샷을 동시에 압박한다. 화면 반영을 병합해도 수신량 자체는 줄지 않으므로 구독 단계에서 범위를 좁히는 수밖에 없다. 지금 파라미터 자리를 남기는 비용은 필드 하나지만, 나중에 구독 프로토콜을 바꾸는 비용은 백엔드 게이트웨이와 전 화면에 전파되므로 자리만 미리 연다.</t>
         </is>
       </c>
       <c r="H12" s="46" t="inlineStr">
         <is>
-          <t>백엔드 서버, 백엔드 엣지노드, 하드웨어</t>
+          <t>백엔드 서버</t>
         </is>
       </c>
       <c r="I12" s="46" t="inlineStr">
         <is>
-          <t>HW-C-06, HW-R-05, HW-A-02</t>
-        </is>
-      </c>
-      <c r="J12" s="47" t="inlineStr">
+          <t>HW-C-01, HW-C-02</t>
+        </is>
+      </c>
+      <c r="J12" s="44" t="inlineStr">
         <is>
           <t>김현우</t>
         </is>
@@ -5594,7 +5594,7 @@
     <row r="13" ht="66.75" customHeight="1" s="43">
       <c r="A13" s="44" t="inlineStr">
         <is>
-          <t>VZ-O-02</t>
+          <t>VZ-O-01</t>
         </is>
       </c>
       <c r="B13" s="45" t="inlineStr">
@@ -5604,40 +5604,40 @@
       </c>
       <c r="C13" s="46" t="inlineStr">
         <is>
-          <t>명령 결과 표시</t>
+          <t>제어 명령 발행</t>
         </is>
       </c>
       <c r="D13" s="46" t="inlineStr">
         <is>
-          <t>명령의 진행을 '수신 확인(ACK) → 수행 중 → 물리 상태 변화 → 완료·실패' 네 단계로 받아 화면에 반영한다. 화면 표시는 진행중·확정·실패 3종이며, 물리 동작 중에는 진행 상태를 함께 표시한다. 되돌리기 어려운 명령은 ACK가 아니라 실제 수행 결과로 확정 표시한다.</t>
+          <t>사용자 조작을 추상 action+params 형태로 백엔드에 발행한다. 명령 식별자(전 파트 단일 상관 키)와 만료 시각(만료 후 실행 금지)을 포함하며, 디바이스 명령으로의 번역은 백엔드가 도메인 어휘집으로 수행한다. 브라우저가 브로커에 직접 쓰지 않고 백엔드를 경유한다.</t>
         </is>
       </c>
       <c r="E13" s="46" t="inlineStr">
         <is>
-          <t>백엔드→가시화(WS)</t>
+          <t>가시화→백엔드 WS 게이트웨이→디바이스</t>
         </is>
       </c>
       <c r="F13" s="44" t="inlineStr">
         <is>
-          <t>결과 단계 도달 시(이벤트 기반) / 물리 동작 중 진행 상태 200ms 주기 수신</t>
+          <t>이벤트 기반(사용자 조작 시 즉시)</t>
         </is>
       </c>
       <c r="G13" s="46" t="inlineStr">
         <is>
-          <t>낙관적 즉시 반영은 실패 시 화면과 현실이 어긋난다. 액추에이터가 동작 중 200ms 주기로 진행 상태를 보고하므로(HW-A-04) 그대로 받아 진행 표시에 쓰면 추가 비용 없이 '멈춘 것처럼 보이는 구간'을 없앨 수 있어 선정. 클라이언트가 상태를 직접 판정하는 방식은 액션별 규칙을 프론트가 떠안게 되어 배제.</t>
+          <t>사용자 조작은 본질적으로 비주기다. 명령을 모아 일괄 발행하는 방식도 있으나 긴급 제어가 지연되고 만료 시각(만료 후 실행 금지)의 의미가 사라진다. 발생 즉시 발행이 지연·안전 양쪽에서 유리해 선정.</t>
         </is>
       </c>
       <c r="H13" s="46" t="inlineStr">
         <is>
-          <t>백엔드 서버, 하드웨어, AI</t>
+          <t>백엔드 서버, 백엔드 엣지노드, 하드웨어</t>
         </is>
       </c>
       <c r="I13" s="46" t="inlineStr">
         <is>
-          <t>HW-C-06, HW-A-03, HW-A-04, RK-03</t>
-        </is>
-      </c>
-      <c r="J13" s="47" t="inlineStr">
+          <t>HW-C-06, HW-R-05, HW-A-02</t>
+        </is>
+      </c>
+      <c r="J13" s="44" t="inlineStr">
         <is>
           <t>김현우</t>
         </is>
@@ -5646,7 +5646,7 @@
     <row r="14" ht="66.75" customHeight="1" s="43">
       <c r="A14" s="44" t="inlineStr">
         <is>
-          <t>VZ-O-03</t>
+          <t>VZ-O-02</t>
         </is>
       </c>
       <c r="B14" s="45" t="inlineStr">
@@ -5656,40 +5656,40 @@
       </c>
       <c r="C14" s="46" t="inlineStr">
         <is>
-          <t>책임소재(감사) 필드 전달</t>
+          <t>명령 결과 표시</t>
         </is>
       </c>
       <c r="D14" s="46" t="inlineStr">
         <is>
-          <t>명령 요청에 입력 수단(클릭/음성/API)과 판단 주체(사람/LLM 제안 수락/자동), 음성 전사·LLM 메타데이터를 실어 보낸다. 감사 기록의 작성·저장은 백엔드가 수행하며 조작자는 토큰에서, 시각은 서버 시각으로 주입한다. 가시화는 감사를 관측 스택에 직접 발행하지 않는다.</t>
+          <t>명령의 진행을 '수신 확인(ACK) → 수행 중 → 물리 상태 변화 → 완료·실패' 네 단계로 받아 화면에 반영한다. 화면 표시는 진행중·확정·실패 3종이며, 물리 동작 중에는 진행 상태를 함께 표시한다. 되돌리기 어려운 명령은 ACK가 아니라 실제 수행 결과로 확정 표시한다.</t>
         </is>
       </c>
       <c r="E14" s="46" t="inlineStr">
         <is>
-          <t>가시화→백엔드(명령 요청에 동봉)</t>
+          <t>백엔드→가시화(WS)</t>
         </is>
       </c>
       <c r="F14" s="44" t="inlineStr">
         <is>
-          <t>명령 1건당 1회(명령에 동봉)</t>
+          <t>결과 단계 도달 시(이벤트 기반) / 물리 동작 중 진행 상태 200ms 주기 수신</t>
         </is>
       </c>
       <c r="G14" s="46" t="inlineStr">
         <is>
-          <t>감사를 별도 경로로 보내면 탭 종료·네트워크 단절 시 "실행은 됐는데 기록이 없음"이 발생한다. 브라우저가 직접 기록하면 조작자 정보가 클라이언트 자기신고가 되어 위조도 가능하고, 시각도 사용자 PC 시계에 의존한다. 장치는 NTP로 시각을 맞추는데(HW-S-08) 브라우저에는 그 보장이 없으므로 서버 시각 주입이 맞아 선정.</t>
+          <t>낙관적 즉시 반영은 실패 시 화면과 현실이 어긋난다. 액추에이터가 동작 중 200ms 주기로 진행 상태를 보고하므로(HW-A-04) 그대로 받아 진행 표시에 쓰면 추가 비용 없이 '멈춘 것처럼 보이는 구간'을 없앨 수 있어 선정. 클라이언트가 상태를 직접 판정하는 방식은 액션별 규칙을 프론트가 떠안게 되어 배제.</t>
         </is>
       </c>
       <c r="H14" s="46" t="inlineStr">
         <is>
-          <t>백엔드 서버, AI</t>
+          <t>백엔드 서버, 하드웨어, AI</t>
         </is>
       </c>
       <c r="I14" s="46" t="inlineStr">
         <is>
-          <t>PL-06, HW-S-08</t>
-        </is>
-      </c>
-      <c r="J14" s="47" t="inlineStr">
+          <t>HW-C-06, HW-A-03, HW-A-04, RK-03</t>
+        </is>
+      </c>
+      <c r="J14" s="44" t="inlineStr">
         <is>
           <t>김현우</t>
         </is>
@@ -5698,7 +5698,7 @@
     <row r="15" ht="66.75" customHeight="1" s="43">
       <c r="A15" s="44" t="inlineStr">
         <is>
-          <t>VZ-O-04</t>
+          <t>VZ-O-03</t>
         </is>
       </c>
       <c r="B15" s="45" t="inlineStr">
@@ -5708,27 +5708,27 @@
       </c>
       <c r="C15" s="46" t="inlineStr">
         <is>
-          <t>자체 관측 지표 발행</t>
+          <t>책임소재(감사) 필드 전달</t>
         </is>
       </c>
       <c r="D15" s="46" t="inlineStr">
         <is>
-          <t>가시화 자신의 성능 지표를 관측 스택에 직접 발행한다. 대시보드 반영 지연, 질의 지연·오류, 음성 인식 지연·실패율, 화면 구성 보조 LLM 응답 지연을 포함하며 단위는 지표 이름이 아니라 단위 필드에 둔다.</t>
+          <t>명령 요청에 입력 수단(클릭/음성/API)과 판단 주체(사람/LLM 제안 수락/자동), 음성 전사·LLM 메타데이터를 실어 보낸다. 감사 기록의 작성·저장은 백엔드가 수행하며 조작자는 토큰에서, 시각은 서버 시각으로 주입한다. 가시화는 감사를 관측 스택에 직접 발행하지 않는다.</t>
         </is>
       </c>
       <c r="E15" s="46" t="inlineStr">
         <is>
-          <t>가시화→관측 스택(직접)</t>
+          <t>가시화→백엔드(명령 요청에 동봉)</t>
         </is>
       </c>
       <c r="F15" s="44" t="inlineStr">
         <is>
-          <t>60초 1회 집계 발행</t>
+          <t>명령 1건당 1회(명령에 동봉)</t>
         </is>
       </c>
       <c r="G15" s="46" t="inlineStr">
         <is>
-          <t>자기 컴포넌트 성능 지표는 추세 확인용이라 고주기가 불필요하고, 관측 수집기의 기본 내보내기 주기와 맞추면 설정이 단순해진다. 1초 발행은 시계열 점 수와 저장 비용만 늘고 판단이 달라지지 않아 배제.</t>
+          <t>감사를 별도 경로로 보내면 탭 종료·네트워크 단절 시 "실행은 됐는데 기록이 없음"이 발생한다. 브라우저가 직접 기록하면 조작자 정보가 클라이언트 자기신고가 되어 위조도 가능하고, 시각도 사용자 PC 시계에 의존한다. 장치는 NTP로 시각을 맞추는데(HW-S-08) 브라우저에는 그 보장이 없으므로 서버 시각 주입이 맞아 선정.</t>
         </is>
       </c>
       <c r="H15" s="46" t="inlineStr">
@@ -5738,10 +5738,10 @@
       </c>
       <c r="I15" s="46" t="inlineStr">
         <is>
-          <t>HW-C-05, OB-01</t>
-        </is>
-      </c>
-      <c r="J15" s="47" t="inlineStr">
+          <t>PL-06, HW-S-08</t>
+        </is>
+      </c>
+      <c r="J15" s="44" t="inlineStr">
         <is>
           <t>김현우</t>
         </is>
@@ -5750,7 +5750,7 @@
     <row r="16" ht="66.75" customHeight="1" s="43">
       <c r="A16" s="44" t="inlineStr">
         <is>
-          <t>VZ-O-05</t>
+          <t>VZ-O-04</t>
         </is>
       </c>
       <c r="B16" s="45" t="inlineStr">
@@ -5760,40 +5760,40 @@
       </c>
       <c r="C16" s="46" t="inlineStr">
         <is>
-          <t>제어 잠금 상태 표시</t>
+          <t>자체 관측 지표 발행</t>
         </is>
       </c>
       <c r="D16" s="46" t="inlineStr">
         <is>
-          <t>통신 두절·장치 오류로 원격 제어가 제한된 대상은 제어 UI를 잠금 상태로 표시하고 발행을 차단한다. 잠금 사유와 안전 상태 유지 여부를 함께 보여주며, 통신 복구 후 실제 상태 재확인이 끝나기 전까지는 잠금을 유지한다.</t>
+          <t>가시화 자신의 성능 지표를 관측 스택에 직접 발행한다. 대시보드 반영 지연, 질의 지연·오류, 음성 인식 지연·실패율, 화면 구성 보조 LLM 응답 지연을 포함하며 단위는 지표 이름이 아니라 단위 필드에 둔다.</t>
         </is>
       </c>
       <c r="E16" s="46" t="inlineStr">
         <is>
-          <t>백엔드→가시화(WS)</t>
+          <t>가시화→관측 스택(직접)</t>
         </is>
       </c>
       <c r="F16" s="44" t="inlineStr">
         <is>
-          <t>잠금·해제 전환 시 즉시(이벤트 기반)</t>
+          <t>60초 1회 집계 발행</t>
         </is>
       </c>
       <c r="G16" s="46" t="inlineStr">
         <is>
-          <t>잠금은 통신 두절 판정(제어노드 하트비트 3회 연속 미수신, 약 3초)과 복구 감지 시점에만 바뀌므로 주기 조회가 필요 없다. 반대로 이 표시가 늦으면 관제사가 눌러도 실행되지 않는 버튼을 계속 누르게 되어 즉시 반영이 필요해 이벤트 기반으로 선정.</t>
+          <t>자기 컴포넌트 성능 지표는 추세 확인용이라 고주기가 불필요하고, 관측 수집기의 기본 내보내기 주기와 맞추면 설정이 단순해진다. 1초 발행은 시계열 점 수와 저장 비용만 늘고 판단이 달라지지 않아 배제.</t>
         </is>
       </c>
       <c r="H16" s="46" t="inlineStr">
         <is>
-          <t>하드웨어, 백엔드 엣지노드</t>
+          <t>백엔드 서버, AI</t>
         </is>
       </c>
       <c r="I16" s="46" t="inlineStr">
         <is>
-          <t>HW-A-05, HW-A-01, HW-S-07</t>
-        </is>
-      </c>
-      <c r="J16" s="47" t="inlineStr">
+          <t>HW-C-05, OB-01</t>
+        </is>
+      </c>
+      <c r="J16" s="44" t="inlineStr">
         <is>
           <t>김현우</t>
         </is>
@@ -5802,50 +5802,50 @@
     <row r="17" ht="66.75" customHeight="1" s="43">
       <c r="A17" s="44" t="inlineStr">
         <is>
-          <t>VZ-U-01</t>
+          <t>VZ-O-05</t>
         </is>
       </c>
       <c r="B17" s="45" t="inlineStr">
         <is>
-          <t>화면</t>
+          <t>송신</t>
         </is>
       </c>
       <c r="C17" s="46" t="inlineStr">
         <is>
-          <t>상태 4종 구분 표시</t>
+          <t>제어 잠금 상태 표시</t>
         </is>
       </c>
       <c r="D17" s="46" t="inlineStr">
         <is>
-          <t>정상 / 장애 / 의도적 미배포 / 판단 불가(값이 오래됨)를 상태 3층의 조합으로 구분해 표시한다. 단일 상태 값으로 뭉쳐 저장하지 않고 3층 원본을 보관해 표시값을 파생시킨다. 액추에이터의 대기·동작 중·완료·오류·확인 불가처럼 대상 종류별 고유 상태는 표준 3층과 별개인 도메인 어휘로 다룬다.</t>
+          <t>통신 두절·장치 오류로 원격 제어가 제한된 대상은 제어 UI를 잠금 상태로 표시하고 발행을 차단한다. 잠금 사유와 안전 상태 유지 여부를 함께 보여주며, 통신 복구 후 실제 상태 재확인이 끝나기 전까지는 잠금을 유지한다.</t>
         </is>
       </c>
       <c r="E17" s="46" t="inlineStr">
         <is>
-          <t>(내부 처리)</t>
+          <t>백엔드→가시화(WS)</t>
         </is>
       </c>
       <c r="F17" s="44" t="inlineStr">
         <is>
-          <t>상태 수신 시 갱신(100ms 병합) / 구역별 장치 현황판은 5초 / 오프라인 감지는 즉시</t>
+          <t>잠금·해제 전환 시 즉시(이벤트 기반)</t>
         </is>
       </c>
       <c r="G17" s="46" t="inlineStr">
         <is>
-          <t>상태를 하나로 합치면 "연결은 됐는데 기기가 고장"과 "값이 오래됨"을 표현할 수 없어 원천이 섞이고 책임소재가 흐려진다. 현황판은 엣지노드의 구역 단위 상태 요약이 5초 1회 갱신(HW-C-04)이고 센서노드 하트비트도 5초(HW-S-05)라 그보다 자주 그려도 값이 같아 5초로 맞췄고, 오프라인 감지(HW-S-07)는 즉시 도달하므로 끊김만은 지연 없이 반영한다.</t>
+          <t>잠금은 통신 두절 판정(제어노드 하트비트 3회 연속 미수신, 약 3초)과 복구 감지 시점에만 바뀌므로 주기 조회가 필요 없다. 반대로 이 표시가 늦으면 관제사가 눌러도 실행되지 않는 버튼을 계속 누르게 되어 즉시 반영이 필요해 이벤트 기반으로 선정.</t>
         </is>
       </c>
       <c r="H17" s="46" t="inlineStr">
         <is>
-          <t>백엔드 서버, 백엔드 엣지노드, AI, 하드웨어</t>
+          <t>하드웨어, 백엔드 엣지노드</t>
         </is>
       </c>
       <c r="I17" s="46" t="inlineStr">
         <is>
-          <t>HW-R-02, HW-S-05, HW-S-07, HW-C-04, HW-A-01</t>
-        </is>
-      </c>
-      <c r="J17" s="47" t="inlineStr">
+          <t>HW-A-05, HW-A-01, HW-S-07</t>
+        </is>
+      </c>
+      <c r="J17" s="44" t="inlineStr">
         <is>
           <t>김현우</t>
         </is>
@@ -5854,7 +5854,7 @@
     <row r="18" ht="66.75" customHeight="1" s="43">
       <c r="A18" s="44" t="inlineStr">
         <is>
-          <t>VZ-U-02</t>
+          <t>VZ-U-01</t>
         </is>
       </c>
       <c r="B18" s="45" t="inlineStr">
@@ -5864,40 +5864,40 @@
       </c>
       <c r="C18" s="46" t="inlineStr">
         <is>
-          <t>디지털 트윈 위치 렌더링</t>
+          <t>상태 4종 구분 표시</t>
         </is>
       </c>
       <c r="D18" s="46" t="inlineStr">
         <is>
-          <t>전역 좌표로 변환된 위치를 트윈 화면에 배치한다. 로컬→글로벌 변환과 축 변환은 백엔드가 수행하므로 가시화는 변환 로직을 구현하지 않으며, 좌표 기준 프레임과 산출 출처(로봇 자기추정/앵커 보정/AI 인지)를 위치 신뢰도 표시에 사용한다. ※ 좌표 기준 프레임·출처 필드의 하드웨어 측 정의가 현재 시트에 명시되지 않아 확정이 필요하다.</t>
+          <t>정상 / 장애 / 의도적 미배포 / 판단 불가(값이 오래됨)를 상태 3층의 조합으로 구분해 표시한다. 단일 상태 값으로 뭉쳐 저장하지 않고 3층 원본을 보관해 표시값을 파생시킨다. 액추에이터의 대기·동작 중·완료·오류·확인 불가처럼 대상 종류별 고유 상태는 표준 3층과 별개인 도메인 어휘로 다룬다.</t>
         </is>
       </c>
       <c r="E18" s="46" t="inlineStr">
         <is>
-          <t>백엔드→가시화(WS)</t>
+          <t>(내부 처리)</t>
         </is>
       </c>
       <c r="F18" s="44" t="inlineStr">
         <is>
-          <t>수신값(임무 중 50ms) 사이를 보간해 화면은 60fps로 렌더</t>
+          <t>상태 수신 시 갱신(100ms 병합) / 구역별 장치 현황판은 5초 / 오프라인 감지는 즉시</t>
         </is>
       </c>
       <c r="G18" s="46" t="inlineStr">
         <is>
-          <t>50ms 수신값을 그대로 찍으면 이동체가 20Hz로 튀어 보인다. 서버에 60Hz 전송을 요구하는 방식도 있으나 무선 구간이 감당하지 못한다. 클라이언트 보간은 추가 통신 없이 부드러움을 얻으므로 비용 대비 효과가 가장 커 선정.</t>
+          <t>상태를 하나로 합치면 "연결은 됐는데 기기가 고장"과 "값이 오래됨"을 표현할 수 없어 원천이 섞이고 책임소재가 흐려진다. 현황판은 엣지노드의 구역 단위 상태 요약이 5초 1회 갱신(HW-C-04)이고 센서노드 하트비트도 5초(HW-S-05)라 그보다 자주 그려도 값이 같아 5초로 맞췄고, 오프라인 감지(HW-S-07)는 즉시 도달하므로 끊김만은 지연 없이 반영한다.</t>
         </is>
       </c>
       <c r="H18" s="46" t="inlineStr">
         <is>
-          <t>백엔드 서버, AI, 하드웨어</t>
+          <t>백엔드 서버, 백엔드 엣지노드, AI, 하드웨어</t>
         </is>
       </c>
       <c r="I18" s="46" t="inlineStr">
         <is>
-          <t>HW-R-03, GN-02</t>
-        </is>
-      </c>
-      <c r="J18" s="47" t="inlineStr">
+          <t>HW-R-02, HW-S-05, HW-S-07, HW-C-04, HW-A-01</t>
+        </is>
+      </c>
+      <c r="J18" s="44" t="inlineStr">
         <is>
           <t>김현우</t>
         </is>
@@ -5906,7 +5906,7 @@
     <row r="19" ht="66.75" customHeight="1" s="43">
       <c r="A19" s="44" t="inlineStr">
         <is>
-          <t>VZ-U-03</t>
+          <t>VZ-U-02</t>
         </is>
       </c>
       <c r="B19" s="45" t="inlineStr">
@@ -5916,40 +5916,40 @@
       </c>
       <c r="C19" s="46" t="inlineStr">
         <is>
-          <t>추상화 계층 뷰(결심자/운영자/개발자)</t>
+          <t>디지털 트윈 위치 렌더링</t>
         </is>
       </c>
       <c r="D19" s="46" t="inlineStr">
         <is>
-          <t>같은 대상을 결심자(집약 판단)·운영자(구성 요소)·개발자(원본) 수준으로 전환해 본다. 상위 지표에서 그 값을 만든 하위 항목으로 드릴다운하며, 집약값을 원본으로 오인해 재집약하지 않도록 각 출력에 표기된 추상화 수준을 따른다.</t>
+          <t>전역 좌표로 변환된 위치를 트윈 화면에 배치한다. 로컬→글로벌 변환과 축 변환은 백엔드가 수행하므로 가시화는 변환 로직을 구현하지 않으며, 좌표 기준 프레임과 산출 출처(로봇 자기추정/앵커 보정/AI 인지)를 위치 신뢰도 표시에 사용한다. ※ 좌표 기준 프레임·출처 필드의 하드웨어 측 정의가 현재 시트에 명시되지 않아 확정이 필요하다.</t>
         </is>
       </c>
       <c r="E19" s="46" t="inlineStr">
         <is>
-          <t>(내부 처리)</t>
+          <t>백엔드→가시화(WS)</t>
         </is>
       </c>
       <c r="F19" s="44" t="inlineStr">
         <is>
-          <t>사용자 전환 시(이벤트 기반)</t>
+          <t>수신값(임무 중 50ms) 사이를 보간해 화면은 60fps로 렌더</t>
         </is>
       </c>
       <c r="G19" s="46" t="inlineStr">
         <is>
-          <t>뷰 전환은 사용자 조작에 종속되어 주기 개념이 없다. 다만 전환 후에도 하위 데이터 구독을 유지해야 드릴다운이 즉시 응답하므로, 구독을 해제하지 않고 표시 수준만 바꾸는 방식으로 선정.</t>
+          <t>50ms 수신값을 그대로 찍으면 이동체가 20Hz로 튀어 보인다. 서버에 60Hz 전송을 요구하는 방식도 있으나 무선 구간이 감당하지 못한다. 클라이언트 보간은 추가 통신 없이 부드러움을 얻으므로 비용 대비 효과가 가장 커 선정.</t>
         </is>
       </c>
       <c r="H19" s="46" t="inlineStr">
         <is>
-          <t>AI, 백엔드 서버</t>
+          <t>백엔드 서버, AI, 하드웨어</t>
         </is>
       </c>
       <c r="I19" s="46" t="inlineStr">
         <is>
-          <t>PR-04, RK-02</t>
-        </is>
-      </c>
-      <c r="J19" s="47" t="inlineStr">
+          <t>HW-R-03, GN-02</t>
+        </is>
+      </c>
+      <c r="J19" s="44" t="inlineStr">
         <is>
           <t>김현우</t>
         </is>
@@ -5958,7 +5958,7 @@
     <row r="20" ht="66.75" customHeight="1" s="43">
       <c r="A20" s="44" t="inlineStr">
         <is>
-          <t>VZ-U-04</t>
+          <t>VZ-U-03</t>
         </is>
       </c>
       <c r="B20" s="45" t="inlineStr">
@@ -5968,40 +5968,40 @@
       </c>
       <c r="C20" s="46" t="inlineStr">
         <is>
-          <t>노드 편집기 구성 반영</t>
+          <t>추상화 계층 뷰(결심자/운영자/개발자)</t>
         </is>
       </c>
       <c r="D20" s="46" t="inlineStr">
         <is>
-          <t>파이프라인·화면 구성을 노드 그래프로 편집하고, 시험 실행으로 검증한 뒤 명시적 '반영' 조작으로만 운영 상태에 적용한다. 반영 행위는 제어 명령급 감사 대상으로 보되, 실제 이벤트 발행은 노드 편집기 구현 시점으로 미룬다(자리만 확보).</t>
+          <t>같은 대상을 결심자(집약 판단)·운영자(구성 요소)·개발자(원본) 수준으로 전환해 본다. 상위 지표에서 그 값을 만든 하위 항목으로 드릴다운하며, 집약값을 원본으로 오인해 재집약하지 않도록 각 출력에 표기된 추상화 수준을 따른다.</t>
         </is>
       </c>
       <c r="E20" s="46" t="inlineStr">
         <is>
-          <t>(내부 처리) / 반영 이벤트: 가시화→백엔드</t>
+          <t>(내부 처리)</t>
         </is>
       </c>
       <c r="F20" s="44" t="inlineStr">
         <is>
-          <t>사용자 '반영' 조작 시(이벤트 기반)</t>
+          <t>사용자 전환 시(이벤트 기반)</t>
         </is>
       </c>
       <c r="G20" s="46" t="inlineStr">
         <is>
-          <t>편집 중 자동 반영은 미완성 그래프가 운영 화면으로 나가는 사고를 만든다. 명시적 반영만 허용하면 되돌리기와 감사 양쪽에 유리하고, 시험 실행으로 사전 검증까지 가능해 선정.</t>
+          <t>뷰 전환은 사용자 조작에 종속되어 주기 개념이 없다. 다만 전환 후에도 하위 데이터 구독을 유지해야 드릴다운이 즉시 응답하므로, 구독을 해제하지 않고 표시 수준만 바꾸는 방식으로 선정.</t>
         </is>
       </c>
       <c r="H20" s="46" t="inlineStr">
         <is>
-          <t>백엔드 서버</t>
+          <t>AI, 백엔드 서버</t>
         </is>
       </c>
       <c r="I20" s="46" t="inlineStr">
         <is>
-          <t>HW-C-02</t>
-        </is>
-      </c>
-      <c r="J20" s="47" t="inlineStr">
+          <t>PR-04, RK-02</t>
+        </is>
+      </c>
+      <c r="J20" s="44" t="inlineStr">
         <is>
           <t>김현우</t>
         </is>
@@ -6010,7 +6010,7 @@
     <row r="21" ht="66.75" customHeight="1" s="43">
       <c r="A21" s="44" t="inlineStr">
         <is>
-          <t>VZ-U-05</t>
+          <t>VZ-U-04</t>
         </is>
       </c>
       <c r="B21" s="45" t="inlineStr">
@@ -6020,40 +6020,40 @@
       </c>
       <c r="C21" s="46" t="inlineStr">
         <is>
-          <t>서브태스크 진행 상태 표시</t>
+          <t>노드 편집기 구성 반영</t>
         </is>
       </c>
       <c r="D21" s="46" t="inlineStr">
         <is>
-          <t>승인된 계획이 구간 단위로 어디까지 수행됐고 어느 단계에서 실패했는지를 노드 형태로 표시해 추적·디버깅할 수 있게 한다. 여러 구역에 걸친 계획은 구역별 구간과 순서를 함께 보여준다.</t>
+          <t>파이프라인·화면 구성을 노드 그래프로 편집하고, 시험 실행으로 검증한 뒤 명시적 '반영' 조작으로만 운영 상태에 적용한다. 반영 행위는 제어 명령급 감사 대상으로 보되, 실제 이벤트 발행은 노드 편집기 구현 시점으로 미룬다(자리만 확보).</t>
         </is>
       </c>
       <c r="E21" s="46" t="inlineStr">
         <is>
-          <t>백엔드→가시화(WS)</t>
+          <t>(내부 처리) / 반영 이벤트: 가시화→백엔드</t>
         </is>
       </c>
       <c r="F21" s="44" t="inlineStr">
         <is>
-          <t>구간 상태 변화 시(이벤트 기반)</t>
+          <t>사용자 '반영' 조작 시(이벤트 기반)</t>
         </is>
       </c>
       <c r="G21" s="46" t="inlineStr">
         <is>
-          <t>구간 상태는 하달·시작·완료·실패 시점에만 바뀌므로 주기 폴링은 낭비다. 수행 시작·완료·실패 보고가 로봇 상태 데이터(HW-R-03)에 실려 오므로 그 변화 시점에 갱신하면 충분해 이벤트 기반으로 선정.</t>
+          <t>편집 중 자동 반영은 미완성 그래프가 운영 화면으로 나가는 사고를 만든다. 명시적 반영만 허용하면 되돌리기와 감사 양쪽에 유리하고, 시험 실행으로 사전 검증까지 가능해 선정.</t>
         </is>
       </c>
       <c r="H21" s="46" t="inlineStr">
         <is>
-          <t>AI, 백엔드 서버, 하드웨어</t>
+          <t>백엔드 서버</t>
         </is>
       </c>
       <c r="I21" s="46" t="inlineStr">
         <is>
-          <t>HW-R-05, HW-R-03, PL-02, PL-03</t>
-        </is>
-      </c>
-      <c r="J21" s="47" t="inlineStr">
+          <t>HW-C-02</t>
+        </is>
+      </c>
+      <c r="J21" s="44" t="inlineStr">
         <is>
           <t>김현우</t>
         </is>
@@ -6062,7 +6062,7 @@
     <row r="22" ht="66.75" customHeight="1" s="43">
       <c r="A22" s="44" t="inlineStr">
         <is>
-          <t>VZ-U-06</t>
+          <t>VZ-U-05</t>
         </is>
       </c>
       <c r="B22" s="45" t="inlineStr">
@@ -6072,40 +6072,40 @@
       </c>
       <c r="C22" s="46" t="inlineStr">
         <is>
-          <t>미확인 탐지 그룹 확인</t>
+          <t>서브태스크 진행 상태 표시</t>
         </is>
       </c>
       <c r="D22" s="46" t="inlineStr">
         <is>
-          <t>AI가 기존 분류에 속하지 않는 탐지를 유사도로 묶어 전달하면, 이를 화면에 표시하고 사용자가 명칭을 확인·입력해 회신한다. 확인된 명칭은 학습 후보 데이터로 반영되며, 사람 확인 없이는 학습에 확정되지 않는다.</t>
+          <t>승인된 계획이 구간 단위로 어디까지 수행됐고 어느 단계에서 실패했는지를 노드 형태로 표시해 추적·디버깅할 수 있게 한다. 여러 구역에 걸친 계획은 구역별 구간과 순서를 함께 보여준다.</t>
         </is>
       </c>
       <c r="E22" s="46" t="inlineStr">
         <is>
-          <t>AI→가시화 / 가시화→AI(확인된 명칭)</t>
+          <t>백엔드→가시화(WS)</t>
         </is>
       </c>
       <c r="F22" s="44" t="inlineStr">
         <is>
-          <t>미확인 그룹 도착 시(이벤트 기반), 사용자 확인 시 회신</t>
+          <t>구간 상태 변화 시(이벤트 기반)</t>
         </is>
       </c>
       <c r="G22" s="46" t="inlineStr">
         <is>
-          <t>탐지 건마다 확인을 요청하면 사용자 부담이 커, AI가 유사 후보를 묶어 보내는 방식과 짝을 이룬다. 가시화도 같은 단위로 묶어 표시해야 확인 절차가 한 번에 끝나므로 그룹 단위 이벤트로 선정.</t>
+          <t>구간 상태는 하달·시작·완료·실패 시점에만 바뀌므로 주기 폴링은 낭비다. 수행 시작·완료·실패 보고가 로봇 상태 데이터(HW-R-03)에 실려 오므로 그 변화 시점에 갱신하면 충분해 이벤트 기반으로 선정.</t>
         </is>
       </c>
       <c r="H22" s="46" t="inlineStr">
         <is>
-          <t>AI, 백엔드 서버</t>
+          <t>AI, 백엔드 서버, 하드웨어</t>
         </is>
       </c>
       <c r="I22" s="46" t="inlineStr">
         <is>
-          <t>PR-05, CL-02, CL-01</t>
-        </is>
-      </c>
-      <c r="J22" s="47" t="inlineStr">
+          <t>HW-R-05, HW-R-03, PL-02, PL-03</t>
+        </is>
+      </c>
+      <c r="J22" s="44" t="inlineStr">
         <is>
           <t>김현우</t>
         </is>
@@ -6114,7 +6114,7 @@
     <row r="23" ht="66.75" customHeight="1" s="43">
       <c r="A23" s="44" t="inlineStr">
         <is>
-          <t>VZ-U-07</t>
+          <t>VZ-U-06</t>
         </is>
       </c>
       <c r="B23" s="45" t="inlineStr">
@@ -6124,27 +6124,27 @@
       </c>
       <c r="C23" s="46" t="inlineStr">
         <is>
-          <t>계획 승인 및 근거 표시</t>
+          <t>미확인 탐지 그룹 확인</t>
         </is>
       </c>
       <c r="D23" s="46" t="inlineStr">
         <is>
-          <t>검증을 통과한 실행 계획과 그 근거(전역 임무 → 구역 분할 → 구간별 계획 → 검증 결과, 계획 생성기 버전, 입력 맥락 버전)를 구조화된 형태로 받아 화면에 펼쳐 보이고, 사용자가 승인하거나 거부할 수 있게 한다. 승인 전에는 계획이 실행되지 않는다.</t>
+          <t>AI가 기존 분류에 속하지 않는 탐지를 유사도로 묶어 전달하면, 이를 화면에 표시하고 사용자가 명칭을 확인·입력해 회신한다. 확인된 명칭은 학습 후보 데이터로 반영되며, 사람 확인 없이는 학습에 확정되지 않는다.</t>
         </is>
       </c>
       <c r="E23" s="46" t="inlineStr">
         <is>
-          <t>백엔드/AI→가시화→(승인)→엣지·로봇</t>
+          <t>AI→가시화 / 가시화→AI(확인된 명칭)</t>
         </is>
       </c>
       <c r="F23" s="44" t="inlineStr">
         <is>
-          <t>계획 검증 완료 시(이벤트 기반), 승인은 사용자 조작 시</t>
+          <t>미확인 그룹 도착 시(이벤트 기반), 사용자 확인 시 회신</t>
         </is>
       </c>
       <c r="G23" s="46" t="inlineStr">
         <is>
-          <t>계획 생성·검증은 임무 발생 시에만 일어나므로 주기가 없다. 승인 절차를 화면에 두는 이유는 생성 결과가 검증을 통과했더라도 사람이 실행 여부를 결정해야 하기 때문이며, 승인 없이 자동 실행하면 책임소재가 성립하지 않아 필수 절차로 선정.</t>
+          <t>탐지 건마다 확인을 요청하면 사용자 부담이 커, AI가 유사 후보를 묶어 보내는 방식과 짝을 이룬다. 가시화도 같은 단위로 묶어 표시해야 확인 절차가 한 번에 끝나므로 그룹 단위 이벤트로 선정.</t>
         </is>
       </c>
       <c r="H23" s="46" t="inlineStr">
@@ -6154,10 +6154,10 @@
       </c>
       <c r="I23" s="46" t="inlineStr">
         <is>
-          <t>PL-04, PL-05, PL-07</t>
-        </is>
-      </c>
-      <c r="J23" s="47" t="inlineStr">
+          <t>PR-05, CL-02, CL-01</t>
+        </is>
+      </c>
+      <c r="J23" s="44" t="inlineStr">
         <is>
           <t>김현우</t>
         </is>
@@ -6166,37 +6166,37 @@
     <row r="24" ht="66.75" customHeight="1" s="43">
       <c r="A24" s="44" t="inlineStr">
         <is>
-          <t>VZ-L-01</t>
+          <t>VZ-U-07</t>
         </is>
       </c>
       <c r="B24" s="45" t="inlineStr">
         <is>
-          <t>LLM·음성</t>
+          <t>화면</t>
         </is>
       </c>
       <c r="C24" s="46" t="inlineStr">
         <is>
-          <t>음성 입력(STT) 및 텍스트 전달</t>
+          <t>계획 승인 및 근거 표시</t>
         </is>
       </c>
       <c r="D24" s="46" t="inlineStr">
         <is>
-          <t>발화를 텍스트로 변환해 기존 클릭과 동일한 액션 트리거로 처리하고, 제어·임무 관련 발화는 텍스트 형태로 AI에 전달한다. 인식된 문장을 화면에 표시해 1차 확인을 받으며, 엔진은 인터페이스 뒤에 은닉하고 로컬 처리를 기본으로 한다. 대상 호칭(예: '503 구역 로봇')은 레지스트리의 표시 이름·별칭으로 해석한다.</t>
+          <t>검증을 통과한 실행 계획과 그 근거(전역 임무 → 구역 분할 → 구간별 계획 → 검증 결과, 계획 생성기 버전, 입력 맥락 버전)를 구조화된 형태로 받아 화면에 펼쳐 보이고, 사용자가 승인하거나 거부할 수 있게 한다. 승인 전에는 계획이 실행되지 않는다.</t>
         </is>
       </c>
       <c r="E24" s="46" t="inlineStr">
         <is>
-          <t>사용자 발화→가시화(STT)→엣지·서버(AI)</t>
+          <t>백엔드/AI→가시화→(승인)→엣지·로봇</t>
         </is>
       </c>
       <c r="F24" s="44" t="inlineStr">
         <is>
-          <t>발화 종료 감지 시 1회(이벤트 기반)</t>
+          <t>계획 검증 완료 시(이벤트 기반), 승인은 사용자 조작 시</t>
         </is>
       </c>
       <c r="G24" s="46" t="inlineStr">
         <is>
-          <t>상시 스트리밍 인식은 관제실 잡음까지 계속 처리해 오인식과 연산 낭비를 동시에 키운다. 발화 구간만 처리하면 정확도와 비용이 모두 유리해 선정. 관제실 음향 조건(소음·다중 화자)은 실측 후 확정.</t>
+          <t>계획 생성·검증은 임무 발생 시에만 일어나므로 주기가 없다. 승인 절차를 화면에 두는 이유는 생성 결과가 검증을 통과했더라도 사람이 실행 여부를 결정해야 하기 때문이며, 승인 없이 자동 실행하면 책임소재가 성립하지 않아 필수 절차로 선정.</t>
         </is>
       </c>
       <c r="H24" s="46" t="inlineStr">
@@ -6206,10 +6206,10 @@
       </c>
       <c r="I24" s="46" t="inlineStr">
         <is>
-          <t>PL-06</t>
-        </is>
-      </c>
-      <c r="J24" s="47" t="inlineStr">
+          <t>PL-04, PL-05, PL-07</t>
+        </is>
+      </c>
+      <c r="J24" s="44" t="inlineStr">
         <is>
           <t>김현우</t>
         </is>
@@ -6218,7 +6218,7 @@
     <row r="25">
       <c r="A25" s="44" t="inlineStr">
         <is>
-          <t>VZ-L-02</t>
+          <t>VZ-L-01</t>
         </is>
       </c>
       <c r="B25" s="45" t="inlineStr">
@@ -6228,27 +6228,27 @@
       </c>
       <c r="C25" s="46" t="inlineStr">
         <is>
-          <t>해석 결과 표시 및 수락</t>
+          <t>음성 입력(STT) 및 텍스트 전달</t>
         </is>
       </c>
       <c r="D25" s="46" t="inlineStr">
         <is>
-          <t>AI가 해석한 임무와 그로부터 생성·검증된 계획을 제안 형태로 화면에 표시하고, 사용자가 검토·수정한 뒤 명시적으로 수락해야 발행된다. 명령 의도 해석과 계획 생성은 AI 담당이며, 가시화는 전달·표시·수락 절차와 결과 추적을 맡는다.</t>
+          <t>발화를 텍스트로 변환해 기존 클릭과 동일한 액션 트리거로 처리하고, 제어·임무 관련 발화는 텍스트 형태로 AI에 전달한다. 인식된 문장을 화면에 표시해 1차 확인을 받으며, 엔진은 인터페이스 뒤에 은닉하고 로컬 처리를 기본으로 한다. 대상 호칭(예: '503 구역 로봇')은 레지스트리의 표시 이름·별칭으로 해석한다.</t>
         </is>
       </c>
       <c r="E25" s="46" t="inlineStr">
         <is>
-          <t>AI→가시화(해석·계획 결과) / 가시화→백엔드(수락된 명령)</t>
+          <t>사용자 발화→가시화(STT)→엣지·서버(AI)</t>
         </is>
       </c>
       <c r="F25" s="44" t="inlineStr">
         <is>
-          <t>해석·계획 결과 도착 시(이벤트 기반)</t>
+          <t>발화 종료 감지 시 1회(이벤트 기반)</t>
         </is>
       </c>
       <c r="G25" s="46" t="inlineStr">
         <is>
-          <t>해석기를 가시화와 AI가 각각 두면 같은 발화가 두 해석기를 거쳐 결과가 갈리고 오류 원인을 추적할 수 없다. 해석은 AI 한 곳으로 모으고 가시화는 표시와 수락만 맡는 편이 결과 일관성과 디버깅에 유리해 선정. 수락 절차는 사용자 조작에 종속되어 주기가 없다.</t>
+          <t>상시 스트리밍 인식은 관제실 잡음까지 계속 처리해 오인식과 연산 낭비를 동시에 키운다. 발화 구간만 처리하면 정확도와 비용이 모두 유리해 선정. 관제실 음향 조건(소음·다중 화자)은 실측 후 확정.</t>
         </is>
       </c>
       <c r="H25" s="46" t="inlineStr">
@@ -6258,10 +6258,10 @@
       </c>
       <c r="I25" s="46" t="inlineStr">
         <is>
-          <t>PL-06, PL-04, PL-05</t>
-        </is>
-      </c>
-      <c r="J25" s="47" t="inlineStr">
+          <t>PL-06</t>
+        </is>
+      </c>
+      <c r="J25" s="44" t="inlineStr">
         <is>
           <t>김현우</t>
         </is>
@@ -6270,7 +6270,7 @@
     <row r="26">
       <c r="A26" s="44" t="inlineStr">
         <is>
-          <t>VZ-L-03</t>
+          <t>VZ-L-02</t>
         </is>
       </c>
       <c r="B26" s="45" t="inlineStr">
@@ -6280,40 +6280,40 @@
       </c>
       <c r="C26" s="46" t="inlineStr">
         <is>
-          <t>실행 전 2단 확인 및 신뢰도 임계</t>
+          <t>해석 결과 표시 및 수락</t>
         </is>
       </c>
       <c r="D26" s="46" t="inlineStr">
         <is>
-          <t>① 인식된 문장이 맞는지, ② 그 문장을 이 임무·경로로 해석한 것이 맞는지 두 단계를 거쳐야 제어 명령이 발행된다. 인식 신뢰도가 임계 미만이면 AI에 전달하지 않고 재확인을 요구한다. 되돌릴 수 있는 조회·뷰 전환은 1차 확인만으로 진행한다.</t>
+          <t>AI가 해석한 임무와 그로부터 생성·검증된 계획을 제안 형태로 화면에 표시하고, 사용자가 검토·수정한 뒤 명시적으로 수락해야 발행된다. 명령 의도 해석과 계획 생성은 AI 담당이며, 가시화는 전달·표시·수락 절차와 결과 추적을 맡는다.</t>
         </is>
       </c>
       <c r="E26" s="46" t="inlineStr">
         <is>
-          <t>(내부 처리)</t>
+          <t>AI→가시화(해석·계획 결과) / 가시화→백엔드(수락된 명령)</t>
         </is>
       </c>
       <c r="F26" s="44" t="inlineStr">
         <is>
-          <t>제어 명령 1건당 매회(생략 불가)</t>
+          <t>해석·계획 결과 도착 시(이벤트 기반)</t>
         </is>
       </c>
       <c r="G26" s="46" t="inlineStr">
         <is>
-          <t>공공 서비스에서 오인식으로 장비가 움직이면 되돌릴 수 없다. 신뢰도가 높을 때 확인을 건너뛰는 방식도 있으나 사고는 임계 근처에서 발생하므로, 제어 액션은 예외 없이 2단 확인을 거치도록 선정. 임계값은 실측 후 확정.</t>
+          <t>해석기를 가시화와 AI가 각각 두면 같은 발화가 두 해석기를 거쳐 결과가 갈리고 오류 원인을 추적할 수 없다. 해석은 AI 한 곳으로 모으고 가시화는 표시와 수락만 맡는 편이 결과 일관성과 디버깅에 유리해 선정. 수락 절차는 사용자 조작에 종속되어 주기가 없다.</t>
         </is>
       </c>
       <c r="H26" s="46" t="inlineStr">
         <is>
-          <t>AI, 백엔드 서버, 하드웨어</t>
+          <t>AI, 백엔드 서버</t>
         </is>
       </c>
       <c r="I26" s="46" t="inlineStr">
         <is>
-          <t>PL-04, PL-06, HW-C-06</t>
-        </is>
-      </c>
-      <c r="J26" s="47" t="inlineStr">
+          <t>PL-06, PL-04, PL-05</t>
+        </is>
+      </c>
+      <c r="J26" s="44" t="inlineStr">
         <is>
           <t>김현우</t>
         </is>
@@ -6322,7 +6322,7 @@
     <row r="27">
       <c r="A27" s="44" t="inlineStr">
         <is>
-          <t>VZ-L-04</t>
+          <t>VZ-L-03</t>
         </is>
       </c>
       <c r="B27" s="45" t="inlineStr">
@@ -6332,40 +6332,40 @@
       </c>
       <c r="C27" s="46" t="inlineStr">
         <is>
-          <t>화면 구성 보조 LLM(가시화 내부)</t>
+          <t>실행 전 2단 확인 및 신뢰도 임계</t>
         </is>
       </c>
       <c r="D27" s="46" t="inlineStr">
         <is>
-          <t>가시화 내부의 로컬 LLM은 화면·파이프라인 구성 생성(노드 그래프), 데이터 요약·자연어 레이블링에 한정해 사용한다. 결과는 제안 상태로 표시하고 사용자가 수락해야 반영되며, 생성물은 측정된 사실과 구별해 표시한다. 로봇 제어 명령의 의도 해석은 범위에 포함하지 않는다.</t>
+          <t>① 인식된 문장이 맞는지, ② 그 문장을 이 임무·경로로 해석한 것이 맞는지 두 단계를 거쳐야 제어 명령이 발행된다. 인식 신뢰도가 임계 미만이면 AI에 전달하지 않고 재확인을 요구한다. 되돌릴 수 있는 조회·뷰 전환은 1차 확인만으로 진행한다.</t>
         </is>
       </c>
       <c r="E27" s="46" t="inlineStr">
         <is>
-          <t>가시화→로컬 LLM(별도 프로세스)→가시화</t>
+          <t>(내부 처리)</t>
         </is>
       </c>
       <c r="F27" s="44" t="inlineStr">
         <is>
-          <t>사용자 요청 시 1회(이벤트 기반), 응답은 스트리밍 표시</t>
+          <t>제어 명령 1건당 매회(생략 불가)</t>
         </is>
       </c>
       <c r="G27" s="46" t="inlineStr">
         <is>
-          <t>LLM 호출은 비용·지연이 커 주기 실행 대상이 아니다. 응답을 전부 받은 뒤 한 번에 띄우면 체감 지연이 커지므로 생성되는 대로 스트리밍 표시하는 방식이 사용성에서 유리해 선정.</t>
+          <t>공공 서비스에서 오인식으로 장비가 움직이면 되돌릴 수 없다. 신뢰도가 높을 때 확인을 건너뛰는 방식도 있으나 사고는 임계 근처에서 발생하므로, 제어 액션은 예외 없이 2단 확인을 거치도록 선정. 임계값은 실측 후 확정.</t>
         </is>
       </c>
       <c r="H27" s="46" t="inlineStr">
         <is>
-          <t>AI</t>
+          <t>AI, 백엔드 서버, 하드웨어</t>
         </is>
       </c>
       <c r="I27" s="46" t="inlineStr">
         <is>
-          <t>PL-06</t>
-        </is>
-      </c>
-      <c r="J27" s="47" t="inlineStr">
+          <t>PL-04, PL-06, HW-C-06</t>
+        </is>
+      </c>
+      <c r="J27" s="44" t="inlineStr">
         <is>
           <t>김현우</t>
         </is>
@@ -6374,46 +6374,50 @@
     <row r="28">
       <c r="A28" s="44" t="inlineStr">
         <is>
-          <t>VZ-C-01</t>
+          <t>VZ-L-04</t>
         </is>
       </c>
       <c r="B28" s="45" t="inlineStr">
         <is>
-          <t>공통</t>
+          <t>LLM·음성</t>
         </is>
       </c>
       <c r="C28" s="46" t="inlineStr">
         <is>
-          <t>권한(RBAC)과 역할 확인</t>
+          <t>화면 구성 보조 LLM(가시화 내부)</t>
         </is>
       </c>
       <c r="D28" s="46" t="inlineStr">
         <is>
-          <t>열람/조작/관리 역할에 따라 화면에서 제어 UI를 사전 차단한다. 화면 차단은 사용자 편의이고 실제 강제는 백엔드가 수행하므로, 가시화는 현재 역할 조회로 역할을 확인해 표시·차단까지만 담당한다.</t>
+          <t>가시화 내부의 로컬 LLM은 화면·파이프라인 구성 생성(노드 그래프), 데이터 요약·자연어 레이블링에 한정해 사용한다. 결과는 제안 상태로 표시하고 사용자가 수락해야 반영되며, 생성물은 측정된 사실과 구별해 표시한다. 로봇 제어 명령의 의도 해석은 범위에 포함하지 않는다.</t>
         </is>
       </c>
       <c r="E28" s="46" t="inlineStr">
         <is>
-          <t>백엔드 역할 조회 API→가시화</t>
+          <t>가시화→로컬 LLM(별도 프로세스)→가시화</t>
         </is>
       </c>
       <c r="F28" s="44" t="inlineStr">
         <is>
-          <t>로그인 시 1회 + 토큰 갱신 시</t>
+          <t>사용자 요청 시 1회(이벤트 기반), 응답은 스트리밍 표시</t>
         </is>
       </c>
       <c r="G28" s="46" t="inlineStr">
         <is>
-          <t>역할은 세션 중 거의 바뀌지 않아 주기 조회는 낭비다. 실제 방어선이 백엔드에 있어 화면이 최신 역할을 조금 늦게 알아도 보안 위험이 없으므로, 로그인·갱신 시점 조회로 충분해 선정.</t>
+          <t>LLM 호출은 비용·지연이 커 주기 실행 대상이 아니다. 응답을 전부 받은 뒤 한 번에 띄우면 체감 지연이 커지므로 생성되는 대로 스트리밍 표시하는 방식이 사용성에서 유리해 선정.</t>
         </is>
       </c>
       <c r="H28" s="46" t="inlineStr">
         <is>
-          <t>백엔드 서버</t>
-        </is>
-      </c>
-      <c r="I28" s="46" t="n"/>
-      <c r="J28" s="47" t="inlineStr">
+          <t>AI</t>
+        </is>
+      </c>
+      <c r="I28" s="46" t="inlineStr">
+        <is>
+          <t>PL-06</t>
+        </is>
+      </c>
+      <c r="J28" s="44" t="inlineStr">
         <is>
           <t>김현우</t>
         </is>
@@ -6422,50 +6426,246 @@
     <row r="29">
       <c r="A29" s="44" t="inlineStr">
         <is>
+          <t>VZ-C-01</t>
+        </is>
+      </c>
+      <c r="B29" s="45" t="inlineStr">
+        <is>
+          <t>공통</t>
+        </is>
+      </c>
+      <c r="C29" s="46" t="inlineStr">
+        <is>
+          <t>권한(RBAC)과 역할 확인</t>
+        </is>
+      </c>
+      <c r="D29" s="46" t="inlineStr">
+        <is>
+          <t>열람/조작/관리 역할에 따라 화면에서 제어 UI를 사전 차단한다. 화면 차단은 사용자 편의이고 실제 강제는 백엔드가 수행하므로, 가시화는 현재 역할 조회로 역할을 확인해 표시·차단까지만 담당한다.</t>
+        </is>
+      </c>
+      <c r="E29" s="46" t="inlineStr">
+        <is>
+          <t>백엔드 역할 조회 API→가시화</t>
+        </is>
+      </c>
+      <c r="F29" s="44" t="inlineStr">
+        <is>
+          <t>로그인 시 1회 + 토큰 갱신 시</t>
+        </is>
+      </c>
+      <c r="G29" s="46" t="inlineStr">
+        <is>
+          <t>역할은 세션 중 거의 바뀌지 않아 주기 조회는 낭비다. 실제 방어선이 백엔드에 있어 화면이 최신 역할을 조금 늦게 알아도 보안 위험이 없으므로, 로그인·갱신 시점 조회로 충분해 선정.</t>
+        </is>
+      </c>
+      <c r="H29" s="46" t="inlineStr">
+        <is>
+          <t>백엔드 서버</t>
+        </is>
+      </c>
+      <c r="I29" s="46" t="n"/>
+      <c r="J29" s="44" t="inlineStr">
+        <is>
+          <t>김현우</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="44" t="inlineStr">
+        <is>
           <t>VZ-C-02</t>
         </is>
       </c>
-      <c r="B29" s="45" t="inlineStr">
+      <c r="B30" s="45" t="inlineStr">
         <is>
           <t>공통</t>
         </is>
       </c>
-      <c r="C29" s="46" t="inlineStr">
+      <c r="C30" s="46" t="inlineStr">
         <is>
           <t>외부 소스 부재 시 동작</t>
         </is>
       </c>
-      <c r="D29" s="46" t="inlineStr">
+      <c r="D30" s="46" t="inlineStr">
         <is>
           <t>레지스트리·상태 소스·AI·LLM이 연결되지 않은 상태에서도 정적 구성 파일로 컴포넌트 목록을 구성해 동작해야 한다. LLM이 미연결·무응답일 때는 관련 기능만 비활성화하고 나머지는 정상 동작한다.</t>
         </is>
       </c>
-      <c r="E29" s="46" t="inlineStr">
+      <c r="E30" s="46" t="inlineStr">
         <is>
           <t>(내부 처리)</t>
         </is>
       </c>
-      <c r="F29" s="44" t="inlineStr">
+      <c r="F30" s="44" t="inlineStr">
         <is>
           <t>해당 없음(기동 시 1회 로드)</t>
         </is>
       </c>
-      <c r="G29" s="46" t="inlineStr">
+      <c r="G30" s="46" t="inlineStr">
         <is>
           <t>다른 파트의 진척에 가시화가 블로킹되지 않게 하기 위한 요건이다. 전송 인터페이스·레지스트리 조회 형태·액션 어휘집·영상 변환 지점이 아직 확정 전이므로, 확정될 때까지는 정적 구성과 대체 데이터로 개발·시연을 진행한다.</t>
         </is>
       </c>
-      <c r="H29" s="46" t="inlineStr">
+      <c r="H30" s="46" t="inlineStr">
         <is>
           <t>전 파트</t>
         </is>
       </c>
-      <c r="I29" s="46" t="inlineStr">
+      <c r="I30" s="46" t="inlineStr">
         <is>
           <t>HW-C-01, HW-C-02</t>
         </is>
       </c>
-      <c r="J29" s="47" t="inlineStr">
+      <c r="J30" s="44" t="inlineStr">
+        <is>
+          <t>김현우</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="44" t="inlineStr">
+        <is>
+          <t>VZ-C-03</t>
+        </is>
+      </c>
+      <c r="B31" s="45" t="inlineStr">
+        <is>
+          <t>공통</t>
+        </is>
+      </c>
+      <c r="C31" s="46" t="inlineStr">
+        <is>
+          <t>집약 계층 경계 표기 — 자리 확보</t>
+        </is>
+      </c>
+      <c r="D31" s="46" t="inlineStr">
+        <is>
+          <t>화면이 받는 값이 원본 측정인지 이미 집약된 값인지, 집약이라면 어느 계층(장치·엣지·서버)에서 집약되었는지를 표기하는 자리를 계약에 둔다. 가시화는 집약값을 원본으로 오인해 재집약하지 않으며, 대상 수가 늘어나면 집약 지점을 화면 바깥으로 옮길 수 있어야 한다. 현 단계에서는 화면 측 집약(추상화 계층 뷰)만 사용한다.</t>
+        </is>
+      </c>
+      <c r="E31" s="46" t="inlineStr">
+        <is>
+          <t>규약(생산자→가시화)</t>
+        </is>
+      </c>
+      <c r="F31" s="44" t="inlineStr">
+        <is>
+          <t>해당 없음(계약 자리만 확보, 현 단계 미사용)</t>
+        </is>
+      </c>
+      <c r="G31" s="46" t="inlineStr">
+        <is>
+          <t>현재는 원본을 받아 화면이 집약해도 양이 감당된다. 그러나 대상이 늘면 집약은 엣지·서버에서 선행되어야 하고, 그때 화면은 '이미 집약된 값'을 받게 된다. 표기가 없으면 화면이 그 값을 다시 평균 내는 재집약 오류가 발생한다. 표기 필드는 지금 한 칸이면 되지만, 나중에 집약 계층을 옮기려면 데이터 의미 자체를 재정의해야 하므로 미리 연다.</t>
+        </is>
+      </c>
+      <c r="H31" s="46" t="inlineStr">
+        <is>
+          <t>AI, 백엔드 서버</t>
+        </is>
+      </c>
+      <c r="I31" s="46" t="inlineStr">
+        <is>
+          <t>PR-04, RK-02, GN-04</t>
+        </is>
+      </c>
+      <c r="J31" s="44" t="inlineStr">
+        <is>
+          <t>김현우</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="44" t="inlineStr">
+        <is>
+          <t>VZ-C-04</t>
+        </is>
+      </c>
+      <c r="B32" s="45" t="inlineStr">
+        <is>
+          <t>공통</t>
+        </is>
+      </c>
+      <c r="C32" s="46" t="inlineStr">
+        <is>
+          <t>권한 범위(scope) — 자리 확보</t>
+        </is>
+      </c>
+      <c r="D32" s="46" t="inlineStr">
+        <is>
+          <t>역할(열람/조작/관리)과 별개로 그 역할이 적용되는 범위(도메인·구역 집합)를 표현하는 자리를 권한 계약에 둔다. 다지점 운영에서는 같은 조작 역할이라도 자기 담당 구역 밖은 열람·제어할 수 없어야 한다. 캡스톤 시연은 단일 도메인이므로 현 단계에서는 전 범위로 간주한다.</t>
+        </is>
+      </c>
+      <c r="E32" s="46" t="inlineStr">
+        <is>
+          <t>백엔드 역할 조회 API→가시화</t>
+        </is>
+      </c>
+      <c r="F32" s="44" t="inlineStr">
+        <is>
+          <t>해당 없음(계약 자리만 확보, 현 단계 미사용)</t>
+        </is>
+      </c>
+      <c r="G32" s="46" t="inlineStr">
+        <is>
+          <t>단일 구역에서는 역할만으로 충분하지만 구역이 늘면 '역할 × 범위'가 되어야 한다. 범위가 없으면 담당이 아닌 구역까지 제어 가능해져 책임소재가 성립하지 않는다. 권한 매트릭스 상세가 추후 확정 항목이므로 그 확정 시 범위 축을 함께 정의하도록 지금 자리를 열어둔다.</t>
+        </is>
+      </c>
+      <c r="H32" s="46" t="inlineStr">
+        <is>
+          <t>백엔드 서버</t>
+        </is>
+      </c>
+      <c r="I32" s="46" t="n"/>
+      <c r="J32" s="44" t="inlineStr">
+        <is>
+          <t>김현우</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="44" t="inlineStr">
+        <is>
+          <t>VZ-C-05</t>
+        </is>
+      </c>
+      <c r="B33" s="45" t="inlineStr">
+        <is>
+          <t>공통</t>
+        </is>
+      </c>
+      <c r="C33" s="46" t="inlineStr">
+        <is>
+          <t>설계 규모 가정 명시 — 확인 요망</t>
+        </is>
+      </c>
+      <c r="D33" s="46" t="inlineStr">
+        <is>
+          <t>시연 규모와 설계 상한(동시 표시 대상 수, 구역 수, 동시 관제 사용자 수)을 요구사항에 명시하고, 그 이상은 별도 요구사항으로 다룬다. 현재 모든 주기·구독 방식은 구역 1개에 장치 수십 개 규모를 전제로 산정되어 있으나 그 전제가 문서에 적혀 있지 않다.</t>
+        </is>
+      </c>
+      <c r="E33" s="46" t="inlineStr">
+        <is>
+          <t>규약(팀 합의)</t>
+        </is>
+      </c>
+      <c r="F33" s="44" t="inlineStr">
+        <is>
+          <t>해당 없음(전제 정의)</t>
+        </is>
+      </c>
+      <c r="G33" s="46" t="inlineStr">
+        <is>
+          <t>주기 산정의 근거가 규모 가정에 걸려 있는데 그 가정이 문서에 없으면, 확장 논의가 나올 때마다 근거 없이 다시 논쟁하게 된다. 시연 규모와 설계 상한을 숫자로 못박아 두면 '이 설계가 어디까지 커버하는가'에 문서로 답할 수 있다. 숫자 자체는 팀 합의 사항이므로 확인 요망으로 둔다.</t>
+        </is>
+      </c>
+      <c r="H33" s="46" t="inlineStr">
+        <is>
+          <t>전 파트</t>
+        </is>
+      </c>
+      <c r="I33" s="46" t="n"/>
+      <c r="J33" s="44" t="inlineStr">
         <is>
           <t>김현우</t>
         </is>

--- a/피지컬팀 프로젝트 mk2 요구사항 정의서.xlsx
+++ b/피지컬팀 프로젝트 mk2 요구사항 정의서.xlsx
@@ -16,7 +16,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="9">
+  <fonts count="10">
     <font>
       <name val="Arial"/>
       <color rgb="FF000000"/>
@@ -61,6 +61,11 @@
       <name val="&quot;\0022\\0022맑은 고딕\\0022\0022&quot;"/>
       <b val="1"/>
       <color rgb="FF7F1D1D"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="맑은 고딕"/>
+      <color rgb="FF0070C0"/>
       <sz val="9"/>
     </font>
   </fonts>
@@ -228,7 +233,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="49">
+  <cellXfs count="52">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="bottom"/>
     </xf>
@@ -374,6 +379,15 @@
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="18" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -17948,7 +17962,7 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O33"/>
+  <dimension ref="A1:O34"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="12.63" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
     <col width="43.38" customWidth="1" style="48" min="4" max="4"/>
@@ -18033,12 +18047,45 @@
       </c>
       <c r="D2" s="43" t="inlineStr">
         <is>
-          <t>가시화 클라이언트(브라우저)가 백엔드 WS 게이트웨이를 통해 관측 대상의 상태를 구독한다. 상태는 device_status(기기 자기보고)·availability(서버 판정)·deployment(오케스트레이터) 3층과 last_seen으로 수신하며, 구독 요청은 전송 프로토콜의 채널·토픽 문자열이 아니라 계약 축 {entity, node, channel}로 표현한다. 브라우저는 브로커에 직접 접속할 수 없어 백엔드를 경유한다.</t>
+          <r>
+            <rPr>
+              <rFont val="맑은 고딕"/>
+              <b val="1"/>
+              <color rgb="FF0070C0"/>
+              <sz val="9"/>
+            </rPr>
+            <t>가시화 뷰어(브라우저·네이티브 앱 등)가</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="맑은 고딕"/>
+              <color rgb="FF000000"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve"> 백엔드 WS 게이트웨이를 통해 관측 대상의 상태를 구독한다. 상태는 device_status(기기 자기보고)·availability(서버 판정)·deployment(오케스트레이터) 3층과 last_seen으로 수신하며, 구독 요청은 전송 프로토콜의 채널·토픽 문자열이 아니라 계약 축 {entity, node, channel}로 표현한다. </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="맑은 고딕"/>
+              <b val="1"/>
+              <color rgb="FF0070C0"/>
+              <sz val="9"/>
+            </rPr>
+            <t>뷰어는 브로커에 직접 접속하지 않고 백엔드를 경유한다. 경유하는 이유는 브라우저의 기술적 제약이 아니라 권한·감사·집약 경계를 백엔드가 단독으로 강제해야 하기 때문이며, 따라서 브라우저가 아닌 뷰어에도 동일하게 적용된다.</t>
+          </r>
         </is>
       </c>
       <c r="E2" s="43" t="inlineStr">
         <is>
-          <t>백엔드 WS 게이트웨이→가시화(브라우저)</t>
+          <r>
+            <rPr>
+              <rFont val="맑은 고딕"/>
+              <b val="1"/>
+              <color rgb="FF0070C0"/>
+              <sz val="9"/>
+            </rPr>
+            <t>백엔드 WS 게이트웨이→가시화 뷰어</t>
+          </r>
         </is>
       </c>
       <c r="F2" s="14" t="inlineStr">
@@ -18085,7 +18132,31 @@
       </c>
       <c r="D3" s="43" t="inlineStr">
         <is>
-          <t>화면을 새로 열거나 재접속했을 때 구독 즉시 각 대상의 최신 상태를 1회 수신한다. 제공 방식은 백엔드가 대상별 마지막 상태를 캐시하고 구독 시점에 즉시 푸시하는 것으로 확정되었다(브로커 마지막 값 보존이 아니라 백엔드 캐시 — 브라우저가 백엔드를 경유하는 구조상 경로가 단일해 유리하다).</t>
+          <r>
+            <rPr>
+              <rFont val="맑은 고딕"/>
+              <color rgb="FF000000"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">화면을 새로 열거나 재접속했을 때 구독 즉시 각 대상의 최신 상태를 1회 수신한다. 제공 방식은 백엔드가 대상별 마지막 상태를 캐시하고 구독 시점에 즉시 푸시하는 것으로 확정되었다(브로커 마지막 값 보존이 아니라 백엔드 캐시 — </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="맑은 고딕"/>
+              <b val="1"/>
+              <color rgb="FF0070C0"/>
+              <sz val="9"/>
+            </rPr>
+            <t>뷰어가 백엔드를 경유하는</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="맑은 고딕"/>
+              <color rgb="FF000000"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve"> 구조상 경로가 단일해 유리하다).</t>
+          </r>
         </is>
       </c>
       <c r="E3" s="43" t="inlineStr">
@@ -18189,7 +18260,31 @@
       </c>
       <c r="D5" s="43" t="inlineStr">
         <is>
-          <t>시계열 지표를 백엔드 질의 프록시로 조회한다(시점 조회/구간 조회). 평시 조회 대상은 구역 단위로 집약된 요약 시계열이며, 원본이 필요한 구간은 프록시가 엣지의 원본 저장소로 중계해 대신 조회한다. 자격 증명 은닉·권한·rate limit을 백엔드에서 통제하므로 브라우저는 지표 저장소에 직접 접근하지 않는다.</t>
+          <r>
+            <rPr>
+              <rFont val="맑은 고딕"/>
+              <color rgb="FF000000"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">시계열 지표를 백엔드 질의 프록시로 조회한다(시점 조회/구간 조회). 평시 조회 대상은 구역 단위로 집약된 요약 시계열이며, 원본이 필요한 구간은 프록시가 엣지의 원본 저장소로 중계해 대신 조회한다. 자격 증명 은닉·권한·rate limit을 백엔드에서 통제하므로 </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="맑은 고딕"/>
+              <b val="1"/>
+              <color rgb="FF0070C0"/>
+              <sz val="9"/>
+            </rPr>
+            <t>가시화 뷰어는 지표 저장소에</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="맑은 고딕"/>
+              <color rgb="FF000000"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve"> 직접 접근하지 않는다.</t>
+          </r>
         </is>
       </c>
       <c r="E5" s="43" t="inlineStr">
@@ -18241,7 +18336,31 @@
       </c>
       <c r="D6" s="43" t="inlineStr">
         <is>
-          <t>백엔드 감사 조회 API로 대상·기간·조작자·발행 경로를 필터해 조회하고, "이 대상을 마지막으로 조작한 사람"과 그 판단 근거를 화면에 표시한다. 브라우저는 감사 저장소에 직접 접근하지 않는다.</t>
+          <r>
+            <rPr>
+              <rFont val="맑은 고딕"/>
+              <color rgb="FF000000"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">백엔드 감사 조회 API로 대상·기간·조작자·발행 경로를 필터해 조회하고, "이 대상을 마지막으로 조작한 사람"과 그 판단 근거를 화면에 표시한다. </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="맑은 고딕"/>
+              <b val="1"/>
+              <color rgb="FF0070C0"/>
+              <sz val="9"/>
+            </rPr>
+            <t>가시화 뷰어는 감사 저장소에</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="맑은 고딕"/>
+              <color rgb="FF000000"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve"> 직접 접근하지 않는다.</t>
+          </r>
         </is>
       </c>
       <c r="E6" s="43" t="inlineStr">
@@ -18293,7 +18412,48 @@
       </c>
       <c r="D7" s="43" t="inlineStr">
         <is>
-          <t>관제용 고해상도 로봇 시점 영상(온디맨드)과 고정 비전센서 상시 영상을 브라우저에서 재생한다. 카메라 원본 규격(RTSP 등)은 브라우저가 직접 재생할 수 없으므로 백엔드 미디어 경로를 경유해 브라우저 재생 가능 규격으로 받는다(변환 지점은 Tier 2). AI 추론용 다운스케일 프레임(HW-R-04)과는 별개의 스트림이다.</t>
+          <r>
+            <rPr>
+              <rFont val="맑은 고딕"/>
+              <color rgb="FF000000"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">관제용 고해상도 로봇 시점 영상(온디맨드)과 고정 비전센서 </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="맑은 고딕"/>
+              <b val="1"/>
+              <color rgb="FF0070C0"/>
+              <sz val="9"/>
+            </rPr>
+            <t>상시 영상을 가시화 뷰어에서 재생한다</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="맑은 고딕"/>
+              <color rgb="FF000000"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">. 카메라 원본 규격(RTSP 등)은 </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="맑은 고딕"/>
+              <b val="1"/>
+              <color rgb="FF0070C0"/>
+              <sz val="9"/>
+            </rPr>
+            <t>뷰어가 직접 재생할 수 없으므로 백엔드 미디어 경로를 경유해 뷰어가 재생 가능한 규격으로 받는다</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="맑은 고딕"/>
+              <color rgb="FF000000"/>
+              <sz val="9"/>
+            </rPr>
+            <t>(변환 지점은 Tier 2). AI 추론용 다운스케일 프레임(HW-R-04)과는 별개의 스트림이다.</t>
+          </r>
         </is>
       </c>
       <c r="E7" s="43" t="inlineStr">
@@ -18308,7 +18468,31 @@
       </c>
       <c r="G7" s="43" t="inlineStr">
         <is>
-          <t>로봇 시점 관제 영상이 온디맨드 15fps 고해상도로 정의되어 있고(HW-R-07) 고정 비전센서는 상시 15fps(HW-S-06)이므로 그 이상을 요구해도 받을 원본이 없다. 전 카메라 상시 재생은 무선 대역폭과 브라우저 디코딩을 동시에 낭비하므로, 열린 패널만 수신하는 온디맨드 방식이 가장 효율적이라 선정.</t>
+          <r>
+            <rPr>
+              <rFont val="맑은 고딕"/>
+              <color rgb="FF000000"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">로봇 시점 관제 영상이 온디맨드 15fps 고해상도로 정의되어 있고(HW-R-07) 고정 비전센서는 상시 15fps(HW-S-06)이므로 그 이상을 요구해도 받을 원본이 없다. 전 카메라 상시 재생은 무선 대역폭과 </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="맑은 고딕"/>
+              <b val="1"/>
+              <color rgb="FF0070C0"/>
+              <sz val="9"/>
+            </rPr>
+            <t>뷰어 디코딩</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="맑은 고딕"/>
+              <color rgb="FF000000"/>
+              <sz val="9"/>
+            </rPr>
+            <t>을 동시에 낭비하므로, 열린 패널만 수신하는 온디맨드 방식이 가장 효율적이라 선정.</t>
+          </r>
         </is>
       </c>
       <c r="H7" s="43" t="inlineStr">
@@ -18568,7 +18752,31 @@
       </c>
       <c r="G12" s="43" t="inlineStr">
         <is>
-          <t>지금은 구역 하나에 장치 수십 개라 전체를 구독해도 문제가 없다. 그러나 다지점·다구역으로 확장되면 전량 구독이 브라우저 수신 대역과 초기 스냅샷을 동시에 압박한다. 화면 반영을 병합해도 수신량 자체는 줄지 않으므로 구독 단계에서 범위를 좁히는 수밖에 없다. 지금 파라미터 자리를 남기는 비용은 필드 하나지만, 나중에 구독 프로토콜을 바꾸는 비용은 백엔드 게이트웨이와 전 화면에 전파되므로 자리만 미리 연다.</t>
+          <r>
+            <rPr>
+              <rFont val="맑은 고딕"/>
+              <color rgb="FF000000"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">지금은 구역 하나에 장치 수십 개라 전체를 구독해도 문제가 없다. 그러나 다지점·다구역으로 확장되면 전량 구독이 </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="맑은 고딕"/>
+              <b val="1"/>
+              <color rgb="FF0070C0"/>
+              <sz val="9"/>
+            </rPr>
+            <t>뷰어 수신 대역</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="맑은 고딕"/>
+              <color rgb="FF000000"/>
+              <sz val="9"/>
+            </rPr>
+            <t>과 초기 스냅샷을 동시에 압박한다. 화면 반영을 병합해도 수신량 자체는 줄지 않으므로 구독 단계에서 범위를 좁히는 수밖에 없다. 지금 파라미터 자리를 남기는 비용은 필드 하나지만, 나중에 구독 프로토콜을 바꾸는 비용은 백엔드 게이트웨이와 전 화면에 전파되므로 자리만 미리 연다.</t>
+          </r>
         </is>
       </c>
       <c r="H12" s="43" t="inlineStr">
@@ -18724,7 +18932,48 @@
       </c>
       <c r="G15" s="43" t="inlineStr">
         <is>
-          <t>감사를 별도 경로로 보내면 탭 종료·네트워크 단절 시 "실행은 됐는데 기록이 없음"이 발생한다. 브라우저가 직접 기록하면 조작자 정보가 클라이언트 자기신고가 되어 위조도 가능하고, 시각도 사용자 PC 시계에 의존한다. 장치는 NTP로 시각을 맞추는데(HW-S-08) 브라우저에는 그 보장이 없으므로 서버 시각 주입이 맞아 선정.</t>
+          <r>
+            <rPr>
+              <rFont val="맑은 고딕"/>
+              <color rgb="FF000000"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">감사를 별도 경로로 보내면 탭 종료·네트워크 단절 시 "실행은 됐는데 기록이 없음"이 발생한다. </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="맑은 고딕"/>
+              <b val="1"/>
+              <color rgb="FF0070C0"/>
+              <sz val="9"/>
+            </rPr>
+            <t>뷰어가 직접 기록하면</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="맑은 고딕"/>
+              <color rgb="FF000000"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve"> 조작자 정보가 클라이언트 자기신고가 되어 위조도 가능하고, 시각도 사용자 PC 시계에 의존한다. 장치는 NTP로 시각을 맞추는데(HW-S-08) </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="맑은 고딕"/>
+              <b val="1"/>
+              <color rgb="FF0070C0"/>
+              <sz val="9"/>
+            </rPr>
+            <t>뷰어를 실행하는 단말에는 그 보장이 없으므로</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="맑은 고딕"/>
+              <color rgb="FF000000"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve"> 서버 시각 주입이 맞아 선정.</t>
+          </r>
         </is>
       </c>
       <c r="H15" s="43" t="inlineStr">
@@ -19627,7 +19876,7 @@
         </is>
       </c>
     </row>
-    <row r="33">
+    <row r="33" s="48">
       <c r="A33" s="14" t="inlineStr">
         <is>
           <t>VZ-C-05</t>
@@ -19674,6 +19923,58 @@
         </is>
       </c>
       <c r="J33" s="14" t="inlineStr">
+        <is>
+          <t>김현우</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" s="48">
+      <c r="A34" s="49" t="inlineStr">
+        <is>
+          <t>VZ-C-06</t>
+        </is>
+      </c>
+      <c r="B34" s="50" t="inlineStr">
+        <is>
+          <t>공통</t>
+        </is>
+      </c>
+      <c r="C34" s="51" t="inlineStr">
+        <is>
+          <t>원천 종류(실물·시뮬레이션) 표기 — 확인 요망</t>
+        </is>
+      </c>
+      <c r="D34" s="51" t="inlineStr">
+        <is>
+          <t>값·이벤트·명령 결과에 그 원천이 실물 장치인지 시뮬레이션인지 기록 재생인지를 표기와 함께 수신해, 화면이 실물과 비실물을 구분해 표시한다. 명령 요청에도 현재 원천 종류를 함께 실어 보내, 감사 기록이 실물 조작과 시뮬레이션 조작을 구분할 수 있게 한다. 표기의 발행 주체와 필드 형식은 전 파트 합의가 필요하며, 가시화는 이 표기를 읽어 구분 표시하는 소비자 역할이다.</t>
+        </is>
+      </c>
+      <c r="E34" s="51" t="inlineStr">
+        <is>
+          <t>원천(하드웨어·시뮬레이터)→백엔드→가시화 / 가시화→백엔드(명령 요청에 동봉)</t>
+        </is>
+      </c>
+      <c r="F34" s="49" t="inlineStr">
+        <is>
+          <t>해당 없음(값·명령에 표기 동반, 팀 합의 대기)</t>
+        </is>
+      </c>
+      <c r="G34" s="51" t="inlineStr">
+        <is>
+          <t>집약 계층 표기(VZ-C-03)와 같이 값에 동반되는 메타이므로 별도 주기가 없다. 표기가 없으면 시뮬레이션 값이 실물 값과 동일한 봉투로 올라와 화면에서 구분할 수단이 없고, 더 중요하게는 감사 기록에 "그때 시뮬레이션 중이었다"가 남지 않아 사후 조사가 성립하지 않는다(VZ-O-03). 캡스톤 시연 규모에서는 드러나지 않지만 시뮬레이터가 실제 원천을 대체·병행하는 순간부터 성립하며, 국가 인프라 규모에서는 훈련과 실제 상황을 기록상 구분하지 못하는 문제가 된다. 지금 표기 자리를 여는 비용은 필드 하나지만 나중에 끼우는 비용은 발행·저장·감사·화면 전 경로로 전파되므로 자리를 먼저 연다.</t>
+        </is>
+      </c>
+      <c r="H34" s="51" t="inlineStr">
+        <is>
+          <t>전 파트</t>
+        </is>
+      </c>
+      <c r="I34" s="51" t="inlineStr">
+        <is>
+          <t>BE-S-06, BE-X-02, BE-S-05</t>
+        </is>
+      </c>
+      <c r="J34" s="49" t="inlineStr">
         <is>
           <t>김현우</t>
         </is>

--- a/피지컬팀 프로젝트 mk2 요구사항 정의서.xlsx
+++ b/피지컬팀 프로젝트 mk2 요구사항 정의서.xlsx
@@ -19569,7 +19569,7 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O42"/>
+  <dimension ref="A1:O47"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="12.63" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
     <col width="43.38" customWidth="1" style="54" min="4" max="4"/>
@@ -20694,7 +20694,7 @@
       </c>
       <c r="D22" s="23" t="inlineStr">
         <is>
-          <t>승인된 계획이 구간 단위로 어디까지 수행됐고 어느 단계에서 실패했는지를 노드 형태로 표시해 추적·디버깅할 수 있게 한다. 여러 구역에 걸친 계획은 구역별 구간과 순서를 함께 보여준다. [확인 요망] 계획을 생성·검증하던 AI-D-01·02가 신판 AI 시트에서 삭제되어 구간 정보의 생산 주체가 없다. 생산 주체가 정해지기 전까지 이 요구사항은 목 데이터로만 성립한다.</t>
+          <t>승인된 계획이 구간 단위로 어디까지 수행됐고 어느 단계에서 실패했는지를 노드 형태로 표시해 추적·디버깅할 수 있게 한다. 여러 구역에 걸친 계획은 구역별 구간과 순서를 함께 보여준다. 구간 정보는 가시화가 생성한 태스크(VZ-G-02)와 그 실행 기록(VZ-D-02)에서 파생된다.</t>
         </is>
       </c>
       <c r="E22" s="23" t="inlineStr">
@@ -20719,7 +20719,7 @@
       </c>
       <c r="I22" s="23" t="inlineStr">
         <is>
-          <t>HW-R-05, HW-R-03, BE-X-04  [계획 생성·검증 상대 없음 — AI-D-01·02 삭제]</t>
+          <t>HW-R-05, HW-R-03, BE-X-04  ← VZ-G-02, VZ-D-02</t>
         </is>
       </c>
       <c r="J22" s="22" t="inlineStr">
@@ -20798,7 +20798,7 @@
       </c>
       <c r="D24" s="23" t="inlineStr">
         <is>
-          <t>실행 계획과 그 근거(전역 임무 → 구역 분할 → 구간별 계획 → 검증 결과, 계획 생성기 버전, 입력 맥락 버전)를 받아 화면에 펼쳐 보이고, 사용자가 승인하거나 거부할 수 있게 한다. 승인 전에는 계획이 실행되지 않으며, 승인·거부 결과는 백엔드로 회신되어 승인된 계획만 엣지·로봇으로 발행된다. [확인 요망] 계획 생성·검증(AI-D-01·02·04)이 신판 AI 시트에서 삭제되어 승인 대상 자체를 만드는 파트가 없다. 승인 절차와 화면은 그대로 필요하나 생산 주체 확정이 선행되어야 한다.</t>
+          <t>실행 계획과 그 근거(발화 → 마일스톤 → 태스크 → 검증 결과, 생성기 버전, 입력 텍스트 버전)를 화면에 펼쳐 보이고, 사용자가 승인하거나 거부할 수 있게 한다. 승인 전에는 계획이 실행되지 않으며, 승인된 계획만 백엔드를 거쳐 엣지·로봇으로 발행된다. 계획 생성·검증 주체가 AI에서 가시화로 바뀌었으므로(VZ-G-01~03) 화면은 자신이 만든 결과를 스스로 승인 요청하는 구조가 된다 — 따라서 생성 근거와 검증 결과를 감추지 않고 그대로 펼치는 것이 이전보다 더 중요하다.</t>
         </is>
       </c>
       <c r="E24" s="23" t="inlineStr">
@@ -20823,7 +20823,7 @@
       </c>
       <c r="I24" s="23" t="inlineStr">
         <is>
-          <t>BE-X-04  [계획 생성·검증 상대 없음 — AI-D-02·04 삭제]</t>
+          <t>BE-X-04  ← VZ-G-01·02·03</t>
         </is>
       </c>
       <c r="J24" s="22" t="inlineStr">
@@ -20902,7 +20902,7 @@
       </c>
       <c r="D26" s="28" t="inlineStr">
         <is>
-          <t>AI가 해석한 임무와 그로부터 생성·검증된 계획을 제안 형태로 화면에 표시하고, 사용자가 검토·수정한 뒤 명시적으로 수락해야 발행된다. 가시화는 전달·표시·수락 절차와 결과 추적을 맡는다. [확인 요망] 구판이 근거로 삼던 계획 생성·검증(AI-D-01·02)이 삭제되어, 명령 의도 해석에 더해 계획 생성 주체까지 미정이 되었다. 두 건 모두 담당 확정이 필요하다.</t>
+          <t>발화 텍스트에서 해석·생성·검증된 임무와 계획(VZ-G-01~03)을 제안 형태로 화면에 표시하고, 사용자가 검토·수정한 뒤 명시적으로 수락해야 발행된다. 가시화는 전달·표시·수락 절차와 결과 추적을 맡는다. 구판에서 비어 있던 명령 의도 해석과 계획 생성이 모두 가시화로 확정되었다 — 발화 텍스트를 마일스톤으로 분리하는 VZ-G-01이 곧 의도 해석에 해당한다. 해석기가 두 파트에 나뉘지 않으므로 같은 발화가 서로 다른 결과를 내는 문제도 사라진다.</t>
         </is>
       </c>
       <c r="E26" s="23" t="inlineStr">
@@ -20927,7 +20927,7 @@
       </c>
       <c r="I26" s="29" t="inlineStr">
         <is>
-          <t>AI-C-09, BE-X-04  [계획 생성 상대 없음 — AI-D-01 삭제]</t>
+          <t>AI-C-09, BE-X-04  ← VZ-G-01·02·03</t>
         </is>
       </c>
       <c r="J26" s="22" t="inlineStr">
@@ -20954,7 +20954,7 @@
       </c>
       <c r="D27" s="28" t="inlineStr">
         <is>
-          <t>① 인식된 문장이 맞는지, ② 그 문장을 이 임무·경로로 해석한 것이 맞는지 두 단계를 거쳐야 제어 명령이 발행된다. 인식 신뢰도가 임계 미만이면 AI에 전달하지 않고 재확인을 요구한다. 해석을 수행하는 기능이 선택 기능으로 배치될 경우(AI-C-09) 그 기능이 없는 배치에서는 음성 제어 경로 자체를 비활성화한다. 계획 검증(AI-D-02)이 삭제되었으므로 2단 확인의 ② 단계는 당분간 '해석 결과'만을 대상으로 하고, 검증 결과 표시는 생산 주체 확정 후 붙인다. 되돌릴 수 있는 조회·뷰 전환은 1차 확인만으로 진행한다.</t>
+          <t>① 인식된 문장이 맞는지, ② 그 문장을 이 임무·경로로 해석한 것이 맞는지 두 단계를 거쳐야 제어 명령이 발행된다. 인식 신뢰도가 임계 미만이면 AI에 전달하지 않고 재확인을 요구한다. 해석을 수행하는 기능이 선택 기능으로 배치될 경우(AI-C-09) 그 기능이 없는 배치에서는 음성 제어 경로 자체를 비활성화한다. 2단 확인의 ② 단계는 VZ-G-01의 해석 결과와 VZ-G-03의 검증 결과를 함께 대상으로 한다. 해석과 검증을 같은 파트가 수행하게 되었으므로, 확인 화면은 '무엇을 근거로 그렇게 해석했는가'를 반드시 함께 보여야 한다 — 생성한 쪽이 확인 화면도 만들면 자기 결과를 유리하게 요약할 여지가 생기기 때문이다. 되돌릴 수 있는 조회·뷰 전환은 1차 확인만으로 진행한다.</t>
         </is>
       </c>
       <c r="E27" s="23" t="inlineStr">
@@ -20979,7 +20979,7 @@
       </c>
       <c r="I27" s="28" t="inlineStr">
         <is>
-          <t>HW-C-06, AI-C-09, BE-X-04  [계획 검증 상대 없음 — AI-D-02 삭제]</t>
+          <t>HW-C-06, AI-C-09, BE-X-04  ← VZ-G-01·03</t>
         </is>
       </c>
       <c r="J27" s="22" t="inlineStr">
@@ -21006,7 +21006,7 @@
       </c>
       <c r="D28" s="23" t="inlineStr">
         <is>
-          <t>가시화 내부의 로컬 LLM은 화면·파이프라인 구성 생성(노드 그래프), 데이터 요약·자연어 레이블링에 한정해 사용한다. 결과는 제안 상태로 표시하고 사용자가 수락해야 반영되며, 생성물은 측정된 사실과 구별해 표시한다. 로봇 제어 명령의 의도 해석은 범위에 포함하지 않는다.</t>
+          <t>가시화 내부의 로컬 LLM은 화면·파이프라인 구성 생성(노드 그래프), 데이터 요약·자연어 레이블링에 한정해 사용한다. 결과는 제안 상태로 표시하고 사용자가 수락해야 반영되며, 생성물은 측정된 사실과 구별해 표시한다. 임무 생성 계열(VZ-G-01~05)은 같은 로컬 LLM 계층을 쓰되 이 요구사항과 별개의 기능으로 분리해 관리한다 — 화면 구성 보조와 임무 생성은 실패했을 때의 영향 범위가 다르므로 한 기능으로 묶지 않는다.</t>
         </is>
       </c>
       <c r="E28" s="23" t="inlineStr">
@@ -21110,7 +21110,7 @@
       </c>
       <c r="D30" s="23" t="inlineStr">
         <is>
-          <t>레지스트리·상태 소스·AI·LLM이 연결되지 않은 상태에서도 정적 구성 파일로 컴포넌트 목록을 구성해 동작해야 한다. LLM이 미연결·무응답일 때는 관련 기능만 비활성화하고 나머지는 정상 동작한다.</t>
+          <t>레지스트리·상태 소스·AI·LLM이 연결되지 않은 상태에서도 정적 구성 파일로 컴포넌트 목록을 구성해 동작해야 한다. LLM이 미연결·무응답일 때는 관련 기능만 비활성화하고 나머지는 정상 동작한다. 임무 생성(VZ-G-01·02)이 로컬 LLM에 의존하게 되었으므로 이 요구사항은 개발 편의가 아니라 운용 요구사항이다 — LLM이 없으면 생성만 멈추고 기존 임무의 실행·관측·디버깅은 계속되어야 하며, 수동 입력 경로를 남긴다.</t>
         </is>
       </c>
       <c r="E30" s="23" t="inlineStr">
@@ -21370,7 +21370,7 @@
       </c>
       <c r="D35" s="45" t="inlineStr">
         <is>
-          <t>임무를 마일스톤 → 태스크 → 액션 아이템 3계층으로 받아 계층을 따라 내려가며 표시한다. 마일스톤은 도메인 무관 추상 단위이고, 태스크는 수행 가능 단위이며 deps로 분기·합류를 표현하는 DAG다. 액션 아이템만이 대상 기종에 의존한다. 태스크 종료는 평가(Evaluation) 통과로만 성립하며 평가 전 상태는 별도 상태로 표시한다. 액션 아이템 전개 중 파생된 태스크는 파생 출처를 유지한다. [확인 요망] 이 계층 구조의 생산 주체가 미정이다 — 계획 생성·검증(구 AI-D-01·02·04)이 삭제되었다.</t>
+          <t>임무를 마일스톤 → 태스크 → 액션 아이템 3계층으로 받아 계층을 따라 내려가며 표시한다. 마일스톤은 도메인 무관 추상 단위이고, 태스크는 수행 가능 단위이며 deps로 분기·합류를 표현하는 DAG다. 액션 아이템만이 대상 기종에 의존한다. 태스크 종료는 평가(Evaluation) 통과로만 성립하며 평가 전 상태는 별도 상태로 표시한다. 액션 아이템 전개 중 파생된 태스크는 파생 출처를 유지한다. 이 계층의 생산 주체는 가시화다 — 마일스톤은 VZ-G-01, 태스크는 VZ-G-02, 액션 아이템은 VZ-G-04가 만들고 평가는 VZ-G-05가 판정한다. 다만 사전조건이 깨졌을 때의 재생성 판단(구 AI-D-04)은 인수 범위에서 제외했으므로, 실행 중 파생 태스크는 VZ-G-04의 되돌림 경로로만 생긴다 [확인 요망].</t>
         </is>
       </c>
       <c r="E35" s="45" t="inlineStr">
@@ -21395,7 +21395,7 @@
       </c>
       <c r="I35" s="45" t="inlineStr">
         <is>
-          <t>BE-X-04, AI-C-09  [계층 생산 주체 미정]</t>
+          <t>BE-X-04, AI-C-09  ← VZ-G-01·02·04·05가 생산</t>
         </is>
       </c>
       <c r="J35" s="43" t="inlineStr">
@@ -21763,6 +21763,266 @@
         </is>
       </c>
       <c r="J42" s="43" t="inlineStr">
+        <is>
+          <t>김현우</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" s="54">
+      <c r="A43" s="43" t="inlineStr">
+        <is>
+          <t>VZ-G-01</t>
+        </is>
+      </c>
+      <c r="B43" s="44" t="inlineStr">
+        <is>
+          <t>생성</t>
+        </is>
+      </c>
+      <c r="C43" s="45" t="inlineStr">
+        <is>
+          <t>발화 텍스트 → 마일스톤 분리</t>
+        </is>
+      </c>
+      <c r="D43" s="45" t="inlineStr">
+        <is>
+          <t>STT로 변환된 발화 텍스트(VZ-L-01)를 임무 하나와 마일스톤 목록으로 분리한다. 마일스톤은 완전히 추상이며 하드웨어 어휘를 포함하지 않는다(VZ-D-03). 분리 결과는 제안 상태로 표시하고 사용자가 수락해야 하위 생성으로 넘어간다(VZ-L-02). 분리에 사용한 생성기 버전과 입력 텍스트를 근거로 함께 남겨 실패 시 이 단계까지 역추적할 수 있게 한다. 대상 호칭은 레지스트리의 표시 이름·별칭으로 해석한다. 로컬 LLM이 없거나 무응답이면 이 기능만 비활성화하고 수동 입력 경로를 남긴다(VZ-C-02).</t>
+        </is>
+      </c>
+      <c r="E43" s="45" t="inlineStr">
+        <is>
+          <t>가시화 내부(로컬 LLM)→가시화</t>
+        </is>
+      </c>
+      <c r="F43" s="43" t="inlineStr">
+        <is>
+          <t>발화 수락 시 1회(이벤트 기반), 응답은 스트리밍 표시</t>
+        </is>
+      </c>
+      <c r="G43" s="45" t="inlineStr">
+        <is>
+          <t>발화는 비주기이므로 생성도 비주기다. 스트리밍 표시하는 이유는 분리 결과를 전부 받은 뒤 한 번에 띄우면 체감 지연이 커지기 때문이다. 이 단계를 별도 요구사항으로 세우는 이유는, 마일스톤 분리 자체가 실패 지점이 될 수 있어서다 — 잘못 쪼갠 마일스톤은 하위 전체를 무너뜨리므로 생성 근거가 기록에 남아야 역추적이 최상위까지 닿는다.</t>
+        </is>
+      </c>
+      <c r="H43" s="45" t="inlineStr">
+        <is>
+          <t>AI, 백엔드 서버</t>
+        </is>
+      </c>
+      <c r="I43" s="45" t="inlineStr">
+        <is>
+          <t>AI-C-09, AI-C-16, BE-Q-03  [구 AI-D-01 삭제분 인수]</t>
+        </is>
+      </c>
+      <c r="J43" s="43" t="inlineStr">
+        <is>
+          <t>김현우</t>
+        </is>
+      </c>
+    </row>
+    <row r="44" s="54">
+      <c r="A44" s="43" t="inlineStr">
+        <is>
+          <t>VZ-G-02</t>
+        </is>
+      </c>
+      <c r="B44" s="44" t="inlineStr">
+        <is>
+          <t>생성</t>
+        </is>
+      </c>
+      <c r="C44" s="45" t="inlineStr">
+        <is>
+          <t>마일스톤 → 태스크 생성</t>
+        </is>
+      </c>
+      <c r="D44" s="45" t="inlineStr">
+        <is>
+          <t>수락된 마일스톤마다 수행 가능한 태스크를 생성한다. 태스크는 일렬이 아니라 deps로 분기·합류를 갖는 DAG이며, 하나의 마일스톤에 여러 태스크가 생길 수 있다. 태스크 계층까지는 적용 대상과 무관한 범용 단위이고 하드웨어 어휘를 포함하지 않는다. 생성 방식은 특정 LLM이나 계획 라이브러리를 필수로 하지 않으며, 검증 가능한 행동 단위와 조건 표현을 사용한다. 확인 가능한 정보 범위를 넘는 계획을 만들지 않고 부족한 근거를 명시한다.</t>
+        </is>
+      </c>
+      <c r="E44" s="45" t="inlineStr">
+        <is>
+          <t>가시화 내부(로컬 LLM)→가시화</t>
+        </is>
+      </c>
+      <c r="F44" s="43" t="inlineStr">
+        <is>
+          <t>마일스톤 수락 시 1회(이벤트 기반)</t>
+        </is>
+      </c>
+      <c r="G44" s="45" t="inlineStr">
+        <is>
+          <t>마일스톤과 마찬가지로 사용자 수락에 종속되어 주기가 없다. DAG로 만드는 이유는 회의록 §4-3의 'flow → process — 여러 갈래가 다시 하나의 박스로 모이는 형태'를 표현해야 하기 때문이고, 일렬 인덱스로 두면 분기·합류가 사라져 실패 경로 역추적(VZ-D-05)이 성립하지 않는다.</t>
+        </is>
+      </c>
+      <c r="H44" s="45" t="inlineStr">
+        <is>
+          <t>AI, 백엔드 서버, 하드웨어</t>
+        </is>
+      </c>
+      <c r="I44" s="45" t="inlineStr">
+        <is>
+          <t>AI-C-09, BE-X-04  [구 AI-D-01 삭제분 인수]</t>
+        </is>
+      </c>
+      <c r="J44" s="43" t="inlineStr">
+        <is>
+          <t>김현우</t>
+        </is>
+      </c>
+    </row>
+    <row r="45" s="54">
+      <c r="A45" s="43" t="inlineStr">
+        <is>
+          <t>VZ-G-03</t>
+        </is>
+      </c>
+      <c r="B45" s="44" t="inlineStr">
+        <is>
+          <t>생성</t>
+        </is>
+      </c>
+      <c r="C45" s="45" t="inlineStr">
+        <is>
+          <t>태스크 검증</t>
+        </is>
+      </c>
+      <c r="D45" s="45" t="inlineStr">
+        <is>
+          <t>생성된 태스크를 실행 전에 검증한다. 구조, 순서, 의존 관계의 순환 여부, 사전조건, 자원 조건, 배정된 대상의 수행 가능성을 확인한다. 검증 기능은 생성 기능과 분리해 동일 입력에서 재현 가능한 결과를 제공한다. 확인할 수 없는 필수 조건이 있으면 해당 태스크만 실행 불가로 표시하고 부족한 근거를 명시한다. 검증 결과는 VZ-U-07의 승인 화면과 VZ-L-03의 2단 확인 ②단계 표시에 사용한다.</t>
+        </is>
+      </c>
+      <c r="E45" s="45" t="inlineStr">
+        <is>
+          <t>(내부 처리)</t>
+        </is>
+      </c>
+      <c r="F45" s="43" t="inlineStr">
+        <is>
+          <t>태스크 생성 직후 1회 + 배정 변경 시 재검증</t>
+        </is>
+      </c>
+      <c r="G45" s="45" t="inlineStr">
+        <is>
+          <t>검증은 생성 결과에 종속되므로 주기가 없다. 배정이 바뀌면 다시 검증하는 이유는 대상이 달라지면 수행 가능성 판정이 달라지기 때문이다(VZ-D-07). 생성과 같은 사람이 만들더라도 모듈은 분리한다 — 생성기가 스스로를 검증하면 같은 오해를 두 번 반복할 뿐이고, 재현 가능한 검증이라야 실패했을 때 생성 탓인지 검증 탓인지 가를 수 있다.</t>
+        </is>
+      </c>
+      <c r="H45" s="45" t="inlineStr">
+        <is>
+          <t>백엔드 서버, 하드웨어</t>
+        </is>
+      </c>
+      <c r="I45" s="45" t="inlineStr">
+        <is>
+          <t>BE-X-04, HW-A-05  [구 AI-D-02 삭제분 인수]</t>
+        </is>
+      </c>
+      <c r="J45" s="43" t="inlineStr">
+        <is>
+          <t>김현우</t>
+        </is>
+      </c>
+    </row>
+    <row r="46" s="54">
+      <c r="A46" s="43" t="inlineStr">
+        <is>
+          <t>VZ-G-04</t>
+        </is>
+      </c>
+      <c r="B46" s="44" t="inlineStr">
+        <is>
+          <t>생성</t>
+        </is>
+      </c>
+      <c r="C46" s="45" t="inlineStr">
+        <is>
+          <t>태스크 → 액션 아이템 전개</t>
+        </is>
+      </c>
+      <c r="D46" s="45" t="inlineStr">
+        <is>
+          <t>검증을 통과한 태스크를 배정된 대상의 어댑터 프로파일에 따라 실제 명령값을 갖는 액션 아이템으로 전개한다. 기종 의존 값과 그 해석 규칙은 어댑터 프로파일에만 두고 상위 계층과 화면 코드에 기종별 표를 두지 않는다(VZ-D-03). 같은 태스크가 다른 대상에 배정되면 상위 정의는 그대로 두고 전개 결과만 달라져야 한다. 전개 중 새 태스크가 필요해지면 파생 출처를 유지한 채 상위로 되돌린다.</t>
+        </is>
+      </c>
+      <c r="E46" s="45" t="inlineStr">
+        <is>
+          <t>(내부 처리) / 발행은 VZ-O-01</t>
+        </is>
+      </c>
+      <c r="F46" s="43" t="inlineStr">
+        <is>
+          <t>태스크 검증 통과 후 1회 + 배정 변경 시 재전개</t>
+        </is>
+      </c>
+      <c r="G46" s="45" t="inlineStr">
+        <is>
+          <t>전개는 검증 결과와 배정에 종속되어 주기가 없다. 실행 직전이 아니라 검증 직후에 전개하는 이유는, 전개 결과를 사용자가 승인 화면에서 미리 볼 수 있어야 하고(VZ-U-07) 전개 단계에서 드러나는 불가능(예: 대상이 지원하지 않는 동작)을 실행 전에 잡아야 하기 때문이다. 실제 디바이스 명령으로의 번역은 여전히 백엔드가 수행한다(VZ-O-01).</t>
+        </is>
+      </c>
+      <c r="H46" s="45" t="inlineStr">
+        <is>
+          <t>백엔드 서버, 하드웨어</t>
+        </is>
+      </c>
+      <c r="I46" s="45" t="inlineStr">
+        <is>
+          <t>HW-R-05, HW-A-02, BE-A-01, BE-A-02, AI-C-15</t>
+        </is>
+      </c>
+      <c r="J46" s="43" t="inlineStr">
+        <is>
+          <t>김현우</t>
+        </is>
+      </c>
+    </row>
+    <row r="47" s="54">
+      <c r="A47" s="43" t="inlineStr">
+        <is>
+          <t>VZ-G-05</t>
+        </is>
+      </c>
+      <c r="B47" s="44" t="inlineStr">
+        <is>
+          <t>생성</t>
+        </is>
+      </c>
+      <c r="C47" s="45" t="inlineStr">
+        <is>
+          <t>평가 기준 생성 및 판정</t>
+        </is>
+      </c>
+      <c r="D47" s="45" t="inlineStr">
+        <is>
+          <t>태스크마다 종료를 판정할 평가 기준을 생성하고, 실행 결과를 그 기준으로 판정한다. 태스크는 실행 완료가 아니라 평가 통과로만 종료되며 평가 전에는 별도 상태로 표시한다(VZ-D-06). 기준은 측정 가능한 항목과 임계로 표현하고, 판정에는 사용한 근거와 판정 주체를 함께 남긴다. 판정에 필요한 값이 도달하지 않으면 통과로 승격하지 않고 근거 부족을 드러낸다. 규칙으로 판정할 수 없는 항목은 사람 판정으로 넘긴다.</t>
+        </is>
+      </c>
+      <c r="E47" s="45" t="inlineStr">
+        <is>
+          <t>(내부 처리) / 판정 입력은 상태·명령 결과 수신</t>
+        </is>
+      </c>
+      <c r="F47" s="43" t="inlineStr">
+        <is>
+          <t>태스크 실행 종료 시 1회, 근거 미도달 시 대기</t>
+        </is>
+      </c>
+      <c r="G47" s="45" t="inlineStr">
+        <is>
+          <t>판정은 실행 종료 이벤트에 종속되어 주기가 없다. 근거가 도달하지 않았을 때 대기하는 이유는, 시간이 지났다는 이유로 통과시키면 '평가가 끝나야 태스크가 끝난다'는 회의 합의가 무의미해지기 때문이다. 판정 주체를 남기는 이유는 규칙 판정과 사람 판정이 섞일 때 사후에 둘을 갈라야 하기 때문이며, 이는 VZ-D-02의 산출 주체 기록과 같은 이유다.</t>
+        </is>
+      </c>
+      <c r="H47" s="45" t="inlineStr">
+        <is>
+          <t>AI, 백엔드 서버, 하드웨어</t>
+        </is>
+      </c>
+      <c r="I47" s="45" t="inlineStr">
+        <is>
+          <t>HW-A-04, HW-R-05, AI-S-03, BE-X-03  [구 AI-D-02 삭제분 인수]</t>
+        </is>
+      </c>
+      <c r="J47" s="43" t="inlineStr">
         <is>
           <t>김현우</t>
         </is>

--- a/피지컬팀 프로젝트 mk2 요구사항 정의서.xlsx
+++ b/피지컬팀 프로젝트 mk2 요구사항 정의서.xlsx
@@ -21370,7 +21370,7 @@
       </c>
       <c r="D35" s="45" t="inlineStr">
         <is>
-          <t>임무를 마일스톤 → 태스크 → 액션 아이템 3계층으로 받아 계층을 따라 내려가며 표시한다. 마일스톤은 도메인 무관 추상 단위이고, 태스크는 수행 가능 단위이며 deps로 분기·합류를 표현하는 DAG다. 액션 아이템만이 대상 기종에 의존한다. 태스크 종료는 평가(Evaluation) 통과로만 성립하며 평가 전 상태는 별도 상태로 표시한다. 액션 아이템 전개 중 파생된 태스크는 파생 출처를 유지한다. 이 계층의 생산 주체는 가시화다 — 마일스톤은 VZ-G-01, 태스크는 VZ-G-02, 액션 아이템은 VZ-G-04가 만들고 평가는 VZ-G-05가 판정한다. 다만 사전조건이 깨졌을 때의 재생성 판단(구 AI-D-04)은 인수 범위에서 제외했으므로, 실행 중 파생 태스크는 VZ-G-04의 되돌림 경로로만 생긴다 [확인 요망].</t>
+          <t>임무를 마일스톤 → 태스크 → 액션 아이템 3계층으로 받아 계층을 따라 내려가며 표시한다. 마일스톤은 도메인 무관 추상 단위이고, 태스크는 수행 가능 단위이며 deps로 분기·합류를 표현하는 DAG다. 액션 아이템만이 대상 기종에 의존한다. 태스크 종료는 평가(Evaluation) 통과로만 성립하며 평가 전 상태는 별도 상태로 표시한다. 액션 아이템 전개 중 파생된 태스크는 파생 출처를 유지한다. 이 계층의 생산 주체는 가시화다 — 마일스톤은 VZ-G-01, 태스크는 VZ-G-02, 액션 아이템은 VZ-G-04가 만들고 평가는 VZ-G-05가 판정한다. 실행 중 파생 태스크는 VZ-G-04의 되돌림 경로로 생긴다. 사전조건이 깨졌을 때 남은 계획을 다시 만드는 재생성 판단(구 AI-D-04)은 확장 기능으로 분류해 이번 범위에서 제외한다(E9) — 필수 동작이 아니고, 넣으면 실행 중 그래프 크기가 변해 탐색 공간 측정의 분모가 흔들린다.</t>
         </is>
       </c>
       <c r="E35" s="45" t="inlineStr">

--- a/피지컬팀 프로젝트 mk2 요구사항 정의서.xlsx
+++ b/피지컬팀 프로젝트 mk2 요구사항 정의서.xlsx
@@ -19577,6 +19577,8 @@
     <col width="22.25" customWidth="1" style="54" min="6" max="6"/>
     <col width="57.88" customWidth="1" style="54" min="7" max="7"/>
     <col width="34.25" customWidth="1" style="54" min="9" max="9"/>
+    <col width="26" customWidth="1" style="54" min="11" max="11"/>
+    <col width="52" customWidth="1" style="54" min="12" max="12"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -19630,8 +19632,16 @@
           <t>담당</t>
         </is>
       </c>
-      <c r="K1" s="5" t="n"/>
-      <c r="L1" s="5" t="n"/>
+      <c r="K1" s="2" t="inlineStr">
+        <is>
+          <t>적용 대상</t>
+        </is>
+      </c>
+      <c r="L1" s="2" t="inlineStr">
+        <is>
+          <t>범위 주석</t>
+        </is>
+      </c>
       <c r="M1" s="5" t="n"/>
       <c r="N1" s="5" t="n"/>
       <c r="O1" s="5" t="n"/>
@@ -19687,6 +19697,12 @@
           <t>김현우</t>
         </is>
       </c>
+      <c r="K2" s="22" t="inlineStr">
+        <is>
+          <t>viz-debugger</t>
+        </is>
+      </c>
+      <c r="L2" s="22" t="inlineStr"/>
     </row>
     <row r="3" ht="66.75" customHeight="1" s="54">
       <c r="A3" s="22" t="inlineStr">
@@ -19739,6 +19755,12 @@
           <t>김현우</t>
         </is>
       </c>
+      <c r="K3" s="22" t="inlineStr">
+        <is>
+          <t>viz-debugger</t>
+        </is>
+      </c>
+      <c r="L3" s="22" t="inlineStr"/>
     </row>
     <row r="4" ht="66.75" customHeight="1" s="54">
       <c r="A4" s="22" t="inlineStr">
@@ -19791,6 +19813,12 @@
           <t>김현우</t>
         </is>
       </c>
+      <c r="K4" s="22" t="inlineStr">
+        <is>
+          <t>viz-debugger</t>
+        </is>
+      </c>
+      <c r="L4" s="22" t="inlineStr"/>
     </row>
     <row r="5" ht="66.75" customHeight="1" s="54">
       <c r="A5" s="22" t="inlineStr">
@@ -19843,6 +19871,12 @@
           <t>김현우</t>
         </is>
       </c>
+      <c r="K5" s="22" t="inlineStr">
+        <is>
+          <t>web-dashboard(유지)</t>
+        </is>
+      </c>
+      <c r="L5" s="22" t="inlineStr"/>
     </row>
     <row r="6" ht="66.75" customHeight="1" s="54">
       <c r="A6" s="22" t="inlineStr">
@@ -19895,6 +19929,12 @@
           <t>김현우</t>
         </is>
       </c>
+      <c r="K6" s="22" t="inlineStr">
+        <is>
+          <t>web-dashboard(유지)</t>
+        </is>
+      </c>
+      <c r="L6" s="22" t="inlineStr"/>
     </row>
     <row r="7" ht="66.75" customHeight="1" s="54">
       <c r="A7" s="22" t="inlineStr">
@@ -19947,6 +19987,12 @@
           <t>김현우</t>
         </is>
       </c>
+      <c r="K7" s="22" t="inlineStr">
+        <is>
+          <t>web-dashboard(유지)</t>
+        </is>
+      </c>
+      <c r="L7" s="22" t="inlineStr"/>
     </row>
     <row r="8" ht="96.75" customHeight="1" s="54">
       <c r="A8" s="22" t="inlineStr">
@@ -19999,6 +20045,12 @@
           <t>김현우</t>
         </is>
       </c>
+      <c r="K8" s="22" t="inlineStr">
+        <is>
+          <t>web-dashboard(유지)</t>
+        </is>
+      </c>
+      <c r="L8" s="22" t="inlineStr"/>
     </row>
     <row r="9" ht="66.75" customHeight="1" s="54">
       <c r="A9" s="22" t="inlineStr">
@@ -20051,6 +20103,12 @@
           <t>김현우</t>
         </is>
       </c>
+      <c r="K9" s="22" t="inlineStr">
+        <is>
+          <t>web-dashboard(유지)</t>
+        </is>
+      </c>
+      <c r="L9" s="22" t="inlineStr"/>
     </row>
     <row r="10" ht="66.75" customHeight="1" s="54">
       <c r="A10" s="22" t="inlineStr">
@@ -20103,6 +20161,12 @@
           <t>김현우</t>
         </is>
       </c>
+      <c r="K10" s="22" t="inlineStr">
+        <is>
+          <t>web-dashboard(유지)</t>
+        </is>
+      </c>
+      <c r="L10" s="22" t="inlineStr"/>
     </row>
     <row r="11" ht="66.75" customHeight="1" s="54">
       <c r="A11" s="22" t="inlineStr">
@@ -20155,6 +20219,16 @@
           <t>김현우</t>
         </is>
       </c>
+      <c r="K11" s="22" t="inlineStr">
+        <is>
+          <t>web-dashboard(유지)</t>
+        </is>
+      </c>
+      <c r="L11" s="22" t="inlineStr">
+        <is>
+          <t>외부 AI의 실패를 받는 경로다. 생성을 우리가 하게 되어 자체 실패 표시가 별도로 필요하다(정의서 7.7).</t>
+        </is>
+      </c>
     </row>
     <row r="12" ht="66.75" customHeight="1" s="54">
       <c r="A12" s="22" t="inlineStr">
@@ -20207,6 +20281,12 @@
           <t>김현우</t>
         </is>
       </c>
+      <c r="K12" s="22" t="inlineStr">
+        <is>
+          <t>web-dashboard(유지)</t>
+        </is>
+      </c>
+      <c r="L12" s="22" t="inlineStr"/>
     </row>
     <row r="13" ht="66.75" customHeight="1" s="54">
       <c r="A13" s="22" t="inlineStr">
@@ -20259,6 +20339,12 @@
           <t>김현우</t>
         </is>
       </c>
+      <c r="K13" s="22" t="inlineStr">
+        <is>
+          <t>viz-debugger</t>
+        </is>
+      </c>
+      <c r="L13" s="22" t="inlineStr"/>
     </row>
     <row r="14" ht="66.75" customHeight="1" s="54">
       <c r="A14" s="22" t="inlineStr">
@@ -20311,6 +20397,12 @@
           <t>김현우</t>
         </is>
       </c>
+      <c r="K14" s="22" t="inlineStr">
+        <is>
+          <t>viz-debugger</t>
+        </is>
+      </c>
+      <c r="L14" s="22" t="inlineStr"/>
     </row>
     <row r="15" ht="66.75" customHeight="1" s="54">
       <c r="A15" s="22" t="inlineStr">
@@ -20363,6 +20455,12 @@
           <t>김현우</t>
         </is>
       </c>
+      <c r="K15" s="22" t="inlineStr">
+        <is>
+          <t>viz-debugger</t>
+        </is>
+      </c>
+      <c r="L15" s="22" t="inlineStr"/>
     </row>
     <row r="16" ht="66.75" customHeight="1" s="54">
       <c r="A16" s="22" t="inlineStr">
@@ -20415,6 +20513,16 @@
           <t>김현우</t>
         </is>
       </c>
+      <c r="K16" s="22" t="inlineStr">
+        <is>
+          <t>공통</t>
+        </is>
+      </c>
+      <c r="L16" s="22" t="inlineStr">
+        <is>
+          <t>viz-debugger에서는 계측 오버헤드 측정(논문 측정축 D)의 발행 경로이기도 하다.</t>
+        </is>
+      </c>
     </row>
     <row r="17" ht="66.75" customHeight="1" s="54">
       <c r="A17" s="22" t="inlineStr">
@@ -20467,6 +20575,12 @@
           <t>김현우</t>
         </is>
       </c>
+      <c r="K17" s="22" t="inlineStr">
+        <is>
+          <t>viz-debugger</t>
+        </is>
+      </c>
+      <c r="L17" s="22" t="inlineStr"/>
     </row>
     <row r="18" ht="83.25" customHeight="1" s="54">
       <c r="A18" s="22" t="inlineStr">
@@ -20519,6 +20633,12 @@
           <t>김현우</t>
         </is>
       </c>
+      <c r="K18" s="22" t="inlineStr">
+        <is>
+          <t>viz-debugger</t>
+        </is>
+      </c>
+      <c r="L18" s="22" t="inlineStr"/>
     </row>
     <row r="19" ht="66.75" customHeight="1" s="54">
       <c r="A19" s="22" t="inlineStr">
@@ -20571,6 +20691,12 @@
           <t>김현우</t>
         </is>
       </c>
+      <c r="K19" s="22" t="inlineStr">
+        <is>
+          <t>web-dashboard(유지)</t>
+        </is>
+      </c>
+      <c r="L19" s="22" t="inlineStr"/>
     </row>
     <row r="20" ht="66.75" customHeight="1" s="54">
       <c r="A20" s="22" t="inlineStr">
@@ -20623,6 +20749,12 @@
           <t>김현우</t>
         </is>
       </c>
+      <c r="K20" s="22" t="inlineStr">
+        <is>
+          <t>viz-debugger</t>
+        </is>
+      </c>
+      <c r="L20" s="22" t="inlineStr"/>
     </row>
     <row r="21" ht="66.75" customHeight="1" s="54">
       <c r="A21" s="22" t="inlineStr">
@@ -20675,6 +20807,12 @@
           <t>김현우</t>
         </is>
       </c>
+      <c r="K21" s="22" t="inlineStr">
+        <is>
+          <t>web-dashboard(유지)</t>
+        </is>
+      </c>
+      <c r="L21" s="22" t="inlineStr"/>
     </row>
     <row r="22" ht="66.75" customHeight="1" s="54">
       <c r="A22" s="22" t="inlineStr">
@@ -20727,6 +20865,16 @@
           <t>김현우</t>
         </is>
       </c>
+      <c r="K22" s="22" t="inlineStr">
+        <is>
+          <t>web-dashboard(VZ-D-01·06이 대체)</t>
+        </is>
+      </c>
+      <c r="L22" s="22" t="inlineStr">
+        <is>
+          <t>구 2계층(계획→구간) 판이다. viz-debugger에서는 3계층 표시(VZ-D-01)와 8상태(VZ-D-06)가 이 역할을 대신하므로 신규 구현 대상이 아니다.</t>
+        </is>
+      </c>
     </row>
     <row r="23" ht="66.75" customHeight="1" s="54">
       <c r="A23" s="22" t="inlineStr">
@@ -20779,6 +20927,12 @@
           <t>김현우</t>
         </is>
       </c>
+      <c r="K23" s="22" t="inlineStr">
+        <is>
+          <t>web-dashboard(유지)</t>
+        </is>
+      </c>
+      <c r="L23" s="22" t="inlineStr"/>
     </row>
     <row r="24" ht="66.75" customHeight="1" s="54">
       <c r="A24" s="22" t="inlineStr">
@@ -20831,6 +20985,16 @@
           <t>김현우</t>
         </is>
       </c>
+      <c r="K24" s="22" t="inlineStr">
+        <is>
+          <t>viz-debugger</t>
+        </is>
+      </c>
+      <c r="L24" s="22" t="inlineStr">
+        <is>
+          <t>승인 절차의 정본이다. viz-debugger에서는 VZ-G-01·02가 만든 결과를 승인하는 화면으로 계속 쓴다.</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="22" t="inlineStr">
@@ -20883,6 +21047,12 @@
           <t>김현우</t>
         </is>
       </c>
+      <c r="K25" s="22" t="inlineStr">
+        <is>
+          <t>viz-debugger</t>
+        </is>
+      </c>
+      <c r="L25" s="22" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" s="22" t="inlineStr">
@@ -20935,6 +21105,12 @@
           <t>김현우</t>
         </is>
       </c>
+      <c r="K26" s="22" t="inlineStr">
+        <is>
+          <t>viz-debugger</t>
+        </is>
+      </c>
+      <c r="L26" s="22" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" s="22" t="inlineStr">
@@ -20987,6 +21163,12 @@
           <t>김현우</t>
         </is>
       </c>
+      <c r="K27" s="22" t="inlineStr">
+        <is>
+          <t>viz-debugger</t>
+        </is>
+      </c>
+      <c r="L27" s="22" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="22" t="inlineStr">
@@ -21039,6 +21221,16 @@
           <t>김현우</t>
         </is>
       </c>
+      <c r="K28" s="22" t="inlineStr">
+        <is>
+          <t>web-dashboard(유지)</t>
+        </is>
+      </c>
+      <c r="L28" s="22" t="inlineStr">
+        <is>
+          <t>화면·파이프라인 구성 생성은 기존 프로토타입 기능이다. 다만 로컬 LLM 계층 자체는 VZ-G와 공유한다.</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="22" t="inlineStr">
@@ -21091,6 +21283,12 @@
           <t>김현우</t>
         </is>
       </c>
+      <c r="K29" s="22" t="inlineStr">
+        <is>
+          <t>공통</t>
+        </is>
+      </c>
+      <c r="L29" s="22" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" s="22" t="inlineStr">
@@ -21143,6 +21341,12 @@
           <t>김현우</t>
         </is>
       </c>
+      <c r="K30" s="22" t="inlineStr">
+        <is>
+          <t>공통</t>
+        </is>
+      </c>
+      <c r="L30" s="22" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" s="22" t="inlineStr">
@@ -21195,6 +21399,12 @@
           <t>김현우</t>
         </is>
       </c>
+      <c r="K31" s="22" t="inlineStr">
+        <is>
+          <t>공통</t>
+        </is>
+      </c>
+      <c r="L31" s="22" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" s="22" t="inlineStr">
@@ -21247,6 +21457,12 @@
           <t>김현우</t>
         </is>
       </c>
+      <c r="K32" s="22" t="inlineStr">
+        <is>
+          <t>공통</t>
+        </is>
+      </c>
+      <c r="L32" s="22" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" s="22" t="inlineStr">
@@ -21299,6 +21515,12 @@
           <t>김현우</t>
         </is>
       </c>
+      <c r="K33" s="22" t="inlineStr">
+        <is>
+          <t>공통</t>
+        </is>
+      </c>
+      <c r="L33" s="22" t="inlineStr"/>
     </row>
     <row r="34" s="54">
       <c r="A34" s="43" t="inlineStr">
@@ -21351,6 +21573,12 @@
           <t>김현우</t>
         </is>
       </c>
+      <c r="K34" s="22" t="inlineStr">
+        <is>
+          <t>공통</t>
+        </is>
+      </c>
+      <c r="L34" s="22" t="inlineStr"/>
     </row>
     <row r="35" s="54">
       <c r="A35" s="43" t="inlineStr">
@@ -21403,6 +21631,12 @@
           <t>김현우</t>
         </is>
       </c>
+      <c r="K35" s="22" t="inlineStr">
+        <is>
+          <t>viz-debugger</t>
+        </is>
+      </c>
+      <c r="L35" s="22" t="inlineStr"/>
     </row>
     <row r="36" s="54">
       <c r="A36" s="43" t="inlineStr">
@@ -21455,6 +21689,12 @@
           <t>김현우</t>
         </is>
       </c>
+      <c r="K36" s="22" t="inlineStr">
+        <is>
+          <t>viz-debugger</t>
+        </is>
+      </c>
+      <c r="L36" s="22" t="inlineStr"/>
     </row>
     <row r="37" s="54">
       <c r="A37" s="43" t="inlineStr">
@@ -21507,6 +21747,12 @@
           <t>김현우</t>
         </is>
       </c>
+      <c r="K37" s="22" t="inlineStr">
+        <is>
+          <t>viz-debugger</t>
+        </is>
+      </c>
+      <c r="L37" s="22" t="inlineStr"/>
     </row>
     <row r="38" s="54">
       <c r="A38" s="43" t="inlineStr">
@@ -21559,6 +21805,12 @@
           <t>김현우</t>
         </is>
       </c>
+      <c r="K38" s="22" t="inlineStr">
+        <is>
+          <t>viz-debugger</t>
+        </is>
+      </c>
+      <c r="L38" s="22" t="inlineStr"/>
     </row>
     <row r="39" s="54">
       <c r="A39" s="43" t="inlineStr">
@@ -21611,6 +21863,12 @@
           <t>김현우</t>
         </is>
       </c>
+      <c r="K39" s="22" t="inlineStr">
+        <is>
+          <t>viz-debugger</t>
+        </is>
+      </c>
+      <c r="L39" s="22" t="inlineStr"/>
     </row>
     <row r="40" s="54">
       <c r="A40" s="43" t="inlineStr">
@@ -21663,6 +21921,12 @@
           <t>김현우</t>
         </is>
       </c>
+      <c r="K40" s="22" t="inlineStr">
+        <is>
+          <t>viz-debugger</t>
+        </is>
+      </c>
+      <c r="L40" s="22" t="inlineStr"/>
     </row>
     <row r="41" s="54">
       <c r="A41" s="43" t="inlineStr">
@@ -21715,6 +21979,12 @@
           <t>김현우</t>
         </is>
       </c>
+      <c r="K41" s="22" t="inlineStr">
+        <is>
+          <t>viz-debugger</t>
+        </is>
+      </c>
+      <c r="L41" s="22" t="inlineStr"/>
     </row>
     <row r="42" s="54">
       <c r="A42" s="43" t="inlineStr">
@@ -21767,6 +22037,12 @@
           <t>김현우</t>
         </is>
       </c>
+      <c r="K42" s="22" t="inlineStr">
+        <is>
+          <t>viz-debugger</t>
+        </is>
+      </c>
+      <c r="L42" s="22" t="inlineStr"/>
     </row>
     <row r="43" s="54">
       <c r="A43" s="43" t="inlineStr">
@@ -21819,6 +22095,12 @@
           <t>김현우</t>
         </is>
       </c>
+      <c r="K43" s="22" t="inlineStr">
+        <is>
+          <t>viz-debugger</t>
+        </is>
+      </c>
+      <c r="L43" s="22" t="inlineStr"/>
     </row>
     <row r="44" s="54">
       <c r="A44" s="43" t="inlineStr">
@@ -21871,6 +22153,12 @@
           <t>김현우</t>
         </is>
       </c>
+      <c r="K44" s="22" t="inlineStr">
+        <is>
+          <t>viz-debugger</t>
+        </is>
+      </c>
+      <c r="L44" s="22" t="inlineStr"/>
     </row>
     <row r="45" s="54">
       <c r="A45" s="43" t="inlineStr">
@@ -21923,6 +22211,12 @@
           <t>김현우</t>
         </is>
       </c>
+      <c r="K45" s="22" t="inlineStr">
+        <is>
+          <t>viz-debugger</t>
+        </is>
+      </c>
+      <c r="L45" s="22" t="inlineStr"/>
     </row>
     <row r="46" s="54">
       <c r="A46" s="43" t="inlineStr">
@@ -21975,6 +22269,12 @@
           <t>김현우</t>
         </is>
       </c>
+      <c r="K46" s="22" t="inlineStr">
+        <is>
+          <t>viz-debugger</t>
+        </is>
+      </c>
+      <c r="L46" s="22" t="inlineStr"/>
     </row>
     <row r="47" s="54">
       <c r="A47" s="43" t="inlineStr">
@@ -22027,6 +22327,12 @@
           <t>김현우</t>
         </is>
       </c>
+      <c r="K47" s="22" t="inlineStr">
+        <is>
+          <t>viz-debugger</t>
+        </is>
+      </c>
+      <c r="L47" s="22" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/피지컬팀 프로젝트 mk2 요구사항 정의서.xlsx
+++ b/피지컬팀 프로젝트 mk2 요구사항 정의서.xlsx
@@ -19634,7 +19634,7 @@
       </c>
       <c r="K1" s="2" t="inlineStr">
         <is>
-          <t>적용 대상</t>
+          <t>통합 앱 배치</t>
         </is>
       </c>
       <c r="L1" s="2" t="inlineStr">
@@ -19699,7 +19699,7 @@
       </c>
       <c r="K2" s="22" t="inlineStr">
         <is>
-          <t>viz-debugger</t>
+          <t>공유 계층 · 전송·구독</t>
         </is>
       </c>
       <c r="L2" s="22" t="inlineStr"/>
@@ -19757,7 +19757,7 @@
       </c>
       <c r="K3" s="22" t="inlineStr">
         <is>
-          <t>viz-debugger</t>
+          <t>공유 계층 · 전송·구독</t>
         </is>
       </c>
       <c r="L3" s="22" t="inlineStr"/>
@@ -19815,10 +19815,14 @@
       </c>
       <c r="K4" s="22" t="inlineStr">
         <is>
-          <t>viz-debugger</t>
-        </is>
-      </c>
-      <c r="L4" s="22" t="inlineStr"/>
+          <t>공유 계층 · 레지스트리</t>
+        </is>
+      </c>
+      <c r="L4" s="22" t="inlineStr">
+        <is>
+          <t>탭①의 장치 카드와 탭⑥의 배정 풀이 같은 원천을 쓴다.</t>
+        </is>
+      </c>
     </row>
     <row r="5" ht="66.75" customHeight="1" s="54">
       <c r="A5" s="22" t="inlineStr">
@@ -19873,7 +19877,7 @@
       </c>
       <c r="K5" s="22" t="inlineStr">
         <is>
-          <t>web-dashboard(유지)</t>
+          <t>탭③ 지표 조회</t>
         </is>
       </c>
       <c r="L5" s="22" t="inlineStr"/>
@@ -19931,7 +19935,7 @@
       </c>
       <c r="K6" s="22" t="inlineStr">
         <is>
-          <t>web-dashboard(유지)</t>
+          <t>탭② 제어 패널</t>
         </is>
       </c>
       <c r="L6" s="22" t="inlineStr"/>
@@ -19989,7 +19993,7 @@
       </c>
       <c r="K7" s="22" t="inlineStr">
         <is>
-          <t>web-dashboard(유지)</t>
+          <t>탭④ 영상 오버레이</t>
         </is>
       </c>
       <c r="L7" s="22" t="inlineStr"/>
@@ -20047,7 +20051,7 @@
       </c>
       <c r="K8" s="22" t="inlineStr">
         <is>
-          <t>web-dashboard(유지)</t>
+          <t>탭④ 영상 오버레이</t>
         </is>
       </c>
       <c r="L8" s="22" t="inlineStr"/>
@@ -20105,10 +20109,14 @@
       </c>
       <c r="K9" s="22" t="inlineStr">
         <is>
-          <t>web-dashboard(유지)</t>
-        </is>
-      </c>
-      <c r="L9" s="22" t="inlineStr"/>
+          <t>탭① 구역 현황판</t>
+        </is>
+      </c>
+      <c r="L9" s="22" t="inlineStr">
+        <is>
+          <t>환경 위험도 판정이다. 탭⑥은 태스크 실행 상태만 다루므로 대체하지 못한다. 구 판단·알림 탭 해체분.</t>
+        </is>
+      </c>
     </row>
     <row r="10" ht="66.75" customHeight="1" s="54">
       <c r="A10" s="22" t="inlineStr">
@@ -20163,7 +20171,7 @@
       </c>
       <c r="K10" s="22" t="inlineStr">
         <is>
-          <t>web-dashboard(유지)</t>
+          <t>탭④ 영상 오버레이</t>
         </is>
       </c>
       <c r="L10" s="22" t="inlineStr"/>
@@ -20221,12 +20229,12 @@
       </c>
       <c r="K11" s="22" t="inlineStr">
         <is>
-          <t>web-dashboard(유지)</t>
+          <t>공유 계층 · 상단 알림</t>
         </is>
       </c>
       <c r="L11" s="22" t="inlineStr">
         <is>
-          <t>외부 AI의 실패를 받는 경로다. 생성을 우리가 하게 되어 자체 실패 표시가 별도로 필요하다(정의서 7.7).</t>
+          <t>외부 AI 실패에 더해 탭⑥의 생성 실패(VZ-G)도 여기로 올린다. 구 판단·알림 탭 해체분.</t>
         </is>
       </c>
     </row>
@@ -20283,7 +20291,7 @@
       </c>
       <c r="K12" s="22" t="inlineStr">
         <is>
-          <t>web-dashboard(유지)</t>
+          <t>공유 계층 · 전송·구독</t>
         </is>
       </c>
       <c r="L12" s="22" t="inlineStr"/>
@@ -20341,10 +20349,14 @@
       </c>
       <c r="K13" s="22" t="inlineStr">
         <is>
-          <t>viz-debugger</t>
-        </is>
-      </c>
-      <c r="L13" s="22" t="inlineStr"/>
+          <t>공유 계층 · 명령 발행·추적</t>
+        </is>
+      </c>
+      <c r="L13" s="22" t="inlineStr">
+        <is>
+          <t>명령 출구는 하나여야 한다. 탭②의 수동 제어와 탭⑥의 재실행이 같은 경로를 쓴다 — 갈라지면 트레이스가 나뉜다.</t>
+        </is>
+      </c>
     </row>
     <row r="14" ht="66.75" customHeight="1" s="54">
       <c r="A14" s="22" t="inlineStr">
@@ -20399,7 +20411,7 @@
       </c>
       <c r="K14" s="22" t="inlineStr">
         <is>
-          <t>viz-debugger</t>
+          <t>공유 계층 · 명령 발행·추적</t>
         </is>
       </c>
       <c r="L14" s="22" t="inlineStr"/>
@@ -20457,7 +20469,7 @@
       </c>
       <c r="K15" s="22" t="inlineStr">
         <is>
-          <t>viz-debugger</t>
+          <t>공유 계층 · 명령 발행·추적</t>
         </is>
       </c>
       <c r="L15" s="22" t="inlineStr"/>
@@ -20515,12 +20527,12 @@
       </c>
       <c r="K16" s="22" t="inlineStr">
         <is>
-          <t>공통</t>
+          <t>공유 계층 · 자체 관측</t>
         </is>
       </c>
       <c r="L16" s="22" t="inlineStr">
         <is>
-          <t>viz-debugger에서는 계측 오버헤드 측정(논문 측정축 D)의 발행 경로이기도 하다.</t>
+          <t>탭⑥ 단독 빌드에서 계측 오버헤드(논문 측정축 D)를 잰다.</t>
         </is>
       </c>
     </row>
@@ -20577,7 +20589,7 @@
       </c>
       <c r="K17" s="22" t="inlineStr">
         <is>
-          <t>viz-debugger</t>
+          <t>공유 계층 · 명령 발행·추적</t>
         </is>
       </c>
       <c r="L17" s="22" t="inlineStr"/>
@@ -20635,10 +20647,14 @@
       </c>
       <c r="K18" s="22" t="inlineStr">
         <is>
-          <t>viz-debugger</t>
-        </is>
-      </c>
-      <c r="L18" s="22" t="inlineStr"/>
+          <t>탭① 구역 현황판</t>
+        </is>
+      </c>
+      <c r="L18" s="22" t="inlineStr">
+        <is>
+          <t>장치 상태 4종이다. 탭⑥의 태스크 상태 8종(VZ-D-06)과 다른 것이므로 코드·화면에서 어휘를 분리한다.</t>
+        </is>
+      </c>
     </row>
     <row r="19" ht="66.75" customHeight="1" s="54">
       <c r="A19" s="22" t="inlineStr">
@@ -20693,7 +20709,7 @@
       </c>
       <c r="K19" s="22" t="inlineStr">
         <is>
-          <t>web-dashboard(유지)</t>
+          <t>Unity 트윈 뷰어(별도 앱)</t>
         </is>
       </c>
       <c r="L19" s="22" t="inlineStr"/>
@@ -20751,10 +20767,14 @@
       </c>
       <c r="K20" s="22" t="inlineStr">
         <is>
-          <t>viz-debugger</t>
-        </is>
-      </c>
-      <c r="L20" s="22" t="inlineStr"/>
+          <t>탭⑥ viz-debugger</t>
+        </is>
+      </c>
+      <c r="L20" s="22" t="inlineStr">
+        <is>
+          <t>구 판단·알림 탭에서 탭⑥으로 흡수. 사용자 계층별 표시 깊이 전환.</t>
+        </is>
+      </c>
     </row>
     <row r="21" ht="66.75" customHeight="1" s="54">
       <c r="A21" s="22" t="inlineStr">
@@ -20809,10 +20829,14 @@
       </c>
       <c r="K21" s="22" t="inlineStr">
         <is>
-          <t>web-dashboard(유지)</t>
-        </is>
-      </c>
-      <c r="L21" s="22" t="inlineStr"/>
+          <t>탭⑤ 파이프라인 편집기(동결)</t>
+        </is>
+      </c>
+      <c r="L21" s="22" t="inlineStr">
+        <is>
+          <t>구 노드 그래프 탭의 데이터 파이프라인 모드. 동결·시연용 — 신규 개발도 논문 반영도 하지 않는다.</t>
+        </is>
+      </c>
     </row>
     <row r="22" ht="66.75" customHeight="1" s="54">
       <c r="A22" s="22" t="inlineStr">
@@ -20867,12 +20891,12 @@
       </c>
       <c r="K22" s="22" t="inlineStr">
         <is>
-          <t>web-dashboard(VZ-D-01·06이 대체)</t>
+          <t>탭⑥이 대체</t>
         </is>
       </c>
       <c r="L22" s="22" t="inlineStr">
         <is>
-          <t>구 2계층(계획→구간) 판이다. viz-debugger에서는 3계층 표시(VZ-D-01)와 8상태(VZ-D-06)가 이 역할을 대신하므로 신규 구현 대상이 아니다.</t>
+          <t>구 2계층 판. 탭⑥의 VZ-D-01(3계층)·VZ-D-06(8상태)이 대신한다.</t>
         </is>
       </c>
     </row>
@@ -20929,10 +20953,14 @@
       </c>
       <c r="K23" s="22" t="inlineStr">
         <is>
-          <t>web-dashboard(유지)</t>
-        </is>
-      </c>
-      <c r="L23" s="22" t="inlineStr"/>
+          <t>보류(미구현)</t>
+        </is>
+      </c>
+      <c r="L23" s="22" t="inlineStr">
+        <is>
+          <t>탭 매핑에 없던 미구현분. AI-L 삭제로 범위도 축소됐다. 필요하면 탭④에 붙인다.</t>
+        </is>
+      </c>
     </row>
     <row r="24" ht="66.75" customHeight="1" s="54">
       <c r="A24" s="22" t="inlineStr">
@@ -20987,12 +21015,12 @@
       </c>
       <c r="K24" s="22" t="inlineStr">
         <is>
-          <t>viz-debugger</t>
+          <t>탭⑥ viz-debugger</t>
         </is>
       </c>
       <c r="L24" s="22" t="inlineStr">
         <is>
-          <t>승인 절차의 정본이다. viz-debugger에서는 VZ-G-01·02가 만든 결과를 승인하는 화면으로 계속 쓴다.</t>
+          <t>구 임무 승인·진행 탭에서 탭⑥으로 통폐합. 승인·거부 버튼으로 들어간다.</t>
         </is>
       </c>
     </row>
@@ -21049,7 +21077,7 @@
       </c>
       <c r="K25" s="22" t="inlineStr">
         <is>
-          <t>viz-debugger</t>
+          <t>탭⑥ viz-debugger</t>
         </is>
       </c>
       <c r="L25" s="22" t="inlineStr"/>
@@ -21107,7 +21135,7 @@
       </c>
       <c r="K26" s="22" t="inlineStr">
         <is>
-          <t>viz-debugger</t>
+          <t>탭⑥ viz-debugger</t>
         </is>
       </c>
       <c r="L26" s="22" t="inlineStr"/>
@@ -21165,7 +21193,7 @@
       </c>
       <c r="K27" s="22" t="inlineStr">
         <is>
-          <t>viz-debugger</t>
+          <t>탭⑥ viz-debugger</t>
         </is>
       </c>
       <c r="L27" s="22" t="inlineStr"/>
@@ -21223,12 +21251,12 @@
       </c>
       <c r="K28" s="22" t="inlineStr">
         <is>
-          <t>web-dashboard(유지)</t>
+          <t>탭⑤ 파이프라인 편집기(동결)</t>
         </is>
       </c>
       <c r="L28" s="22" t="inlineStr">
         <is>
-          <t>화면·파이프라인 구성 생성은 기존 프로토타입 기능이다. 다만 로컬 LLM 계층 자체는 VZ-G와 공유한다.</t>
+          <t>화면·파이프라인 구성 생성이라 탭⑤에 속한다. 로컬 LLM 계층 자체는 VZ-G와 공유한다.</t>
         </is>
       </c>
     </row>
@@ -21285,7 +21313,7 @@
       </c>
       <c r="K29" s="22" t="inlineStr">
         <is>
-          <t>공통</t>
+          <t>공유 계층 · 권한</t>
         </is>
       </c>
       <c r="L29" s="22" t="inlineStr"/>
@@ -21343,7 +21371,7 @@
       </c>
       <c r="K30" s="22" t="inlineStr">
         <is>
-          <t>공통</t>
+          <t>공유 계층 · 기동</t>
         </is>
       </c>
       <c r="L30" s="22" t="inlineStr"/>
@@ -21401,7 +21429,7 @@
       </c>
       <c r="K31" s="22" t="inlineStr">
         <is>
-          <t>공통</t>
+          <t>공유 계층 · 표기 규약</t>
         </is>
       </c>
       <c r="L31" s="22" t="inlineStr"/>
@@ -21459,7 +21487,7 @@
       </c>
       <c r="K32" s="22" t="inlineStr">
         <is>
-          <t>공통</t>
+          <t>공유 계층 · 권한</t>
         </is>
       </c>
       <c r="L32" s="22" t="inlineStr"/>
@@ -21517,7 +21545,7 @@
       </c>
       <c r="K33" s="22" t="inlineStr">
         <is>
-          <t>공통</t>
+          <t>공유 계층 · 기동</t>
         </is>
       </c>
       <c r="L33" s="22" t="inlineStr"/>
@@ -21575,7 +21603,7 @@
       </c>
       <c r="K34" s="22" t="inlineStr">
         <is>
-          <t>공통</t>
+          <t>공유 계층 · 표기 규약</t>
         </is>
       </c>
       <c r="L34" s="22" t="inlineStr"/>
@@ -21633,7 +21661,7 @@
       </c>
       <c r="K35" s="22" t="inlineStr">
         <is>
-          <t>viz-debugger</t>
+          <t>탭⑥ viz-debugger</t>
         </is>
       </c>
       <c r="L35" s="22" t="inlineStr"/>
@@ -21691,7 +21719,7 @@
       </c>
       <c r="K36" s="22" t="inlineStr">
         <is>
-          <t>viz-debugger</t>
+          <t>탭⑥ viz-debugger</t>
         </is>
       </c>
       <c r="L36" s="22" t="inlineStr"/>
@@ -21749,7 +21777,7 @@
       </c>
       <c r="K37" s="22" t="inlineStr">
         <is>
-          <t>viz-debugger</t>
+          <t>탭⑥ viz-debugger</t>
         </is>
       </c>
       <c r="L37" s="22" t="inlineStr"/>
@@ -21807,7 +21835,7 @@
       </c>
       <c r="K38" s="22" t="inlineStr">
         <is>
-          <t>viz-debugger</t>
+          <t>탭⑥ viz-debugger</t>
         </is>
       </c>
       <c r="L38" s="22" t="inlineStr"/>
@@ -21865,7 +21893,7 @@
       </c>
       <c r="K39" s="22" t="inlineStr">
         <is>
-          <t>viz-debugger</t>
+          <t>탭⑥ viz-debugger</t>
         </is>
       </c>
       <c r="L39" s="22" t="inlineStr"/>
@@ -21923,7 +21951,7 @@
       </c>
       <c r="K40" s="22" t="inlineStr">
         <is>
-          <t>viz-debugger</t>
+          <t>탭⑥ viz-debugger</t>
         </is>
       </c>
       <c r="L40" s="22" t="inlineStr"/>
@@ -21981,7 +22009,7 @@
       </c>
       <c r="K41" s="22" t="inlineStr">
         <is>
-          <t>viz-debugger</t>
+          <t>탭⑥ viz-debugger</t>
         </is>
       </c>
       <c r="L41" s="22" t="inlineStr"/>
@@ -22039,7 +22067,7 @@
       </c>
       <c r="K42" s="22" t="inlineStr">
         <is>
-          <t>viz-debugger</t>
+          <t>탭⑥ viz-debugger</t>
         </is>
       </c>
       <c r="L42" s="22" t="inlineStr"/>
@@ -22097,7 +22125,7 @@
       </c>
       <c r="K43" s="22" t="inlineStr">
         <is>
-          <t>viz-debugger</t>
+          <t>탭⑥ viz-debugger</t>
         </is>
       </c>
       <c r="L43" s="22" t="inlineStr"/>
@@ -22155,7 +22183,7 @@
       </c>
       <c r="K44" s="22" t="inlineStr">
         <is>
-          <t>viz-debugger</t>
+          <t>탭⑥ viz-debugger</t>
         </is>
       </c>
       <c r="L44" s="22" t="inlineStr"/>
@@ -22213,7 +22241,7 @@
       </c>
       <c r="K45" s="22" t="inlineStr">
         <is>
-          <t>viz-debugger</t>
+          <t>탭⑥ viz-debugger</t>
         </is>
       </c>
       <c r="L45" s="22" t="inlineStr"/>
@@ -22271,7 +22299,7 @@
       </c>
       <c r="K46" s="22" t="inlineStr">
         <is>
-          <t>viz-debugger</t>
+          <t>탭⑥ viz-debugger</t>
         </is>
       </c>
       <c r="L46" s="22" t="inlineStr"/>
@@ -22329,7 +22357,7 @@
       </c>
       <c r="K47" s="22" t="inlineStr">
         <is>
-          <t>viz-debugger</t>
+          <t>탭⑥ viz-debugger</t>
         </is>
       </c>
       <c r="L47" s="22" t="inlineStr"/>

--- a/피지컬팀 프로젝트 mk2 요구사항 정의서.xlsx
+++ b/피지컬팀 프로젝트 mk2 요구사항 정의서.xlsx
@@ -20767,7 +20767,7 @@
       </c>
       <c r="K20" s="22" t="inlineStr">
         <is>
-          <t>탭⑥ viz-debugger</t>
+          <t>탭⑥ 임무 설계 및 디버깅</t>
         </is>
       </c>
       <c r="L20" s="22" t="inlineStr">
@@ -21015,7 +21015,7 @@
       </c>
       <c r="K24" s="22" t="inlineStr">
         <is>
-          <t>탭⑥ viz-debugger</t>
+          <t>탭⑥ 임무 설계 및 디버깅</t>
         </is>
       </c>
       <c r="L24" s="22" t="inlineStr">
@@ -21077,7 +21077,7 @@
       </c>
       <c r="K25" s="22" t="inlineStr">
         <is>
-          <t>탭⑥ viz-debugger</t>
+          <t>탭⑥ 임무 설계 및 디버깅</t>
         </is>
       </c>
       <c r="L25" s="22" t="inlineStr"/>
@@ -21135,7 +21135,7 @@
       </c>
       <c r="K26" s="22" t="inlineStr">
         <is>
-          <t>탭⑥ viz-debugger</t>
+          <t>탭⑥ 임무 설계 및 디버깅</t>
         </is>
       </c>
       <c r="L26" s="22" t="inlineStr"/>
@@ -21193,7 +21193,7 @@
       </c>
       <c r="K27" s="22" t="inlineStr">
         <is>
-          <t>탭⑥ viz-debugger</t>
+          <t>탭⑥ 임무 설계 및 디버깅</t>
         </is>
       </c>
       <c r="L27" s="22" t="inlineStr"/>
@@ -21661,7 +21661,7 @@
       </c>
       <c r="K35" s="22" t="inlineStr">
         <is>
-          <t>탭⑥ viz-debugger</t>
+          <t>탭⑥ 임무 설계 및 디버깅</t>
         </is>
       </c>
       <c r="L35" s="22" t="inlineStr"/>
@@ -21719,7 +21719,7 @@
       </c>
       <c r="K36" s="22" t="inlineStr">
         <is>
-          <t>탭⑥ viz-debugger</t>
+          <t>탭⑥ 임무 설계 및 디버깅</t>
         </is>
       </c>
       <c r="L36" s="22" t="inlineStr"/>
@@ -21777,7 +21777,7 @@
       </c>
       <c r="K37" s="22" t="inlineStr">
         <is>
-          <t>탭⑥ viz-debugger</t>
+          <t>탭⑥ 임무 설계 및 디버깅</t>
         </is>
       </c>
       <c r="L37" s="22" t="inlineStr"/>
@@ -21835,7 +21835,7 @@
       </c>
       <c r="K38" s="22" t="inlineStr">
         <is>
-          <t>탭⑥ viz-debugger</t>
+          <t>탭⑥ 임무 설계 및 디버깅</t>
         </is>
       </c>
       <c r="L38" s="22" t="inlineStr"/>
@@ -21893,7 +21893,7 @@
       </c>
       <c r="K39" s="22" t="inlineStr">
         <is>
-          <t>탭⑥ viz-debugger</t>
+          <t>탭⑥ 임무 설계 및 디버깅</t>
         </is>
       </c>
       <c r="L39" s="22" t="inlineStr"/>
@@ -21951,7 +21951,7 @@
       </c>
       <c r="K40" s="22" t="inlineStr">
         <is>
-          <t>탭⑥ viz-debugger</t>
+          <t>탭⑥ 임무 설계 및 디버깅</t>
         </is>
       </c>
       <c r="L40" s="22" t="inlineStr"/>
@@ -22009,7 +22009,7 @@
       </c>
       <c r="K41" s="22" t="inlineStr">
         <is>
-          <t>탭⑥ viz-debugger</t>
+          <t>탭⑥ 임무 설계 및 디버깅</t>
         </is>
       </c>
       <c r="L41" s="22" t="inlineStr"/>
@@ -22067,7 +22067,7 @@
       </c>
       <c r="K42" s="22" t="inlineStr">
         <is>
-          <t>탭⑥ viz-debugger</t>
+          <t>탭⑥ 임무 설계 및 디버깅</t>
         </is>
       </c>
       <c r="L42" s="22" t="inlineStr"/>
@@ -22125,7 +22125,7 @@
       </c>
       <c r="K43" s="22" t="inlineStr">
         <is>
-          <t>탭⑥ viz-debugger</t>
+          <t>탭⑥ 임무 설계 및 디버깅</t>
         </is>
       </c>
       <c r="L43" s="22" t="inlineStr"/>
@@ -22183,7 +22183,7 @@
       </c>
       <c r="K44" s="22" t="inlineStr">
         <is>
-          <t>탭⑥ viz-debugger</t>
+          <t>탭⑥ 임무 설계 및 디버깅</t>
         </is>
       </c>
       <c r="L44" s="22" t="inlineStr"/>
@@ -22241,7 +22241,7 @@
       </c>
       <c r="K45" s="22" t="inlineStr">
         <is>
-          <t>탭⑥ viz-debugger</t>
+          <t>탭⑥ 임무 설계 및 디버깅</t>
         </is>
       </c>
       <c r="L45" s="22" t="inlineStr"/>
@@ -22299,7 +22299,7 @@
       </c>
       <c r="K46" s="22" t="inlineStr">
         <is>
-          <t>탭⑥ viz-debugger</t>
+          <t>탭⑥ 임무 설계 및 디버깅</t>
         </is>
       </c>
       <c r="L46" s="22" t="inlineStr"/>
@@ -22357,7 +22357,7 @@
       </c>
       <c r="K47" s="22" t="inlineStr">
         <is>
-          <t>탭⑥ viz-debugger</t>
+          <t>탭⑥ 임무 설계 및 디버깅</t>
         </is>
       </c>
       <c r="L47" s="22" t="inlineStr"/>

--- a/피지컬팀 프로젝트 mk2 요구사항 정의서.xlsx
+++ b/피지컬팀 프로젝트 mk2 요구사항 정의서.xlsx
@@ -19820,7 +19820,7 @@
       </c>
       <c r="L4" s="22" t="inlineStr">
         <is>
-          <t>탭①의 장치 카드와 탭⑥의 배정 풀이 같은 원천을 쓴다.</t>
+          <t>탭②의 장치 카드와 탭①의 배정 풀이 같은 원천을 쓴다.</t>
         </is>
       </c>
     </row>
@@ -19877,7 +19877,7 @@
       </c>
       <c r="K5" s="22" t="inlineStr">
         <is>
-          <t>탭③ 지표 조회</t>
+          <t>탭④ 지표 조회</t>
         </is>
       </c>
       <c r="L5" s="22" t="inlineStr"/>
@@ -19935,7 +19935,7 @@
       </c>
       <c r="K6" s="22" t="inlineStr">
         <is>
-          <t>탭② 제어 패널</t>
+          <t>탭③ 제어 패널</t>
         </is>
       </c>
       <c r="L6" s="22" t="inlineStr"/>
@@ -19993,7 +19993,7 @@
       </c>
       <c r="K7" s="22" t="inlineStr">
         <is>
-          <t>탭④ 영상 오버레이</t>
+          <t>탭⑤ 영상 오버레이</t>
         </is>
       </c>
       <c r="L7" s="22" t="inlineStr"/>
@@ -20051,7 +20051,7 @@
       </c>
       <c r="K8" s="22" t="inlineStr">
         <is>
-          <t>탭④ 영상 오버레이</t>
+          <t>탭⑤ 영상 오버레이</t>
         </is>
       </c>
       <c r="L8" s="22" t="inlineStr"/>
@@ -20109,12 +20109,12 @@
       </c>
       <c r="K9" s="22" t="inlineStr">
         <is>
-          <t>탭① 구역 현황판</t>
+          <t>탭② 구역 현황판</t>
         </is>
       </c>
       <c r="L9" s="22" t="inlineStr">
         <is>
-          <t>환경 위험도 판정이다. 탭⑥은 태스크 실행 상태만 다루므로 대체하지 못한다. 구 판단·알림 탭 해체분.</t>
+          <t>환경 위험도 판정이다. 탭①은 태스크 실행 상태만 다루므로 대체하지 못한다. 구 판단·알림 탭 해체분.</t>
         </is>
       </c>
     </row>
@@ -20171,7 +20171,7 @@
       </c>
       <c r="K10" s="22" t="inlineStr">
         <is>
-          <t>탭④ 영상 오버레이</t>
+          <t>탭⑤ 영상 오버레이</t>
         </is>
       </c>
       <c r="L10" s="22" t="inlineStr"/>
@@ -20234,7 +20234,7 @@
       </c>
       <c r="L11" s="22" t="inlineStr">
         <is>
-          <t>외부 AI 실패에 더해 탭⑥의 생성 실패(VZ-G)도 여기로 올린다. 구 판단·알림 탭 해체분.</t>
+          <t>외부 AI 실패에 더해 탭①의 생성 실패(VZ-G)도 여기로 올린다. 구 판단·알림 탭 해체분.</t>
         </is>
       </c>
     </row>
@@ -20354,7 +20354,7 @@
       </c>
       <c r="L13" s="22" t="inlineStr">
         <is>
-          <t>명령 출구는 하나여야 한다. 탭②의 수동 제어와 탭⑥의 재실행이 같은 경로를 쓴다 — 갈라지면 트레이스가 나뉜다.</t>
+          <t>명령 출구는 하나여야 한다. 탭③의 수동 제어와 탭①의 재실행이 같은 경로를 쓴다 — 갈라지면 트레이스가 나뉜다.</t>
         </is>
       </c>
     </row>
@@ -20532,7 +20532,7 @@
       </c>
       <c r="L16" s="22" t="inlineStr">
         <is>
-          <t>탭⑥ 단독 빌드에서 계측 오버헤드(논문 측정축 D)를 잰다.</t>
+          <t>탭① 단독 빌드에서 계측 오버헤드(논문 측정축 D)를 잰다.</t>
         </is>
       </c>
     </row>
@@ -20647,12 +20647,12 @@
       </c>
       <c r="K18" s="22" t="inlineStr">
         <is>
-          <t>탭① 구역 현황판</t>
+          <t>탭② 구역 현황판</t>
         </is>
       </c>
       <c r="L18" s="22" t="inlineStr">
         <is>
-          <t>장치 상태 4종이다. 탭⑥의 태스크 상태 8종(VZ-D-06)과 다른 것이므로 코드·화면에서 어휘를 분리한다.</t>
+          <t>장치 상태 4종이다. 탭①의 태스크 상태 8종(VZ-D-06)과 다른 것이므로 코드·화면에서 어휘를 분리한다.</t>
         </is>
       </c>
     </row>
@@ -20767,12 +20767,12 @@
       </c>
       <c r="K20" s="22" t="inlineStr">
         <is>
-          <t>탭⑥ 임무 설계 및 디버깅</t>
+          <t>탭① 임무 설계 및 디버깅</t>
         </is>
       </c>
       <c r="L20" s="22" t="inlineStr">
         <is>
-          <t>구 판단·알림 탭에서 탭⑥으로 흡수. 사용자 계층별 표시 깊이 전환.</t>
+          <t>구 판단·알림 탭에서 탭①으로 흡수. 사용자 계층별 표시 깊이 전환.</t>
         </is>
       </c>
     </row>
@@ -20829,7 +20829,7 @@
       </c>
       <c r="K21" s="22" t="inlineStr">
         <is>
-          <t>탭⑤ 파이프라인 편집기(동결)</t>
+          <t>탭⑥ 파이프라인 편집기(동결)</t>
         </is>
       </c>
       <c r="L21" s="22" t="inlineStr">
@@ -20891,12 +20891,12 @@
       </c>
       <c r="K22" s="22" t="inlineStr">
         <is>
-          <t>탭⑥이 대체</t>
+          <t>탭①이 대체</t>
         </is>
       </c>
       <c r="L22" s="22" t="inlineStr">
         <is>
-          <t>구 2계층 판. 탭⑥의 VZ-D-01(3계층)·VZ-D-06(8상태)이 대신한다.</t>
+          <t>구 2계층 판. 탭①의 VZ-D-01(3계층)·VZ-D-06(8상태)이 대신한다.</t>
         </is>
       </c>
     </row>
@@ -20958,7 +20958,7 @@
       </c>
       <c r="L23" s="22" t="inlineStr">
         <is>
-          <t>탭 매핑에 없던 미구현분. AI-L 삭제로 범위도 축소됐다. 필요하면 탭④에 붙인다.</t>
+          <t>탭 매핑에 없던 미구현분. AI-L 삭제로 범위도 축소됐다. 필요하면 탭⑤에 붙인다.</t>
         </is>
       </c>
     </row>
@@ -21015,12 +21015,12 @@
       </c>
       <c r="K24" s="22" t="inlineStr">
         <is>
-          <t>탭⑥ 임무 설계 및 디버깅</t>
+          <t>탭① 임무 설계 및 디버깅</t>
         </is>
       </c>
       <c r="L24" s="22" t="inlineStr">
         <is>
-          <t>구 임무 승인·진행 탭에서 탭⑥으로 통폐합. 승인·거부 버튼으로 들어간다.</t>
+          <t>구 임무 승인·진행 탭에서 탭①으로 통폐합. 승인·거부 버튼으로 들어간다.</t>
         </is>
       </c>
     </row>
@@ -21077,7 +21077,7 @@
       </c>
       <c r="K25" s="22" t="inlineStr">
         <is>
-          <t>탭⑥ 임무 설계 및 디버깅</t>
+          <t>탭① 임무 설계 및 디버깅</t>
         </is>
       </c>
       <c r="L25" s="22" t="inlineStr"/>
@@ -21135,7 +21135,7 @@
       </c>
       <c r="K26" s="22" t="inlineStr">
         <is>
-          <t>탭⑥ 임무 설계 및 디버깅</t>
+          <t>탭① 임무 설계 및 디버깅</t>
         </is>
       </c>
       <c r="L26" s="22" t="inlineStr"/>
@@ -21193,7 +21193,7 @@
       </c>
       <c r="K27" s="22" t="inlineStr">
         <is>
-          <t>탭⑥ 임무 설계 및 디버깅</t>
+          <t>탭① 임무 설계 및 디버깅</t>
         </is>
       </c>
       <c r="L27" s="22" t="inlineStr"/>
@@ -21251,12 +21251,12 @@
       </c>
       <c r="K28" s="22" t="inlineStr">
         <is>
-          <t>탭⑤ 파이프라인 편집기(동결)</t>
+          <t>탭⑥ 파이프라인 편집기(동결)</t>
         </is>
       </c>
       <c r="L28" s="22" t="inlineStr">
         <is>
-          <t>화면·파이프라인 구성 생성이라 탭⑤에 속한다. 로컬 LLM 계층 자체는 VZ-G와 공유한다.</t>
+          <t>화면·파이프라인 구성 생성이라 탭⑥에 속한다. 로컬 LLM 계층 자체는 VZ-G와 공유한다.</t>
         </is>
       </c>
     </row>
@@ -21661,7 +21661,7 @@
       </c>
       <c r="K35" s="22" t="inlineStr">
         <is>
-          <t>탭⑥ 임무 설계 및 디버깅</t>
+          <t>탭① 임무 설계 및 디버깅</t>
         </is>
       </c>
       <c r="L35" s="22" t="inlineStr"/>
@@ -21719,7 +21719,7 @@
       </c>
       <c r="K36" s="22" t="inlineStr">
         <is>
-          <t>탭⑥ 임무 설계 및 디버깅</t>
+          <t>탭① 임무 설계 및 디버깅</t>
         </is>
       </c>
       <c r="L36" s="22" t="inlineStr"/>
@@ -21777,7 +21777,7 @@
       </c>
       <c r="K37" s="22" t="inlineStr">
         <is>
-          <t>탭⑥ 임무 설계 및 디버깅</t>
+          <t>탭① 임무 설계 및 디버깅</t>
         </is>
       </c>
       <c r="L37" s="22" t="inlineStr"/>
@@ -21835,7 +21835,7 @@
       </c>
       <c r="K38" s="22" t="inlineStr">
         <is>
-          <t>탭⑥ 임무 설계 및 디버깅</t>
+          <t>탭① 임무 설계 및 디버깅</t>
         </is>
       </c>
       <c r="L38" s="22" t="inlineStr"/>
@@ -21893,7 +21893,7 @@
       </c>
       <c r="K39" s="22" t="inlineStr">
         <is>
-          <t>탭⑥ 임무 설계 및 디버깅</t>
+          <t>탭① 임무 설계 및 디버깅</t>
         </is>
       </c>
       <c r="L39" s="22" t="inlineStr"/>
@@ -21951,7 +21951,7 @@
       </c>
       <c r="K40" s="22" t="inlineStr">
         <is>
-          <t>탭⑥ 임무 설계 및 디버깅</t>
+          <t>탭① 임무 설계 및 디버깅</t>
         </is>
       </c>
       <c r="L40" s="22" t="inlineStr"/>
@@ -22009,7 +22009,7 @@
       </c>
       <c r="K41" s="22" t="inlineStr">
         <is>
-          <t>탭⑥ 임무 설계 및 디버깅</t>
+          <t>탭① 임무 설계 및 디버깅</t>
         </is>
       </c>
       <c r="L41" s="22" t="inlineStr"/>
@@ -22067,7 +22067,7 @@
       </c>
       <c r="K42" s="22" t="inlineStr">
         <is>
-          <t>탭⑥ 임무 설계 및 디버깅</t>
+          <t>탭① 임무 설계 및 디버깅</t>
         </is>
       </c>
       <c r="L42" s="22" t="inlineStr"/>
@@ -22125,7 +22125,7 @@
       </c>
       <c r="K43" s="22" t="inlineStr">
         <is>
-          <t>탭⑥ 임무 설계 및 디버깅</t>
+          <t>탭① 임무 설계 및 디버깅</t>
         </is>
       </c>
       <c r="L43" s="22" t="inlineStr"/>
@@ -22183,7 +22183,7 @@
       </c>
       <c r="K44" s="22" t="inlineStr">
         <is>
-          <t>탭⑥ 임무 설계 및 디버깅</t>
+          <t>탭① 임무 설계 및 디버깅</t>
         </is>
       </c>
       <c r="L44" s="22" t="inlineStr"/>
@@ -22241,7 +22241,7 @@
       </c>
       <c r="K45" s="22" t="inlineStr">
         <is>
-          <t>탭⑥ 임무 설계 및 디버깅</t>
+          <t>탭① 임무 설계 및 디버깅</t>
         </is>
       </c>
       <c r="L45" s="22" t="inlineStr"/>
@@ -22299,7 +22299,7 @@
       </c>
       <c r="K46" s="22" t="inlineStr">
         <is>
-          <t>탭⑥ 임무 설계 및 디버깅</t>
+          <t>탭① 임무 설계 및 디버깅</t>
         </is>
       </c>
       <c r="L46" s="22" t="inlineStr"/>
@@ -22357,7 +22357,7 @@
       </c>
       <c r="K47" s="22" t="inlineStr">
         <is>
-          <t>탭⑥ 임무 설계 및 디버깅</t>
+          <t>탭① 임무 설계 및 디버깅</t>
         </is>
       </c>
       <c r="L47" s="22" t="inlineStr"/>

--- a/피지컬팀 프로젝트 mk2 요구사항 정의서.xlsx
+++ b/피지컬팀 프로젝트 mk2 요구사항 정의서.xlsx
@@ -1,12 +1,12 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="조병현" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="이대규" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="진나영" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="김현우" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="조병현" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="이대규" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="진나영" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="김현우" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -20321,7 +20321,7 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O47"/>
+  <dimension ref="A1:O46"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="12.63" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
     <col width="43.38" customWidth="1" style="54" min="4" max="4"/>
@@ -21529,7 +21529,7 @@
     <row r="21" ht="66.75" customHeight="1" s="54">
       <c r="A21" s="27" t="inlineStr">
         <is>
-          <t>VZ-U-04</t>
+          <t>VZ-U-05</t>
         </is>
       </c>
       <c r="B21" s="33" t="inlineStr">
@@ -21539,37 +21539,37 @@
       </c>
       <c r="C21" s="28" t="inlineStr">
         <is>
-          <t>노드 편집기 구성 반영</t>
+          <t>서브태스크 진행 상태 표시</t>
         </is>
       </c>
       <c r="D21" s="28" t="inlineStr">
         <is>
-          <t>파이프라인·화면 구성을 노드 그래프로 편집하고, 시험 실행으로 검증한 뒤 명시적 '반영' 조작으로만 운영 상태에 적용한다. 반영 행위는 제어 명령급 감사 대상으로 보되, 실제 이벤트 발행은 노드 편집기 구현 시점으로 미룬다(자리만 확보).</t>
+          <t>승인된 계획이 구간 단위로 어디까지 수행됐고 어느 단계에서 실패했는지를 노드 형태로 표시해 추적·디버깅할 수 있게 한다. 여러 구역에 걸친 계획은 구역별 구간과 순서를 함께 보여준다. 구간 정보는 가시화가 생성한 태스크(VZ-G-02)와 그 실행 기록(VZ-D-02)에서 파생된다.</t>
         </is>
       </c>
       <c r="E21" s="28" t="inlineStr">
         <is>
-          <t>(내부 처리) / 반영 이벤트: 가시화→백엔드</t>
+          <t>백엔드→가시화(WS)</t>
         </is>
       </c>
       <c r="F21" s="27" t="inlineStr">
         <is>
-          <t>사용자 '반영' 조작 시(이벤트 기반)</t>
+          <t>구간 상태 변화 시(이벤트 기반)</t>
         </is>
       </c>
       <c r="G21" s="28" t="inlineStr">
         <is>
-          <t>편집 중 자동 반영은 미완성 그래프가 운영 화면으로 나가는 사고를 만든다. 명시적 반영만 허용하면 되돌리기와 감사 양쪽에 유리하고, 시험 실행으로 사전 검증까지 가능해 선정.</t>
+          <t>구간 상태는 하달·시작·완료·실패 시점에만 바뀌므로 주기 폴링은 낭비다. 수행 시작·완료·실패 보고가 로봇 상태 데이터(HW-R-03)에 실려 오므로 그 변화 시점에 갱신하면 충분해 이벤트 기반으로 선정.</t>
         </is>
       </c>
       <c r="H21" s="28" t="inlineStr">
         <is>
-          <t>백엔드 서버</t>
+          <t>AI, 백엔드 서버, 하드웨어</t>
         </is>
       </c>
       <c r="I21" s="28" t="inlineStr">
         <is>
-          <t>HW-C-02, BE-C-01</t>
+          <t>HW-R-05, HW-R-03, BE-X-04 ← VZ-G-02, VZ-D-02</t>
         </is>
       </c>
       <c r="J21" s="27" t="inlineStr">
@@ -21579,19 +21579,19 @@
       </c>
       <c r="K21" s="27" t="inlineStr">
         <is>
-          <t>탭⑥ 파이프라인 편집기(동결)</t>
+          <t>탭①이 대체</t>
         </is>
       </c>
       <c r="L21" s="27" t="inlineStr">
         <is>
-          <t>구 노드 그래프 탭의 데이터 파이프라인 모드. 동결·시연용 — 신규 개발도 논문 반영도 하지 않는다.</t>
+          <t>구 2계층 판. 탭①의 VZ-D-01(3계층)·VZ-D-06(8상태)이 대신한다.</t>
         </is>
       </c>
     </row>
     <row r="22" ht="66.75" customHeight="1" s="54">
       <c r="A22" s="27" t="inlineStr">
         <is>
-          <t>VZ-U-05</t>
+          <t>VZ-U-06</t>
         </is>
       </c>
       <c r="B22" s="33" t="inlineStr">
@@ -21601,37 +21601,37 @@
       </c>
       <c r="C22" s="28" t="inlineStr">
         <is>
-          <t>서브태스크 진행 상태 표시</t>
+          <t>미확인 탐지 그룹 확인</t>
         </is>
       </c>
       <c r="D22" s="28" t="inlineStr">
         <is>
-          <t>승인된 계획이 구간 단위로 어디까지 수행됐고 어느 단계에서 실패했는지를 노드 형태로 표시해 추적·디버깅할 수 있게 한다. 여러 구역에 걸친 계획은 구역별 구간과 순서를 함께 보여준다. 구간 정보는 가시화가 생성한 태스크(VZ-G-02)와 그 실행 기록(VZ-D-02)에서 파생된다.</t>
+          <t>AI가 기존 분류로 확정하지 못한 미확인 객체 후보를 전달하면 이를 화면에 표시하고 사용자가 명칭을 확인·입력해 회신한다. 확인된 명칭은 AI-S-04의 분류 상태 갱신 근거가 되며, 사람 확인 없이는 분류가 확정되지 않는다. [변경 2026-08-31] 신판 엑셀에서 AI-L-01·02·03이 부활했다. 그룹 단위 전달(군집화·대표선정)과 학습 반영 연계가 다시 성립할 수 있으므로, 구판 전제를 축소했던 직전 [변경](개별 단위 확인·분류 갱신 한정)을 되돌릴지 회의에서 정한다. 정하기 전까지는 개별 단위 확인 기준을 유지한다.</t>
         </is>
       </c>
       <c r="E22" s="28" t="inlineStr">
         <is>
-          <t>백엔드→가시화(WS)</t>
+          <t>AI→가시화 / 가시화→AI(확인된 명칭)</t>
         </is>
       </c>
       <c r="F22" s="27" t="inlineStr">
         <is>
-          <t>구간 상태 변화 시(이벤트 기반)</t>
+          <t>미확인 그룹 도착 시(이벤트 기반), 사용자 확인 시 회신</t>
         </is>
       </c>
       <c r="G22" s="28" t="inlineStr">
         <is>
-          <t>구간 상태는 하달·시작·완료·실패 시점에만 바뀌므로 주기 폴링은 낭비다. 수행 시작·완료·실패 보고가 로봇 상태 데이터(HW-R-03)에 실려 오므로 그 변화 시점에 갱신하면 충분해 이벤트 기반으로 선정.</t>
+          <t>탐지 건마다 확인을 요청하면 사용자 부담이 커, AI가 유사 후보를 묶어 보내는 방식과 짝을 이룬다. 가시화도 같은 단위로 묶어 표시해야 확인 절차가 한 번에 끝나므로 그룹 단위 이벤트로 선정.</t>
         </is>
       </c>
       <c r="H22" s="28" t="inlineStr">
         <is>
-          <t>AI, 백엔드 서버, 하드웨어</t>
+          <t>AI, 백엔드 서버</t>
         </is>
       </c>
       <c r="I22" s="28" t="inlineStr">
         <is>
-          <t>HW-R-05, HW-R-03, BE-X-04 ← VZ-G-02, VZ-D-02</t>
+          <t>AI-S-04, AI-L-01, AI-L-02, AI-L-03 [신판에서 AI-L 부활 — 보류 근거 재검토]</t>
         </is>
       </c>
       <c r="J22" s="27" t="inlineStr">
@@ -21641,19 +21641,19 @@
       </c>
       <c r="K22" s="27" t="inlineStr">
         <is>
-          <t>탭①이 대체</t>
+          <t>보류(미구현) — 근거 재검토(2026-08-31)</t>
         </is>
       </c>
       <c r="L22" s="27" t="inlineStr">
         <is>
-          <t>구 2계층 판. 탭①의 VZ-D-01(3계층)·VZ-D-06(8상태)이 대신한다.</t>
+          <t>탭 매핑에 없던 미구현분. 신판 엑셀에서 AI-L이 부활해 '상대 없음'이던 보류 근거가 사라졌다 — 구현 여부·시기는 회의 재판단. 구현한다면 탭⑤에 붙인다. AI-L-03 경로에 '가시화 사용자 확인'이 명시돼 있다.</t>
         </is>
       </c>
     </row>
     <row r="23" ht="66.75" customHeight="1" s="54">
       <c r="A23" s="27" t="inlineStr">
         <is>
-          <t>VZ-U-06</t>
+          <t>VZ-U-07</t>
         </is>
       </c>
       <c r="B23" s="33" t="inlineStr">
@@ -21663,27 +21663,27 @@
       </c>
       <c r="C23" s="28" t="inlineStr">
         <is>
-          <t>미확인 탐지 그룹 확인</t>
+          <t>계획 승인 및 근거 표시</t>
         </is>
       </c>
       <c r="D23" s="28" t="inlineStr">
         <is>
-          <t>AI가 기존 분류로 확정하지 못한 미확인 객체 후보를 전달하면 이를 화면에 표시하고 사용자가 명칭을 확인·입력해 회신한다. 확인된 명칭은 AI-S-04의 분류 상태 갱신 근거가 되며, 사람 확인 없이는 분류가 확정되지 않는다. [변경] 구판은 AI가 유사도로 묶은 '그룹' 단위 전달을 전제했으나 군집화·대표선정(AI-L-02)이 삭제되어 후보 '개별' 단위 확인으로 바꾼다. 학습 반영(AI-L-01·03)도 삭제되어 확인 결과는 학습 후보가 아니라 분류 상태 갱신 근거로만 쓰인다.</t>
+          <t>실행 계획과 그 근거(발화 → 마일스톤 → 태스크 → 검증 결과, 생성기 버전, 입력 텍스트 버전)를 화면에 펼쳐 보이고, 사용자가 승인하거나 거부할 수 있게 한다. 승인 전에는 계획이 실행되지 않으며, 승인된 계획만 백엔드를 거쳐 엣지·로봇으로 발행된다. 계획 생성·검증 주체가 AI에서 가시화로 바뀌었으므로(VZ-G-01~03) 화면은 자신이 만든 결과를 스스로 승인 요청하는 구조가 된다 — 따라서 생성 근거와 검증 결과를 감추지 않고 그대로 펼치는 것이 이전보다 더 중요하다.</t>
         </is>
       </c>
       <c r="E23" s="28" t="inlineStr">
         <is>
-          <t>AI→가시화 / 가시화→AI(확인된 명칭)</t>
+          <t>백엔드→가시화→(승인)→백엔드→엣지·로봇</t>
         </is>
       </c>
       <c r="F23" s="27" t="inlineStr">
         <is>
-          <t>미확인 그룹 도착 시(이벤트 기반), 사용자 확인 시 회신</t>
+          <t>계획 검증 완료 시(이벤트 기반), 승인은 사용자 조작 시</t>
         </is>
       </c>
       <c r="G23" s="28" t="inlineStr">
         <is>
-          <t>탐지 건마다 확인을 요청하면 사용자 부담이 커, AI가 유사 후보를 묶어 보내는 방식과 짝을 이룬다. 가시화도 같은 단위로 묶어 표시해야 확인 절차가 한 번에 끝나므로 그룹 단위 이벤트로 선정.</t>
+          <t>계획 생성·검증은 임무 발생 시에만 일어나므로 주기가 없다. 승인 절차를 화면에 두는 이유는 생성 결과가 검증을 통과했더라도 사람이 실행 여부를 결정해야 하기 때문이며, 승인 없이 자동 실행하면 책임소재가 성립하지 않아 필수 절차로 선정. 계획 생성·검증은 AI가, 승인 왕복의 중계는 백엔드가 담당한다.</t>
         </is>
       </c>
       <c r="H23" s="28" t="inlineStr">
@@ -21693,7 +21693,7 @@
       </c>
       <c r="I23" s="28" t="inlineStr">
         <is>
-          <t>AI-S-04 [군집화·학습 상대 없음 — AI-L-01·02 삭제]</t>
+          <t>BE-X-04 ← VZ-G-01·02·03</t>
         </is>
       </c>
       <c r="J23" s="27" t="inlineStr">
@@ -21703,74 +21703,74 @@
       </c>
       <c r="K23" s="27" t="inlineStr">
         <is>
-          <t>보류(미구현)</t>
+          <t>탭① 임무 설계 및 디버깅</t>
         </is>
       </c>
       <c r="L23" s="27" t="inlineStr">
         <is>
-          <t>탭 매핑에 없던 미구현분. AI-L 삭제로 범위도 축소됐다. 필요하면 탭⑤에 붙인다.</t>
+          <t>구 임무 승인·진행 탭에서 탭①으로 통폐합. 승인·거부 버튼으로 들어간다.</t>
         </is>
       </c>
     </row>
     <row r="24" ht="66.75" customHeight="1" s="54">
-      <c r="A24" s="27" t="inlineStr">
-        <is>
-          <t>VZ-U-07</t>
-        </is>
-      </c>
-      <c r="B24" s="33" t="inlineStr">
+      <c r="A24" s="0" t="inlineStr">
+        <is>
+          <t>VZ-U-08</t>
+        </is>
+      </c>
+      <c r="B24" s="0" t="inlineStr">
         <is>
           <t>화면</t>
         </is>
       </c>
-      <c r="C24" s="28" t="inlineStr">
-        <is>
-          <t>계획 승인 및 근거 표시</t>
-        </is>
-      </c>
-      <c r="D24" s="28" t="inlineStr">
-        <is>
-          <t>실행 계획과 그 근거(발화 → 마일스톤 → 태스크 → 검증 결과, 생성기 버전, 입력 텍스트 버전)를 화면에 펼쳐 보이고, 사용자가 승인하거나 거부할 수 있게 한다. 승인 전에는 계획이 실행되지 않으며, 승인된 계획만 백엔드를 거쳐 엣지·로봇으로 발행된다. 계획 생성·검증 주체가 AI에서 가시화로 바뀌었으므로(VZ-G-01~03) 화면은 자신이 만든 결과를 스스로 승인 요청하는 구조가 된다 — 따라서 생성 근거와 검증 결과를 감추지 않고 그대로 펼치는 것이 이전보다 더 중요하다.</t>
-        </is>
-      </c>
-      <c r="E24" s="28" t="inlineStr">
-        <is>
-          <t>백엔드→가시화→(승인)→백엔드→엣지·로봇</t>
-        </is>
-      </c>
-      <c r="F24" s="27" t="inlineStr">
-        <is>
-          <t>계획 검증 완료 시(이벤트 기반), 승인은 사용자 조작 시</t>
-        </is>
-      </c>
-      <c r="G24" s="28" t="inlineStr">
-        <is>
-          <t>계획 생성·검증은 임무 발생 시에만 일어나므로 주기가 없다. 승인 절차를 화면에 두는 이유는 생성 결과가 검증을 통과했더라도 사람이 실행 여부를 결정해야 하기 때문이며, 승인 없이 자동 실행하면 책임소재가 성립하지 않아 필수 절차로 선정. 계획 생성·검증은 AI가, 승인 왕복의 중계는 백엔드가 담당한다.</t>
-        </is>
-      </c>
-      <c r="H24" s="28" t="inlineStr">
+      <c r="C24" s="0" t="inlineStr">
+        <is>
+          <t>학습 결과 적용 승인(관리자 판단 정보)</t>
+        </is>
+      </c>
+      <c r="D24" s="0" t="inlineStr">
+        <is>
+          <t>시스템은 AI 학습 결과(모델·판단 정책·환경 지식 후보)의 운영 적용 전에 관리자 판단 정보(학습 발생 이유, 사용 데이터의 출처·확인 상태, 신규·기존 성능 변화, 자원·지연 변화, 알려진 실패 사례, 검증된 적용 범위, 복구 가능한 이전 정상 버전)를 표시하고 관리자의 승인·거부를 백엔드로 회신할 수 있어야 한다. 임무 계획 승인(VZ-U-07)과 별개 화면이다 — 승인 대상이 임무가 아니라 모델·정책·지식이다. [신설 2026-08-31] AI-L-06 전달 경로가 '가시화 승인 UI'를 명시해 대응 항목을 만들었다.</t>
+        </is>
+      </c>
+      <c r="E24" s="0" t="inlineStr">
+        <is>
+          <t>AI→백엔드→가시화(판단 정보) / 가시화→백엔드(승인 결과)</t>
+        </is>
+      </c>
+      <c r="F24" s="0" t="inlineStr">
+        <is>
+          <t>승인 요청 도착 시(이벤트 기반)</t>
+        </is>
+      </c>
+      <c r="G24" s="0" t="inlineStr">
+        <is>
+          <t>학습 결과의 운영 적용은 드문 사건이라 주기가 없다. 요청 도착 시 상단 알림으로 표시한다.</t>
+        </is>
+      </c>
+      <c r="H24" s="0" t="inlineStr">
         <is>
           <t>AI, 백엔드 서버</t>
         </is>
       </c>
-      <c r="I24" s="28" t="inlineStr">
-        <is>
-          <t>BE-X-04 ← VZ-G-01·02·03</t>
-        </is>
-      </c>
-      <c r="J24" s="27" t="inlineStr">
+      <c r="I24" s="0" t="inlineStr">
+        <is>
+          <t>AI-L-06, AI-L-07</t>
+        </is>
+      </c>
+      <c r="J24" s="0" t="inlineStr">
         <is>
           <t>김현우</t>
         </is>
       </c>
-      <c r="K24" s="27" t="inlineStr">
-        <is>
-          <t>탭① 임무 설계 및 디버깅</t>
-        </is>
-      </c>
-      <c r="L24" s="27" t="inlineStr">
-        <is>
-          <t>구 임무 승인·진행 탭에서 탭①으로 통폐합. 승인·거부 버튼으로 들어간다.</t>
+      <c r="K24" s="0" t="inlineStr">
+        <is>
+          <t>미정 — 신설(2026-08-31), 배치·구현 시기 회의 확정</t>
+        </is>
+      </c>
+      <c r="L24" s="0" t="inlineStr">
+        <is>
+          <t>승인 정보의 계약(구조·필드)을 AI 파트와 합의하기 전에는 구현하지 않는다.</t>
         </is>
       </c>
     </row>
@@ -21951,47 +21951,47 @@
     <row r="28">
       <c r="A28" s="27" t="inlineStr">
         <is>
-          <t>VZ-L-04</t>
-        </is>
-      </c>
-      <c r="B28" s="38" t="inlineStr">
-        <is>
-          <t>LLM·음성</t>
+          <t>VZ-C-01</t>
+        </is>
+      </c>
+      <c r="B28" s="41" t="inlineStr">
+        <is>
+          <t>공통</t>
         </is>
       </c>
       <c r="C28" s="28" t="inlineStr">
         <is>
-          <t>화면 구성 보조 LLM(가시화 내부)</t>
+          <t>권한(RBAC)과 역할 확인</t>
         </is>
       </c>
       <c r="D28" s="28" t="inlineStr">
         <is>
-          <t>가시화 내부의 로컬 LLM은 화면·파이프라인 구성 생성(노드 그래프), 데이터 요약·자연어 레이블링에 한정해 사용한다. 결과는 제안 상태로 표시하고 사용자가 수락해야 반영되며, 생성물은 측정된 사실과 구별해 표시한다. 임무 생성 계열(VZ-G-01~05)은 같은 로컬 LLM 계층을 쓰되 이 요구사항과 별개의 기능으로 분리해 관리한다 — 화면 구성 보조와 임무 생성은 실패했을 때의 영향 범위가 다르므로 한 기능으로 묶지 않는다.</t>
+          <t>열람/조작/관리 역할에 따라 화면에서 제어 UI를 사전 차단한다. 화면 차단은 사용자 편의이고 실제 강제는 백엔드가 수행하므로, 가시화는 현재 역할 조회로 역할을 확인해 표시·차단까지만 담당한다.</t>
         </is>
       </c>
       <c r="E28" s="28" t="inlineStr">
         <is>
-          <t>가시화→로컬 LLM(별도 프로세스)→가시화</t>
+          <t>백엔드 역할 조회 API→가시화</t>
         </is>
       </c>
       <c r="F28" s="27" t="inlineStr">
         <is>
-          <t>사용자 요청 시 1회(이벤트 기반), 응답은 스트리밍 표시</t>
+          <t>로그인 시 1회 + 토큰 갱신 시</t>
         </is>
       </c>
       <c r="G28" s="28" t="inlineStr">
         <is>
-          <t>LLM 호출은 비용·지연이 커 주기 실행 대상이 아니다. 응답을 전부 받은 뒤 한 번에 띄우면 체감 지연이 커지므로 생성되는 대로 스트리밍 표시하는 방식이 사용성에서 유리해 선정.</t>
+          <t>역할은 세션 중 거의 바뀌지 않아 주기 조회는 낭비다. 실제 방어선이 백엔드에 있어 화면이 최신 역할을 조금 늦게 알아도 보안 위험이 없으므로, 로그인·갱신 시점 조회로 충분해 선정.</t>
         </is>
       </c>
       <c r="H28" s="28" t="inlineStr">
         <is>
-          <t>AI</t>
-        </is>
-      </c>
-      <c r="I28" s="25" t="inlineStr">
-        <is>
-          <t>AI-C-09, AI-C-05</t>
+          <t>백엔드 서버</t>
+        </is>
+      </c>
+      <c r="I28" s="28" t="inlineStr">
+        <is>
+          <t>BE-Q-04</t>
         </is>
       </c>
       <c r="J28" s="27" t="inlineStr">
@@ -22001,19 +22001,15 @@
       </c>
       <c r="K28" s="27" t="inlineStr">
         <is>
-          <t>탭⑥ 파이프라인 편집기(동결)</t>
-        </is>
-      </c>
-      <c r="L28" s="27" t="inlineStr">
-        <is>
-          <t>화면·파이프라인 구성 생성이라 탭⑥에 속한다. 로컬 LLM 계층 자체는 VZ-G와 공유한다.</t>
-        </is>
-      </c>
+          <t>공유 계층 · 권한</t>
+        </is>
+      </c>
+      <c r="L28" s="27" t="n"/>
     </row>
     <row r="29">
       <c r="A29" s="27" t="inlineStr">
         <is>
-          <t>VZ-C-01</t>
+          <t>VZ-C-02</t>
         </is>
       </c>
       <c r="B29" s="41" t="inlineStr">
@@ -22023,37 +22019,37 @@
       </c>
       <c r="C29" s="28" t="inlineStr">
         <is>
-          <t>권한(RBAC)과 역할 확인</t>
+          <t>외부 소스 부재 시 동작</t>
         </is>
       </c>
       <c r="D29" s="28" t="inlineStr">
         <is>
-          <t>열람/조작/관리 역할에 따라 화면에서 제어 UI를 사전 차단한다. 화면 차단은 사용자 편의이고 실제 강제는 백엔드가 수행하므로, 가시화는 현재 역할 조회로 역할을 확인해 표시·차단까지만 담당한다.</t>
+          <t>레지스트리·상태 소스·AI·LLM이 연결되지 않은 상태에서도 정적 구성 파일로 컴포넌트 목록을 구성해 동작해야 한다. LLM이 미연결·무응답일 때는 관련 기능만 비활성화하고 나머지는 정상 동작한다. 임무 생성(VZ-G-01·02)이 로컬 LLM에 의존하게 되었으므로 이 요구사항은 개발 편의가 아니라 운용 요구사항이다 — LLM이 없으면 생성만 멈추고 기존 임무의 실행·관측·디버깅은 계속되어야 하며, 수동 입력 경로를 남긴다.</t>
         </is>
       </c>
       <c r="E29" s="28" t="inlineStr">
         <is>
-          <t>백엔드 역할 조회 API→가시화</t>
+          <t>(내부 처리)</t>
         </is>
       </c>
       <c r="F29" s="27" t="inlineStr">
         <is>
-          <t>로그인 시 1회 + 토큰 갱신 시</t>
+          <t>해당 없음(기동 시 1회 로드)</t>
         </is>
       </c>
       <c r="G29" s="28" t="inlineStr">
         <is>
-          <t>역할은 세션 중 거의 바뀌지 않아 주기 조회는 낭비다. 실제 방어선이 백엔드에 있어 화면이 최신 역할을 조금 늦게 알아도 보안 위험이 없으므로, 로그인·갱신 시점 조회로 충분해 선정.</t>
+          <t>다른 파트의 진척에 가시화가 블로킹되지 않게 하기 위한 요건이다. 전송 인터페이스·레지스트리 조회 형태·액션 어휘집·영상 변환 지점이 아직 확정 전이므로, 확정될 때까지는 정적 구성과 대체 데이터로 개발·시연을 진행한다.</t>
         </is>
       </c>
       <c r="H29" s="28" t="inlineStr">
         <is>
-          <t>백엔드 서버</t>
+          <t>전 파트</t>
         </is>
       </c>
       <c r="I29" s="28" t="inlineStr">
         <is>
-          <t>BE-Q-04</t>
+          <t>HW-C-01, HW-C-02, BE-C-01, BE-T-01</t>
         </is>
       </c>
       <c r="J29" s="27" t="inlineStr">
@@ -22063,7 +22059,7 @@
       </c>
       <c r="K29" s="27" t="inlineStr">
         <is>
-          <t>공유 계층 · 권한</t>
+          <t>공유 계층 · 기동</t>
         </is>
       </c>
       <c r="L29" s="27" t="n"/>
@@ -22071,7 +22067,7 @@
     <row r="30">
       <c r="A30" s="27" t="inlineStr">
         <is>
-          <t>VZ-C-02</t>
+          <t>VZ-C-03</t>
         </is>
       </c>
       <c r="B30" s="41" t="inlineStr">
@@ -22081,37 +22077,37 @@
       </c>
       <c r="C30" s="28" t="inlineStr">
         <is>
-          <t>외부 소스 부재 시 동작</t>
+          <t>집약 계층 경계 표기</t>
         </is>
       </c>
       <c r="D30" s="28" t="inlineStr">
         <is>
-          <t>레지스트리·상태 소스·AI·LLM이 연결되지 않은 상태에서도 정적 구성 파일로 컴포넌트 목록을 구성해 동작해야 한다. LLM이 미연결·무응답일 때는 관련 기능만 비활성화하고 나머지는 정상 동작한다. 임무 생성(VZ-G-01·02)이 로컬 LLM에 의존하게 되었으므로 이 요구사항은 개발 편의가 아니라 운용 요구사항이다 — LLM이 없으면 생성만 멈추고 기존 임무의 실행·관측·디버깅은 계속되어야 하며, 수동 입력 경로를 남긴다.</t>
+          <t>화면이 받는 값이 원본 측정인지 이미 집약된 값인지, 집약이라면 어느 계층(장치·엣지·서버)에서 집약되었는지를 표기와 함께 수신한다. 평시 지표는 구역 단위로 집약된 요약이 올라오므로, 가시화는 이 표기를 확인해 집약값을 원본으로 오인한 재집약을 하지 않는다.</t>
         </is>
       </c>
       <c r="E30" s="28" t="inlineStr">
         <is>
-          <t>(내부 처리)</t>
+          <t>규약(생산자→가시화)</t>
         </is>
       </c>
       <c r="F30" s="27" t="inlineStr">
         <is>
-          <t>해당 없음(기동 시 1회 로드)</t>
+          <t>값 수신 시 상시(표기 동반)</t>
         </is>
       </c>
       <c r="G30" s="28" t="inlineStr">
         <is>
-          <t>다른 파트의 진척에 가시화가 블로킹되지 않게 하기 위한 요건이다. 전송 인터페이스·레지스트리 조회 형태·액션 어휘집·영상 변환 지점이 아직 확정 전이므로, 확정될 때까지는 정적 구성과 대체 데이터로 개발·시연을 진행한다.</t>
+          <t>백엔드가 평시에는 구역 요약만 올리고 원본은 엣지에 남기는 구조라, 화면이 받는 값의 상당수가 이미 집약된 값이다. 표기가 없으면 그 값을 다시 평균·합산해 틀린 숫자를 만든다. 표기를 확인하는 비용은 필드 하나를 읽는 정도인 반면 재집약 오류는 화면상으로 드러나지 않아 발견이 늦으므로, 수신 시마다 확인하는 방식으로 선정.</t>
         </is>
       </c>
       <c r="H30" s="28" t="inlineStr">
         <is>
-          <t>전 파트</t>
+          <t>AI, 백엔드 서버</t>
         </is>
       </c>
       <c r="I30" s="28" t="inlineStr">
         <is>
-          <t>HW-C-01, HW-C-02, BE-C-01, BE-T-01</t>
+          <t>BE-S-06, BE-S-03</t>
         </is>
       </c>
       <c r="J30" s="27" t="inlineStr">
@@ -22121,7 +22117,7 @@
       </c>
       <c r="K30" s="27" t="inlineStr">
         <is>
-          <t>공유 계층 · 기동</t>
+          <t>공유 계층 · 표기 규약</t>
         </is>
       </c>
       <c r="L30" s="27" t="n"/>
@@ -22129,7 +22125,7 @@
     <row r="31">
       <c r="A31" s="27" t="inlineStr">
         <is>
-          <t>VZ-C-03</t>
+          <t>VZ-C-04</t>
         </is>
       </c>
       <c r="B31" s="41" t="inlineStr">
@@ -22139,37 +22135,37 @@
       </c>
       <c r="C31" s="28" t="inlineStr">
         <is>
-          <t>집약 계층 경계 표기</t>
+          <t>권한 범위(scope)</t>
         </is>
       </c>
       <c r="D31" s="28" t="inlineStr">
         <is>
-          <t>화면이 받는 값이 원본 측정인지 이미 집약된 값인지, 집약이라면 어느 계층(장치·엣지·서버)에서 집약되었는지를 표기와 함께 수신한다. 평시 지표는 구역 단위로 집약된 요약이 올라오므로, 가시화는 이 표기를 확인해 집약값을 원본으로 오인한 재집약을 하지 않는다.</t>
+          <t>역할(열람/조작/관리)과 함께 그 역할이 적용되는 범위(도메인·구역 집합)를 조회해, 담당 범위 밖의 대상은 화면에서 제어 UI를 노출하지 않는다. 화면 차단은 사용자 편의이고 역할·범위의 실제 강제는 백엔드가 수행한다.</t>
         </is>
       </c>
       <c r="E31" s="28" t="inlineStr">
         <is>
-          <t>규약(생산자→가시화)</t>
+          <t>백엔드 역할 조회 API→가시화</t>
         </is>
       </c>
       <c r="F31" s="27" t="inlineStr">
         <is>
-          <t>값 수신 시 상시(표기 동반)</t>
+          <t>로그인 시 1회 + 토큰 갱신 시</t>
         </is>
       </c>
       <c r="G31" s="28" t="inlineStr">
         <is>
-          <t>백엔드가 평시에는 구역 요약만 올리고 원본은 엣지에 남기는 구조라, 화면이 받는 값의 상당수가 이미 집약된 값이다. 표기가 없으면 그 값을 다시 평균·합산해 틀린 숫자를 만든다. 표기를 확인하는 비용은 필드 하나를 읽는 정도인 반면 재집약 오류는 화면상으로 드러나지 않아 발견이 늦으므로, 수신 시마다 확인하는 방식으로 선정.</t>
+          <t>역할과 범위는 세션 중 거의 바뀌지 않아 주기 조회는 낭비다. 실제 방어선이 백엔드에 있어 화면이 최신 값을 조금 늦게 알아도 보안 위험이 없으므로, 역할 조회와 같은 시점에 범위를 함께 받는 방식으로 선정.</t>
         </is>
       </c>
       <c r="H31" s="28" t="inlineStr">
         <is>
-          <t>AI, 백엔드 서버</t>
+          <t>백엔드 서버</t>
         </is>
       </c>
       <c r="I31" s="28" t="inlineStr">
         <is>
-          <t>BE-S-06, BE-S-03</t>
+          <t>BE-Q-04, BE-C-02</t>
         </is>
       </c>
       <c r="J31" s="27" t="inlineStr">
@@ -22179,7 +22175,7 @@
       </c>
       <c r="K31" s="27" t="inlineStr">
         <is>
-          <t>공유 계층 · 표기 규약</t>
+          <t>공유 계층 · 권한</t>
         </is>
       </c>
       <c r="L31" s="27" t="n"/>
@@ -22187,7 +22183,7 @@
     <row r="32">
       <c r="A32" s="27" t="inlineStr">
         <is>
-          <t>VZ-C-04</t>
+          <t>VZ-C-05</t>
         </is>
       </c>
       <c r="B32" s="41" t="inlineStr">
@@ -22197,37 +22193,37 @@
       </c>
       <c r="C32" s="28" t="inlineStr">
         <is>
-          <t>권한 범위(scope)</t>
+          <t>설계 규모 가정 명시 — 확인 요망</t>
         </is>
       </c>
       <c r="D32" s="28" t="inlineStr">
         <is>
-          <t>역할(열람/조작/관리)과 함께 그 역할이 적용되는 범위(도메인·구역 집합)를 조회해, 담당 범위 밖의 대상은 화면에서 제어 UI를 노출하지 않는다. 화면 차단은 사용자 편의이고 역할·범위의 실제 강제는 백엔드가 수행한다.</t>
+          <t>시연 규모와 설계 상한(동시 표시 대상 수, 구역 수, 동시 관제 사용자 수)을 요구사항에 명시하고, 그 이상은 별도 요구사항으로 다룬다. 현재 모든 주기·구독 방식은 구역 1개에 장치 수십 개 규모를 전제로 산정되어 있으나 그 전제가 문서에 적혀 있지 않다.</t>
         </is>
       </c>
       <c r="E32" s="28" t="inlineStr">
         <is>
-          <t>백엔드 역할 조회 API→가시화</t>
+          <t>규약(팀 합의)</t>
         </is>
       </c>
       <c r="F32" s="27" t="inlineStr">
         <is>
-          <t>로그인 시 1회 + 토큰 갱신 시</t>
+          <t>해당 없음(전제 정의)</t>
         </is>
       </c>
       <c r="G32" s="28" t="inlineStr">
         <is>
-          <t>역할과 범위는 세션 중 거의 바뀌지 않아 주기 조회는 낭비다. 실제 방어선이 백엔드에 있어 화면이 최신 값을 조금 늦게 알아도 보안 위험이 없으므로, 역할 조회와 같은 시점에 범위를 함께 받는 방식으로 선정.</t>
+          <t>주기 산정의 근거가 규모 가정에 걸려 있는데 그 가정이 문서에 없으면, 확장 논의가 나올 때마다 근거 없이 다시 논쟁하게 된다. 시연 규모와 설계 상한을 숫자로 못박아 두면 '이 설계가 어디까지 커버하는가'에 문서로 답할 수 있다. 숫자 자체는 팀 합의 사항이므로 확인 요망으로 둔다.</t>
         </is>
       </c>
       <c r="H32" s="28" t="inlineStr">
         <is>
-          <t>백엔드 서버</t>
+          <t>전 파트</t>
         </is>
       </c>
       <c r="I32" s="28" t="inlineStr">
         <is>
-          <t>BE-Q-04, BE-C-02</t>
+          <t>BE-S-03, BE-S-07</t>
         </is>
       </c>
       <c r="J32" s="27" t="inlineStr">
@@ -22237,65 +22233,65 @@
       </c>
       <c r="K32" s="27" t="inlineStr">
         <is>
-          <t>공유 계층 · 권한</t>
+          <t>공유 계층 · 기동</t>
         </is>
       </c>
       <c r="L32" s="27" t="n"/>
     </row>
     <row r="33">
-      <c r="A33" s="27" t="inlineStr">
-        <is>
-          <t>VZ-C-05</t>
-        </is>
-      </c>
-      <c r="B33" s="41" t="inlineStr">
+      <c r="A33" s="43" t="inlineStr">
+        <is>
+          <t>VZ-C-06</t>
+        </is>
+      </c>
+      <c r="B33" s="44" t="inlineStr">
         <is>
           <t>공통</t>
         </is>
       </c>
-      <c r="C33" s="28" t="inlineStr">
-        <is>
-          <t>설계 규모 가정 명시 — 확인 요망</t>
-        </is>
-      </c>
-      <c r="D33" s="28" t="inlineStr">
-        <is>
-          <t>시연 규모와 설계 상한(동시 표시 대상 수, 구역 수, 동시 관제 사용자 수)을 요구사항에 명시하고, 그 이상은 별도 요구사항으로 다룬다. 현재 모든 주기·구독 방식은 구역 1개에 장치 수십 개 규모를 전제로 산정되어 있으나 그 전제가 문서에 적혀 있지 않다.</t>
-        </is>
-      </c>
-      <c r="E33" s="28" t="inlineStr">
-        <is>
-          <t>규약(팀 합의)</t>
-        </is>
-      </c>
-      <c r="F33" s="27" t="inlineStr">
-        <is>
-          <t>해당 없음(전제 정의)</t>
-        </is>
-      </c>
-      <c r="G33" s="28" t="inlineStr">
-        <is>
-          <t>주기 산정의 근거가 규모 가정에 걸려 있는데 그 가정이 문서에 없으면, 확장 논의가 나올 때마다 근거 없이 다시 논쟁하게 된다. 시연 규모와 설계 상한을 숫자로 못박아 두면 '이 설계가 어디까지 커버하는가'에 문서로 답할 수 있다. 숫자 자체는 팀 합의 사항이므로 확인 요망으로 둔다.</t>
-        </is>
-      </c>
-      <c r="H33" s="28" t="inlineStr">
+      <c r="C33" s="45" t="inlineStr">
+        <is>
+          <t>원천 종류(실물·시뮬레이션) 표기 — 확인 요망</t>
+        </is>
+      </c>
+      <c r="D33" s="45" t="inlineStr">
+        <is>
+          <t>값·이벤트·명령 결과에 그 원천이 실물 장치인지 시뮬레이션인지 기록 재생인지를 표기와 함께 수신해, 화면이 실물과 비실물을 구분해 표시한다. 명령 요청에도 현재 원천 종류를 함께 실어 보내, 감사 기록이 실물 조작과 시뮬레이션 조작을 구분할 수 있게 한다. 표기의 발행 주체와 필드 형식은 전 파트 합의가 필요하며, 가시화는 이 표기를 읽어 구분 표시하는 소비자 역할이다.</t>
+        </is>
+      </c>
+      <c r="E33" s="45" t="inlineStr">
+        <is>
+          <t>원천(하드웨어·시뮬레이터)→백엔드→가시화 / 가시화→백엔드(명령 요청에 동봉)</t>
+        </is>
+      </c>
+      <c r="F33" s="43" t="inlineStr">
+        <is>
+          <t>해당 없음(값·명령에 표기 동반, 팀 합의 대기)</t>
+        </is>
+      </c>
+      <c r="G33" s="45" t="inlineStr">
+        <is>
+          <t>집약 계층 표기(VZ-C-03)와 같이 값에 동반되는 메타이므로 별도 주기가 없다. 표기가 없으면 시뮬레이션 값이 실물 값과 동일한 봉투로 올라와 화면에서 구분할 수단이 없고, 더 중요하게는 감사 기록에 "그때 시뮬레이션 중이었다"가 남지 않아 사후 조사가 성립하지 않는다(VZ-O-03). 캡스톤 시연 규모에서는 드러나지 않지만 시뮬레이터가 실제 원천을 대체·병행하는 순간부터 성립하며, 국가 인프라 규모에서는 훈련과 실제 상황을 기록상 구분하지 못하는 문제가 된다. 지금 표기 자리를 여는 비용은 필드 하나지만 나중에 끼우는 비용은 발행·저장·감사·화면 전 경로로 전파되므로 자리를 먼저 연다.</t>
+        </is>
+      </c>
+      <c r="H33" s="45" t="inlineStr">
         <is>
           <t>전 파트</t>
         </is>
       </c>
-      <c r="I33" s="28" t="inlineStr">
-        <is>
-          <t>BE-S-03, BE-S-07</t>
-        </is>
-      </c>
-      <c r="J33" s="27" t="inlineStr">
+      <c r="I33" s="45" t="inlineStr">
+        <is>
+          <t>BE-S-06, BE-X-02, BE-S-05</t>
+        </is>
+      </c>
+      <c r="J33" s="43" t="inlineStr">
         <is>
           <t>김현우</t>
         </is>
       </c>
       <c r="K33" s="27" t="inlineStr">
         <is>
-          <t>공유 계층 · 기동</t>
+          <t>공유 계층 · 표기 규약</t>
         </is>
       </c>
       <c r="L33" s="27" t="n"/>
@@ -22303,47 +22299,47 @@
     <row r="34">
       <c r="A34" s="43" t="inlineStr">
         <is>
-          <t>VZ-C-06</t>
+          <t>VZ-D-01</t>
         </is>
       </c>
       <c r="B34" s="44" t="inlineStr">
         <is>
-          <t>공통</t>
+          <t>디버깅</t>
         </is>
       </c>
       <c r="C34" s="45" t="inlineStr">
         <is>
-          <t>원천 종류(실물·시뮬레이션) 표기 — 확인 요망</t>
+          <t>3계층 임무 모델 표시</t>
         </is>
       </c>
       <c r="D34" s="45" t="inlineStr">
         <is>
-          <t>값·이벤트·명령 결과에 그 원천이 실물 장치인지 시뮬레이션인지 기록 재생인지를 표기와 함께 수신해, 화면이 실물과 비실물을 구분해 표시한다. 명령 요청에도 현재 원천 종류를 함께 실어 보내, 감사 기록이 실물 조작과 시뮬레이션 조작을 구분할 수 있게 한다. 표기의 발행 주체와 필드 형식은 전 파트 합의가 필요하며, 가시화는 이 표기를 읽어 구분 표시하는 소비자 역할이다.</t>
+          <t>임무를 마일스톤 → 태스크 → 액션 아이템 3계층으로 받아 계층을 따라 내려가며 표시한다. 마일스톤은 도메인 무관 추상 단위이고, 태스크는 수행 가능 단위이며 deps로 분기·합류를 표현하는 DAG다. 액션 아이템만이 대상 기종에 의존한다. 태스크 종료는 평가(Evaluation) 통과로만 성립하며 평가 전 상태는 별도 상태로 표시한다. 액션 아이템 전개 중 파생된 태스크는 파생 출처를 유지한다. 이 계층의 생산 주체는 가시화다 — 마일스톤은 VZ-G-01, 태스크는 VZ-G-02, 액션 아이템은 VZ-G-04가 만들고 평가는 VZ-G-05가 판정한다. 실행 중 파생 태스크는 VZ-G-04의 되돌림 경로로 생긴다. 사전조건이 깨졌을 때 남은 계획을 다시 만드는 재생성 판단(구 AI-D-04)은 확장 기능으로 분류해 이번 범위에서 제외한다(E9) — 필수 동작이 아니고, 넣으면 실행 중 그래프 크기가 변해 탐색 공간 측정의 분모가 흔들린다.</t>
         </is>
       </c>
       <c r="E34" s="45" t="inlineStr">
         <is>
-          <t>원천(하드웨어·시뮬레이터)→백엔드→가시화 / 가시화→백엔드(명령 요청에 동봉)</t>
+          <t>생산자→백엔드→가시화(WS)</t>
         </is>
       </c>
       <c r="F34" s="43" t="inlineStr">
         <is>
-          <t>해당 없음(값·명령에 표기 동반, 팀 합의 대기)</t>
+          <t>계층 생성·상태 변화 시(이벤트 기반)</t>
         </is>
       </c>
       <c r="G34" s="45" t="inlineStr">
         <is>
-          <t>집약 계층 표기(VZ-C-03)와 같이 값에 동반되는 메타이므로 별도 주기가 없다. 표기가 없으면 시뮬레이션 값이 실물 값과 동일한 봉투로 올라와 화면에서 구분할 수단이 없고, 더 중요하게는 감사 기록에 "그때 시뮬레이션 중이었다"가 남지 않아 사후 조사가 성립하지 않는다(VZ-O-03). 캡스톤 시연 규모에서는 드러나지 않지만 시뮬레이터가 실제 원천을 대체·병행하는 순간부터 성립하며, 국가 인프라 규모에서는 훈련과 실제 상황을 기록상 구분하지 못하는 문제가 된다. 지금 표기 자리를 여는 비용은 필드 하나지만 나중에 끼우는 비용은 발행·저장·감사·화면 전 경로로 전파되므로 자리를 먼저 연다.</t>
+          <t>계층 구조는 임무 하달 시 1회 생성되고 이후에는 상태만 바뀐다. 주기 조회는 같은 구조를 반복 수신할 뿐이다. 액션 아이템 전개 중 새 태스크가 파생될 수 있으므로 구조 변경도 이벤트로 받아야 하며, 초기 1회 조회만으로는 그래프가 실행 중 자라는 것을 표현할 수 없다.</t>
         </is>
       </c>
       <c r="H34" s="45" t="inlineStr">
         <is>
-          <t>전 파트</t>
+          <t>AI, 백엔드 서버, 하드웨어</t>
         </is>
       </c>
       <c r="I34" s="45" t="inlineStr">
         <is>
-          <t>BE-S-06, BE-X-02, BE-S-05</t>
+          <t>BE-X-04, AI-C-09 ← VZ-G-01·02·04·05가 생산</t>
         </is>
       </c>
       <c r="J34" s="43" t="inlineStr">
@@ -22353,7 +22349,7 @@
       </c>
       <c r="K34" s="27" t="inlineStr">
         <is>
-          <t>공유 계층 · 표기 규약</t>
+          <t>탭① 임무 설계 및 디버깅</t>
         </is>
       </c>
       <c r="L34" s="27" t="n"/>
@@ -22361,7 +22357,7 @@
     <row r="35">
       <c r="A35" s="43" t="inlineStr">
         <is>
-          <t>VZ-D-01</t>
+          <t>VZ-D-02</t>
         </is>
       </c>
       <c r="B35" s="44" t="inlineStr">
@@ -22371,12 +22367,12 @@
       </c>
       <c r="C35" s="45" t="inlineStr">
         <is>
-          <t>3계층 임무 모델 표시</t>
+          <t>실행 추적 기록 수신·보관</t>
         </is>
       </c>
       <c r="D35" s="45" t="inlineStr">
         <is>
-          <t>임무를 마일스톤 → 태스크 → 액션 아이템 3계층으로 받아 계층을 따라 내려가며 표시한다. 마일스톤은 도메인 무관 추상 단위이고, 태스크는 수행 가능 단위이며 deps로 분기·합류를 표현하는 DAG다. 액션 아이템만이 대상 기종에 의존한다. 태스크 종료는 평가(Evaluation) 통과로만 성립하며 평가 전 상태는 별도 상태로 표시한다. 액션 아이템 전개 중 파생된 태스크는 파생 출처를 유지한다. 이 계층의 생산 주체는 가시화다 — 마일스톤은 VZ-G-01, 태스크는 VZ-G-02, 액션 아이템은 VZ-G-04가 만들고 평가는 VZ-G-05가 판정한다. 실행 중 파생 태스크는 VZ-G-04의 되돌림 경로로 생긴다. 사전조건이 깨졌을 때 남은 계획을 다시 만드는 재생성 판단(구 AI-D-04)은 확장 기능으로 분류해 이번 범위에서 제외한다(E9) — 필수 동작이 아니고, 넣으면 실행 중 그래프 크기가 변해 탐색 공간 측정의 분모가 흔들린다.</t>
+          <t>임무 실행 중 발생한 사건을 순번·시각·계층·노드·사건 종류·산출 주체·상세로 이루어진 기록 열로 받아 보관한다. 기록은 덧붙이기만 하며 수정·삭제 경로를 두지 않는다. 산출 주체(AI·백엔드·사람)를 반드시 포함하며, 실패한 임무의 기록도 보존한다. 상태를 단일 값으로 뭉쳐 저장하지 않고 기록 열에서 표시값을 파생시킨다.</t>
         </is>
       </c>
       <c r="E35" s="45" t="inlineStr">
@@ -22386,12 +22382,12 @@
       </c>
       <c r="F35" s="43" t="inlineStr">
         <is>
-          <t>계층 생성·상태 변화 시(이벤트 기반)</t>
+          <t>사건 발생 시(이벤트 기반), 화면 반영은 100 ms 창으로 병합</t>
         </is>
       </c>
       <c r="G35" s="45" t="inlineStr">
         <is>
-          <t>계층 구조는 임무 하달 시 1회 생성되고 이후에는 상태만 바뀐다. 주기 조회는 같은 구조를 반복 수신할 뿐이다. 액션 아이템 전개 중 새 태스크가 파생될 수 있으므로 구조 변경도 이벤트로 받아야 하며, 초기 1회 조회만으로는 그래프가 실행 중 자라는 것을 표현할 수 없다.</t>
+          <t>기록은 실행 사건에 종속되므로 주기가 없다. 임무 중 로봇 상태가 50 ms(HW-R-03), 액추에이터 진행이 50 ms(HW-A-04)로 올라오므로 사건 밀도가 초당 수십 건에 이를 수 있어, 수신은 전량 하되 화면 반영만 VZ-I-01과 같은 100 ms 창으로 병합한다. 기록을 요약해 받으면 되감기(VZ-D-04)와 경로 격리(VZ-D-05)가 성립하지 않으므로 수신 자체를 줄이지 않는다.</t>
         </is>
       </c>
       <c r="H35" s="45" t="inlineStr">
@@ -22401,7 +22397,7 @@
       </c>
       <c r="I35" s="45" t="inlineStr">
         <is>
-          <t>BE-X-04, AI-C-09 ← VZ-G-01·02·04·05가 생산</t>
+          <t>HW-R-03, HW-A-04, BE-S-01, BE-X-03 [기록 계약 미정]</t>
         </is>
       </c>
       <c r="J35" s="43" t="inlineStr">
@@ -22419,7 +22415,7 @@
     <row r="36">
       <c r="A36" s="43" t="inlineStr">
         <is>
-          <t>VZ-D-02</t>
+          <t>VZ-D-03</t>
         </is>
       </c>
       <c r="B36" s="44" t="inlineStr">
@@ -22429,37 +22425,37 @@
       </c>
       <c r="C36" s="45" t="inlineStr">
         <is>
-          <t>실행 추적 기록 수신·보관</t>
+          <t>계층 경계 강제(범용/대상 의존)</t>
         </is>
       </c>
       <c r="D36" s="45" t="inlineStr">
         <is>
-          <t>임무 실행 중 발생한 사건을 순번·시각·계층·노드·사건 종류·산출 주체·상세로 이루어진 기록 열로 받아 보관한다. 기록은 덧붙이기만 하며 수정·삭제 경로를 두지 않는다. 산출 주체(AI·백엔드·사람)를 반드시 포함하며, 실패한 임무의 기록도 보존한다. 상태를 단일 값으로 뭉쳐 저장하지 않고 기록 열에서 표시값을 파생시킨다.</t>
+          <t>마일스톤·태스크 계층의 계약에 하드웨어 어휘가 필드로 들어가지 못하게 하고, 기종 의존 값은 액션 아이템의 파라미터 안에만 둔다. 파라미터 해석 규칙은 대상별 어댑터 프로파일 파일에 두고 화면·모델 코드에 기종 표를 다시 적지 않는다. 새 대상 프로파일을 추가할 때 상위 두 계층의 코드가 바뀌지 않아야 하며, 이를 검증 스크립트로 확인한다.</t>
         </is>
       </c>
       <c r="E36" s="45" t="inlineStr">
         <is>
-          <t>생산자→백엔드→가시화(WS)</t>
+          <t>(내부 처리) / 계약 규약</t>
         </is>
       </c>
       <c r="F36" s="43" t="inlineStr">
         <is>
-          <t>사건 발생 시(이벤트 기반), 화면 반영은 100 ms 창으로 병합</t>
+          <t>해당 없음(계약·검증 규약)</t>
         </is>
       </c>
       <c r="G36" s="45" t="inlineStr">
         <is>
-          <t>기록은 실행 사건에 종속되므로 주기가 없다. 임무 중 로봇 상태가 50 ms(HW-R-03), 액추에이터 진행이 50 ms(HW-A-04)로 올라오므로 사건 밀도가 초당 수십 건에 이를 수 있어, 수신은 전량 하되 화면 반영만 VZ-I-01과 같은 100 ms 창으로 병합한다. 기록을 요약해 받으면 되감기(VZ-D-04)와 경로 격리(VZ-D-05)가 성립하지 않으므로 수신 자체를 줄이지 않는다.</t>
+          <t>합의만으로는 경계가 무너진다. 기존 F4 계약이 좌표를 계약 본문 밖으로 막는 것과 같은 방식으로, 스키마의 추가 속성 금지와 회귀 검증으로 강제한다. 강제 장치가 없으면 편의상 태스크에 기종 필드가 하나씩 붙고, 그 순간 같은 임무 정의를 다른 기종에 재사용할 수 없게 된다.</t>
         </is>
       </c>
       <c r="H36" s="45" t="inlineStr">
         <is>
-          <t>AI, 백엔드 서버, 하드웨어</t>
+          <t>AI, 백엔드 서버</t>
         </is>
       </c>
       <c r="I36" s="45" t="inlineStr">
         <is>
-          <t>HW-R-03, HW-A-04, BE-S-01, BE-X-03 [기록 계약 미정]</t>
+          <t>BE-C-01, AI-C-15</t>
         </is>
       </c>
       <c r="J36" s="43" t="inlineStr">
@@ -22477,7 +22473,7 @@
     <row r="37">
       <c r="A37" s="43" t="inlineStr">
         <is>
-          <t>VZ-D-03</t>
+          <t>VZ-D-04</t>
         </is>
       </c>
       <c r="B37" s="44" t="inlineStr">
@@ -22487,37 +22483,37 @@
       </c>
       <c r="C37" s="45" t="inlineStr">
         <is>
-          <t>계층 경계 강제(범용/대상 의존)</t>
+          <t>시점 복원(되감기)과 임무 이력</t>
         </is>
       </c>
       <c r="D37" s="45" t="inlineStr">
         <is>
-          <t>마일스톤·태스크 계층의 계약에 하드웨어 어휘가 필드로 들어가지 못하게 하고, 기종 의존 값은 액션 아이템의 파라미터 안에만 둔다. 파라미터 해석 규칙은 대상별 어댑터 프로파일 파일에 두고 화면·모델 코드에 기종 표를 다시 적지 않는다. 새 대상 프로파일을 추가할 때 상위 두 계층의 코드가 바뀌지 않아야 하며, 이를 검증 스크립트로 확인한다.</t>
+          <t>보관된 기록을 앞에서부터 접어 임의 시점의 계층 상태를 복원하고, 시간 슬라이더로 그 시점 화면을 표시한다. 실패·재실행 등 사건이 있는 지점으로 바로 이동할 수 있어야 한다. 지난 임무를 이력에서 선택해 같은 방식으로 되감으며, 되감기 중에는 대상으로 나가는 명령을 차단한다. 되감기는 별도 화면이 아니라 3계층 표시 화면의 재생 모드다.</t>
         </is>
       </c>
       <c r="E37" s="45" t="inlineStr">
         <is>
-          <t>(내부 처리) / 계약 규약</t>
+          <t>(내부 처리) / 이력 조회: 백엔드→가시화</t>
         </is>
       </c>
       <c r="F37" s="43" t="inlineStr">
         <is>
-          <t>해당 없음(계약·검증 규약)</t>
+          <t>사용자 조작 시(이벤트 기반), 이력 목록은 열람 시 조회</t>
         </is>
       </c>
       <c r="G37" s="45" t="inlineStr">
         <is>
-          <t>합의만으로는 경계가 무너진다. 기존 F4 계약이 좌표를 계약 본문 밖으로 막는 것과 같은 방식으로, 스키마의 추가 속성 금지와 회귀 검증으로 강제한다. 강제 장치가 없으면 편의상 태스크에 기종 필드가 하나씩 붙고, 그 순간 같은 임무 정의를 다른 기종에 재사용할 수 없게 된다.</t>
+          <t>되감기는 저장된 기록만 읽으므로 새 수신이 필요 없고 주기 개념이 없다. 이력도 확정된 과거라 폴링해도 새 값이 나오지 않아 열람 시 조회가 낭비가 적다. 되감기 중 명령을 차단하는 이유는, 과거 시점을 보고 있는 화면에서 낸 명령이 현재 상태에 적용되면 사람이 의도하지 않은 대상에 나가기 때문이다.</t>
         </is>
       </c>
       <c r="H37" s="45" t="inlineStr">
         <is>
-          <t>AI, 백엔드 서버</t>
+          <t>백엔드 서버</t>
         </is>
       </c>
       <c r="I37" s="45" t="inlineStr">
         <is>
-          <t>BE-C-01, AI-C-15</t>
+          <t>BE-S-01, BE-Q-01</t>
         </is>
       </c>
       <c r="J37" s="43" t="inlineStr">
@@ -22535,7 +22531,7 @@
     <row r="38">
       <c r="A38" s="43" t="inlineStr">
         <is>
-          <t>VZ-D-04</t>
+          <t>VZ-D-05</t>
         </is>
       </c>
       <c r="B38" s="44" t="inlineStr">
@@ -22545,37 +22541,37 @@
       </c>
       <c r="C38" s="45" t="inlineStr">
         <is>
-          <t>시점 복원(되감기)과 임무 이력</t>
+          <t>실패 경로 격리</t>
         </is>
       </c>
       <c r="D38" s="45" t="inlineStr">
         <is>
-          <t>보관된 기록을 앞에서부터 접어 임의 시점의 계층 상태를 복원하고, 시간 슬라이더로 그 시점 화면을 표시한다. 실패·재실행 등 사건이 있는 지점으로 바로 이동할 수 있어야 한다. 지난 임무를 이력에서 선택해 같은 방식으로 되감으며, 되감기 중에는 대상으로 나가는 명령을 차단한다. 되감기는 별도 화면이 아니라 3계층 표시 화면의 재생 모드다.</t>
+          <t>실패한 노드에서 의존 관계와 파생 관계를 역방향으로 따라가 실패에 관여한 노드 집합만 남기고 나머지를 접는다. 격리 집합에는 근본 원인이 반드시 포함되어야 하며, 축소 정도와 함께 근본 원인 포함 여부를 검증한다. 격리 결과에는 실패 단계와 사유, 판정 주체가 함께 표시된다.</t>
         </is>
       </c>
       <c r="E38" s="45" t="inlineStr">
         <is>
-          <t>(내부 처리) / 이력 조회: 백엔드→가시화</t>
+          <t>(내부 처리)</t>
         </is>
       </c>
       <c r="F38" s="43" t="inlineStr">
         <is>
-          <t>사용자 조작 시(이벤트 기반), 이력 목록은 열람 시 조회</t>
+          <t>실패 사건 도달 시 즉시 산출</t>
         </is>
       </c>
       <c r="G38" s="45" t="inlineStr">
         <is>
-          <t>되감기는 저장된 기록만 읽으므로 새 수신이 필요 없고 주기 개념이 없다. 이력도 확정된 과거라 폴링해도 새 값이 나오지 않아 열람 시 조회가 낭비가 적다. 되감기 중 명령을 차단하는 이유는, 과거 시점을 보고 있는 화면에서 낸 명령이 현재 상태에 적용되면 사람이 의도하지 않은 대상에 나가기 때문이다.</t>
+          <t>격리는 보관된 기록 위의 계산이라 외부 수신이 없다. 실패 도달 즉시 산출하는 이유는, 사람이 화면을 보는 시점에 이미 좁혀져 있어야 탐색 시간이 줄기 때문이다. 사후 배치 계산으로 미루면 실패 직후 대응 구간에서는 여전히 전체를 훑게 되어 목적을 잃는다.</t>
         </is>
       </c>
       <c r="H38" s="45" t="inlineStr">
         <is>
-          <t>백엔드 서버</t>
+          <t>AI, 백엔드 서버</t>
         </is>
       </c>
       <c r="I38" s="45" t="inlineStr">
         <is>
-          <t>BE-S-01, BE-Q-01</t>
+          <t>BE-X-04 [실패 단계 어휘 합의 필요]</t>
         </is>
       </c>
       <c r="J38" s="43" t="inlineStr">
@@ -22593,7 +22589,7 @@
     <row r="39">
       <c r="A39" s="43" t="inlineStr">
         <is>
-          <t>VZ-D-05</t>
+          <t>VZ-D-06</t>
         </is>
       </c>
       <c r="B39" s="44" t="inlineStr">
@@ -22603,37 +22599,37 @@
       </c>
       <c r="C39" s="45" t="inlineStr">
         <is>
-          <t>실패 경로 격리</t>
+          <t>실행 상태 8종 표시</t>
         </is>
       </c>
       <c r="D39" s="45" t="inlineStr">
         <is>
-          <t>실패한 노드에서 의존 관계와 파생 관계를 역방향으로 따라가 실패에 관여한 노드 집합만 남기고 나머지를 접는다. 격리 집합에는 근본 원인이 반드시 포함되어야 하며, 축소 정도와 함께 근본 원인 포함 여부를 검증한다. 격리 결과에는 실패 단계와 사유, 판정 주체가 함께 표시된다.</t>
+          <t>노드 상태를 대기·진행·완료·실패·건너뜀·평가 대기·미수행·재실행 8종으로 구분해 표시한다. 특히 조건상 의도적으로 넘긴 '건너뜀'과 선행 실패로 실행 자체가 일어나지 않은 '미수행'을 구분하며, 재실행은 회차를 함께 표시한다. 색만으로 8종을 구분하지 않고 테두리 형태·아이콘·회차 표기를 함께 사용한다.</t>
         </is>
       </c>
       <c r="E39" s="45" t="inlineStr">
         <is>
-          <t>(내부 처리)</t>
+          <t>(내부 처리) / 상태는 VZ-D-02 기록에서 파생</t>
         </is>
       </c>
       <c r="F39" s="43" t="inlineStr">
         <is>
-          <t>실패 사건 도달 시 즉시 산출</t>
+          <t>기록 수신 시 갱신(100 ms 병합)</t>
         </is>
       </c>
       <c r="G39" s="45" t="inlineStr">
         <is>
-          <t>격리는 보관된 기록 위의 계산이라 외부 수신이 없다. 실패 도달 즉시 산출하는 이유는, 사람이 화면을 보는 시점에 이미 좁혀져 있어야 탐색 시간이 줄기 때문이다. 사후 배치 계산으로 미루면 실패 직후 대응 구간에서는 여전히 전체를 훑게 되어 목적을 잃는다.</t>
+          <t>상태는 기록에서 파생되므로 별도 주기가 없다. 8종으로 나누는 이유는 디버깅에서 '안 돌렸다'와 '못 돌았다'가 완전히 다른 단서이기 때문이다. 둘을 한 색으로 합치면 사람이 실패 원인을 위쪽에서 찾을지 아래쪽에서 찾을지 판단할 근거를 잃는다. 색만으로 8종을 구분하려 하면 색각 접근성에서도 실패한다.</t>
         </is>
       </c>
       <c r="H39" s="45" t="inlineStr">
         <is>
-          <t>AI, 백엔드 서버</t>
+          <t>백엔드 서버, 하드웨어</t>
         </is>
       </c>
       <c r="I39" s="45" t="inlineStr">
         <is>
-          <t>BE-X-04 [실패 단계 어휘 합의 필요]</t>
+          <t>BE-X-03, BE-X-04</t>
         </is>
       </c>
       <c r="J39" s="43" t="inlineStr">
@@ -22651,7 +22647,7 @@
     <row r="40">
       <c r="A40" s="43" t="inlineStr">
         <is>
-          <t>VZ-D-06</t>
+          <t>VZ-D-07</t>
         </is>
       </c>
       <c r="B40" s="44" t="inlineStr">
@@ -22661,37 +22657,37 @@
       </c>
       <c r="C40" s="45" t="inlineStr">
         <is>
-          <t>실행 상태 8종 표시</t>
+          <t>대상 배정과 대상 상태 조회</t>
         </is>
       </c>
       <c r="D40" s="45" t="inlineStr">
         <is>
-          <t>노드 상태를 대기·진행·완료·실패·건너뜀·평가 대기·미수행·재실행 8종으로 구분해 표시한다. 특히 조건상 의도적으로 넘긴 '건너뜀'과 선행 실패로 실행 자체가 일어나지 않은 '미수행'을 구분하며, 재실행은 회차를 함께 표시한다. 색만으로 8종을 구분하지 않고 테두리 형태·아이콘·회차 표기를 함께 사용한다.</t>
+          <t>레지스트리의 대상 목록을 화면에 두고 마일스톤에 배정해 하위 태스크의 실행 대상을 정한다. 목록과 노드에는 연결 상태와 주요 지표(전원·링크 품질 등)를 함께 표시하고, 액션 아이템 상세에서는 대상의 상세 상태를 조회한다. 조회 항목은 대상별 어댑터 프로파일이 정의하며 화면 코드에 기종별 항목표를 두지 않는다. 배정된 대상이 실행 불가 상태이면 해당 태스크가 실행 전에도 위험으로 드러나야 한다.</t>
         </is>
       </c>
       <c r="E40" s="45" t="inlineStr">
         <is>
-          <t>(내부 처리) / 상태는 VZ-D-02 기록에서 파생</t>
+          <t>백엔드 레지스트리·상태→가시화</t>
         </is>
       </c>
       <c r="F40" s="43" t="inlineStr">
         <is>
-          <t>기록 수신 시 갱신(100 ms 병합)</t>
+          <t>레지스트리는 VZ-I-03과 동일, 상태는 VZ-I-01과 동일(100 ms 병합)</t>
         </is>
       </c>
       <c r="G40" s="45" t="inlineStr">
         <is>
-          <t>상태는 기록에서 파생되므로 별도 주기가 없다. 8종으로 나누는 이유는 디버깅에서 '안 돌렸다'와 '못 돌았다'가 완전히 다른 단서이기 때문이다. 둘을 한 색으로 합치면 사람이 실패 원인을 위쪽에서 찾을지 아래쪽에서 찾을지 판단할 근거를 잃는다. 색만으로 8종을 구분하려 하면 색각 접근성에서도 실패한다.</t>
+          <t>배정은 사용자 조작이라 주기가 없고, 상태는 이미 구독 중인 값을 재사용하므로 추가 수신이 없다. 실행 전 위험 표시를 요구하는 이유는, 배정 대상이 오프라인인 태스크는 실행하면 반드시 실패하는데 그 사실이 실패 이후에야 드러나면 이 도구가 사후 추적으로만 쓰이기 때문이다.</t>
         </is>
       </c>
       <c r="H40" s="45" t="inlineStr">
         <is>
-          <t>백엔드 서버, 하드웨어</t>
+          <t>백엔드 서버, 백엔드 엣지노드, 하드웨어</t>
         </is>
       </c>
       <c r="I40" s="45" t="inlineStr">
         <is>
-          <t>BE-X-03, BE-X-04</t>
+          <t>HW-C-04, HW-S-07, HW-A-05, BE-C-02, AI-O-04</t>
         </is>
       </c>
       <c r="J40" s="43" t="inlineStr">
@@ -22709,7 +22705,7 @@
     <row r="41">
       <c r="A41" s="43" t="inlineStr">
         <is>
-          <t>VZ-D-07</t>
+          <t>VZ-D-08</t>
         </is>
       </c>
       <c r="B41" s="44" t="inlineStr">
@@ -22719,37 +22715,37 @@
       </c>
       <c r="C41" s="45" t="inlineStr">
         <is>
-          <t>대상 배정과 대상 상태 조회</t>
+          <t>화면에서의 실행 개입</t>
         </is>
       </c>
       <c r="D41" s="45" t="inlineStr">
         <is>
-          <t>레지스트리의 대상 목록을 화면에 두고 마일스톤에 배정해 하위 태스크의 실행 대상을 정한다. 목록과 노드에는 연결 상태와 주요 지표(전원·링크 품질 등)를 함께 표시하고, 액션 아이템 상세에서는 대상의 상세 상태를 조회한다. 조회 항목은 대상별 어댑터 프로파일이 정의하며 화면 코드에 기종별 항목표를 두지 않는다. 배정된 대상이 실행 불가 상태이면 해당 태스크가 실행 전에도 위험으로 드러나야 한다.</t>
+          <t>임무 정지·재시작·중단, 실패한 태스크의 파라미터 수정 후 재실행, 액션 아이템 단독 실행, 결함 주입을 화면에서 발행한다. 정지는 하달 중인 액션 아이템까지 끝내고 멈추며 재시작은 멈춘 지점의 태스크부터 이어서 실행한다. 이 조작은 전부 산출 주체를 사람으로 기록에 남기고, 파라미터 수정은 회차를 누적한다. 실제 대상을 움직이지 않고 저장된 기록 위에서 결과만 확인하는 모드를 함께 제공한다.</t>
         </is>
       </c>
       <c r="E41" s="45" t="inlineStr">
         <is>
-          <t>백엔드 레지스트리·상태→가시화</t>
+          <t>가시화→백엔드→대상</t>
         </is>
       </c>
       <c r="F41" s="43" t="inlineStr">
         <is>
-          <t>레지스트리는 VZ-I-03과 동일, 상태는 VZ-I-01과 동일(100 ms 병합)</t>
+          <t>이벤트 기반(사용자 조작 시 즉시)</t>
         </is>
       </c>
       <c r="G41" s="45" t="inlineStr">
         <is>
-          <t>배정은 사용자 조작이라 주기가 없고, 상태는 이미 구독 중인 값을 재사용하므로 추가 수신이 없다. 실행 전 위험 표시를 요구하는 이유는, 배정 대상이 오프라인인 태스크는 실행하면 반드시 실패하는데 그 사실이 실패 이후에야 드러나면 이 도구가 사후 추적으로만 쓰이기 때문이다.</t>
+          <t>사용자 조작은 비주기다. 정지를 액션 아이템 경계에서만 허용하는 이유는, 물리 동작 중간에 끊으면 대상이 어중간한 자세로 남고 그 상태가 기록으로 설명되지 않기 때문이다. 사람의 개입이 기록에 빠지면 되감기와 경로 격리가 잘못된 결론을 낸다 — 개입 기록은 성능이 아니라 도구의 신뢰성 문제라 예외를 두지 않는다.</t>
         </is>
       </c>
       <c r="H41" s="45" t="inlineStr">
         <is>
-          <t>백엔드 서버, 백엔드 엣지노드, 하드웨어</t>
+          <t>백엔드 서버, 하드웨어</t>
         </is>
       </c>
       <c r="I41" s="45" t="inlineStr">
         <is>
-          <t>HW-C-04, HW-S-07, HW-A-05, BE-C-02, AI-O-04</t>
+          <t>HW-C-06, HW-R-05, BE-A-01, BE-X-01, BE-X-02</t>
         </is>
       </c>
       <c r="J41" s="43" t="inlineStr">
@@ -22767,47 +22763,47 @@
     <row r="42">
       <c r="A42" s="43" t="inlineStr">
         <is>
-          <t>VZ-D-08</t>
+          <t>VZ-G-01</t>
         </is>
       </c>
       <c r="B42" s="44" t="inlineStr">
         <is>
-          <t>디버깅</t>
+          <t>생성</t>
         </is>
       </c>
       <c r="C42" s="45" t="inlineStr">
         <is>
-          <t>화면에서의 실행 개입</t>
+          <t>발화 텍스트 → 마일스톤 분리</t>
         </is>
       </c>
       <c r="D42" s="45" t="inlineStr">
         <is>
-          <t>임무 정지·재시작·중단, 실패한 태스크의 파라미터 수정 후 재실행, 액션 아이템 단독 실행, 결함 주입을 화면에서 발행한다. 정지는 하달 중인 액션 아이템까지 끝내고 멈추며 재시작은 멈춘 지점의 태스크부터 이어서 실행한다. 이 조작은 전부 산출 주체를 사람으로 기록에 남기고, 파라미터 수정은 회차를 누적한다. 실제 대상을 움직이지 않고 저장된 기록 위에서 결과만 확인하는 모드를 함께 제공한다.</t>
+          <t>STT로 변환된 발화 텍스트(VZ-L-01)를 임무 하나와 마일스톤 목록으로 분리한다. 마일스톤은 완전히 추상이며 하드웨어 어휘를 포함하지 않는다(VZ-D-03). 분리 결과는 제안 상태로 표시하고 사용자가 수락해야 하위 생성으로 넘어간다(VZ-L-02). 분리에 사용한 생성기 버전과 입력 텍스트를 근거로 함께 남겨 실패 시 이 단계까지 역추적할 수 있게 한다. 대상 호칭은 레지스트리의 표시 이름·별칭으로 해석한다. 로컬 LLM이 없거나 무응답이면 이 기능만 비활성화하고 수동 입력 경로를 남긴다(VZ-C-02).</t>
         </is>
       </c>
       <c r="E42" s="45" t="inlineStr">
         <is>
-          <t>가시화→백엔드→대상</t>
+          <t>가시화 내부(로컬 LLM)→가시화</t>
         </is>
       </c>
       <c r="F42" s="43" t="inlineStr">
         <is>
-          <t>이벤트 기반(사용자 조작 시 즉시)</t>
+          <t>발화 수락 시 1회(이벤트 기반), 응답은 스트리밍 표시</t>
         </is>
       </c>
       <c r="G42" s="45" t="inlineStr">
         <is>
-          <t>사용자 조작은 비주기다. 정지를 액션 아이템 경계에서만 허용하는 이유는, 물리 동작 중간에 끊으면 대상이 어중간한 자세로 남고 그 상태가 기록으로 설명되지 않기 때문이다. 사람의 개입이 기록에 빠지면 되감기와 경로 격리가 잘못된 결론을 낸다 — 개입 기록은 성능이 아니라 도구의 신뢰성 문제라 예외를 두지 않는다.</t>
+          <t>발화는 비주기이므로 생성도 비주기다. 스트리밍 표시하는 이유는 분리 결과를 전부 받은 뒤 한 번에 띄우면 체감 지연이 커지기 때문이다. 이 단계를 별도 요구사항으로 세우는 이유는, 마일스톤 분리 자체가 실패 지점이 될 수 있어서다 — 잘못 쪼갠 마일스톤은 하위 전체를 무너뜨리므로 생성 근거가 기록에 남아야 역추적이 최상위까지 닿는다.</t>
         </is>
       </c>
       <c r="H42" s="45" t="inlineStr">
         <is>
-          <t>백엔드 서버, 하드웨어</t>
+          <t>AI, 백엔드 서버</t>
         </is>
       </c>
       <c r="I42" s="45" t="inlineStr">
         <is>
-          <t>HW-C-06, HW-R-05, BE-A-01, BE-X-01, BE-X-02</t>
+          <t>AI-C-09, AI-C-16, BE-Q-03 [구 AI-D-01 삭제분 인수]</t>
         </is>
       </c>
       <c r="J42" s="43" t="inlineStr">
@@ -22825,7 +22821,7 @@
     <row r="43">
       <c r="A43" s="43" t="inlineStr">
         <is>
-          <t>VZ-G-01</t>
+          <t>VZ-G-02</t>
         </is>
       </c>
       <c r="B43" s="44" t="inlineStr">
@@ -22835,12 +22831,12 @@
       </c>
       <c r="C43" s="45" t="inlineStr">
         <is>
-          <t>발화 텍스트 → 마일스톤 분리</t>
+          <t>마일스톤 → 태스크 생성</t>
         </is>
       </c>
       <c r="D43" s="45" t="inlineStr">
         <is>
-          <t>STT로 변환된 발화 텍스트(VZ-L-01)를 임무 하나와 마일스톤 목록으로 분리한다. 마일스톤은 완전히 추상이며 하드웨어 어휘를 포함하지 않는다(VZ-D-03). 분리 결과는 제안 상태로 표시하고 사용자가 수락해야 하위 생성으로 넘어간다(VZ-L-02). 분리에 사용한 생성기 버전과 입력 텍스트를 근거로 함께 남겨 실패 시 이 단계까지 역추적할 수 있게 한다. 대상 호칭은 레지스트리의 표시 이름·별칭으로 해석한다. 로컬 LLM이 없거나 무응답이면 이 기능만 비활성화하고 수동 입력 경로를 남긴다(VZ-C-02).</t>
+          <t>수락된 마일스톤마다 수행 가능한 태스크를 생성한다. 태스크는 일렬이 아니라 deps로 분기·합류를 갖는 DAG이며, 하나의 마일스톤에 여러 태스크가 생길 수 있다. 태스크 계층까지는 적용 대상과 무관한 범용 단위이고 하드웨어 어휘를 포함하지 않는다. 생성 방식은 특정 LLM이나 계획 라이브러리를 필수로 하지 않으며, 검증 가능한 행동 단위와 조건 표현을 사용한다. 확인 가능한 정보 범위를 넘는 계획을 만들지 않고 부족한 근거를 명시한다.</t>
         </is>
       </c>
       <c r="E43" s="45" t="inlineStr">
@@ -22850,22 +22846,22 @@
       </c>
       <c r="F43" s="43" t="inlineStr">
         <is>
-          <t>발화 수락 시 1회(이벤트 기반), 응답은 스트리밍 표시</t>
+          <t>마일스톤 수락 시 1회(이벤트 기반)</t>
         </is>
       </c>
       <c r="G43" s="45" t="inlineStr">
         <is>
-          <t>발화는 비주기이므로 생성도 비주기다. 스트리밍 표시하는 이유는 분리 결과를 전부 받은 뒤 한 번에 띄우면 체감 지연이 커지기 때문이다. 이 단계를 별도 요구사항으로 세우는 이유는, 마일스톤 분리 자체가 실패 지점이 될 수 있어서다 — 잘못 쪼갠 마일스톤은 하위 전체를 무너뜨리므로 생성 근거가 기록에 남아야 역추적이 최상위까지 닿는다.</t>
+          <t>마일스톤과 마찬가지로 사용자 수락에 종속되어 주기가 없다. DAG로 만드는 이유는 회의록 §4-3의 'flow → process — 여러 갈래가 다시 하나의 박스로 모이는 형태'를 표현해야 하기 때문이고, 일렬 인덱스로 두면 분기·합류가 사라져 실패 경로 역추적(VZ-D-05)이 성립하지 않는다.</t>
         </is>
       </c>
       <c r="H43" s="45" t="inlineStr">
         <is>
-          <t>AI, 백엔드 서버</t>
+          <t>AI, 백엔드 서버, 하드웨어</t>
         </is>
       </c>
       <c r="I43" s="45" t="inlineStr">
         <is>
-          <t>AI-C-09, AI-C-16, BE-Q-03 [구 AI-D-01 삭제분 인수]</t>
+          <t>AI-C-09, BE-X-04 [구 AI-D-01 삭제분 인수]</t>
         </is>
       </c>
       <c r="J43" s="43" t="inlineStr">
@@ -22883,7 +22879,7 @@
     <row r="44">
       <c r="A44" s="43" t="inlineStr">
         <is>
-          <t>VZ-G-02</t>
+          <t>VZ-G-03</t>
         </is>
       </c>
       <c r="B44" s="44" t="inlineStr">
@@ -22893,37 +22889,37 @@
       </c>
       <c r="C44" s="45" t="inlineStr">
         <is>
-          <t>마일스톤 → 태스크 생성</t>
+          <t>태스크 검증</t>
         </is>
       </c>
       <c r="D44" s="45" t="inlineStr">
         <is>
-          <t>수락된 마일스톤마다 수행 가능한 태스크를 생성한다. 태스크는 일렬이 아니라 deps로 분기·합류를 갖는 DAG이며, 하나의 마일스톤에 여러 태스크가 생길 수 있다. 태스크 계층까지는 적용 대상과 무관한 범용 단위이고 하드웨어 어휘를 포함하지 않는다. 생성 방식은 특정 LLM이나 계획 라이브러리를 필수로 하지 않으며, 검증 가능한 행동 단위와 조건 표현을 사용한다. 확인 가능한 정보 범위를 넘는 계획을 만들지 않고 부족한 근거를 명시한다.</t>
+          <t>생성된 태스크를 실행 전에 검증한다. 구조, 순서, 의존 관계의 순환 여부, 사전조건, 자원 조건, 배정된 대상의 수행 가능성을 확인한다. 검증 기능은 생성 기능과 분리해 동일 입력에서 재현 가능한 결과를 제공한다. 확인할 수 없는 필수 조건이 있으면 해당 태스크만 실행 불가로 표시하고 부족한 근거를 명시한다. 검증 결과는 VZ-U-07의 승인 화면과 VZ-L-03의 2단 확인 ②단계 표시에 사용한다.</t>
         </is>
       </c>
       <c r="E44" s="45" t="inlineStr">
         <is>
-          <t>가시화 내부(로컬 LLM)→가시화</t>
+          <t>(내부 처리)</t>
         </is>
       </c>
       <c r="F44" s="43" t="inlineStr">
         <is>
-          <t>마일스톤 수락 시 1회(이벤트 기반)</t>
+          <t>태스크 생성 직후 1회 + 배정 변경 시 재검증</t>
         </is>
       </c>
       <c r="G44" s="45" t="inlineStr">
         <is>
-          <t>마일스톤과 마찬가지로 사용자 수락에 종속되어 주기가 없다. DAG로 만드는 이유는 회의록 §4-3의 'flow → process — 여러 갈래가 다시 하나의 박스로 모이는 형태'를 표현해야 하기 때문이고, 일렬 인덱스로 두면 분기·합류가 사라져 실패 경로 역추적(VZ-D-05)이 성립하지 않는다.</t>
+          <t>검증은 생성 결과에 종속되므로 주기가 없다. 배정이 바뀌면 다시 검증하는 이유는 대상이 달라지면 수행 가능성 판정이 달라지기 때문이다(VZ-D-07). 생성과 같은 사람이 만들더라도 모듈은 분리한다 — 생성기가 스스로를 검증하면 같은 오해를 두 번 반복할 뿐이고, 재현 가능한 검증이라야 실패했을 때 생성 탓인지 검증 탓인지 가를 수 있다.</t>
         </is>
       </c>
       <c r="H44" s="45" t="inlineStr">
         <is>
-          <t>AI, 백엔드 서버, 하드웨어</t>
+          <t>백엔드 서버, 하드웨어</t>
         </is>
       </c>
       <c r="I44" s="45" t="inlineStr">
         <is>
-          <t>AI-C-09, BE-X-04 [구 AI-D-01 삭제분 인수]</t>
+          <t>BE-X-04, HW-A-05 [구 AI-D-02 삭제분 인수]</t>
         </is>
       </c>
       <c r="J44" s="43" t="inlineStr">
@@ -22941,7 +22937,7 @@
     <row r="45">
       <c r="A45" s="43" t="inlineStr">
         <is>
-          <t>VZ-G-03</t>
+          <t>VZ-G-04</t>
         </is>
       </c>
       <c r="B45" s="44" t="inlineStr">
@@ -22951,27 +22947,27 @@
       </c>
       <c r="C45" s="45" t="inlineStr">
         <is>
-          <t>태스크 검증</t>
+          <t>태스크 → 액션 아이템 전개</t>
         </is>
       </c>
       <c r="D45" s="45" t="inlineStr">
         <is>
-          <t>생성된 태스크를 실행 전에 검증한다. 구조, 순서, 의존 관계의 순환 여부, 사전조건, 자원 조건, 배정된 대상의 수행 가능성을 확인한다. 검증 기능은 생성 기능과 분리해 동일 입력에서 재현 가능한 결과를 제공한다. 확인할 수 없는 필수 조건이 있으면 해당 태스크만 실행 불가로 표시하고 부족한 근거를 명시한다. 검증 결과는 VZ-U-07의 승인 화면과 VZ-L-03의 2단 확인 ②단계 표시에 사용한다.</t>
+          <t>검증을 통과한 태스크를 배정된 대상의 어댑터 프로파일에 따라 실제 명령값을 갖는 액션 아이템으로 전개한다. 기종 의존 값과 그 해석 규칙은 어댑터 프로파일에만 두고 상위 계층과 화면 코드에 기종별 표를 두지 않는다(VZ-D-03). 같은 태스크가 다른 대상에 배정되면 상위 정의는 그대로 두고 전개 결과만 달라져야 한다. 전개 중 새 태스크가 필요해지면 파생 출처를 유지한 채 상위로 되돌린다.</t>
         </is>
       </c>
       <c r="E45" s="45" t="inlineStr">
         <is>
-          <t>(내부 처리)</t>
+          <t>(내부 처리) / 발행은 VZ-O-01</t>
         </is>
       </c>
       <c r="F45" s="43" t="inlineStr">
         <is>
-          <t>태스크 생성 직후 1회 + 배정 변경 시 재검증</t>
+          <t>태스크 검증 통과 후 1회 + 배정 변경 시 재전개</t>
         </is>
       </c>
       <c r="G45" s="45" t="inlineStr">
         <is>
-          <t>검증은 생성 결과에 종속되므로 주기가 없다. 배정이 바뀌면 다시 검증하는 이유는 대상이 달라지면 수행 가능성 판정이 달라지기 때문이다(VZ-D-07). 생성과 같은 사람이 만들더라도 모듈은 분리한다 — 생성기가 스스로를 검증하면 같은 오해를 두 번 반복할 뿐이고, 재현 가능한 검증이라야 실패했을 때 생성 탓인지 검증 탓인지 가를 수 있다.</t>
+          <t>전개는 검증 결과와 배정에 종속되어 주기가 없다. 실행 직전이 아니라 검증 직후에 전개하는 이유는, 전개 결과를 사용자가 승인 화면에서 미리 볼 수 있어야 하고(VZ-U-07) 전개 단계에서 드러나는 불가능(예: 대상이 지원하지 않는 동작)을 실행 전에 잡아야 하기 때문이다. 실제 디바이스 명령으로의 번역은 여전히 백엔드가 수행한다(VZ-O-01).</t>
         </is>
       </c>
       <c r="H45" s="45" t="inlineStr">
@@ -22981,7 +22977,7 @@
       </c>
       <c r="I45" s="45" t="inlineStr">
         <is>
-          <t>BE-X-04, HW-A-05 [구 AI-D-02 삭제분 인수]</t>
+          <t>HW-R-05, HW-A-02, BE-A-01, BE-A-02, AI-C-15</t>
         </is>
       </c>
       <c r="J45" s="43" t="inlineStr">
@@ -22999,7 +22995,7 @@
     <row r="46">
       <c r="A46" s="43" t="inlineStr">
         <is>
-          <t>VZ-G-04</t>
+          <t>VZ-G-05</t>
         </is>
       </c>
       <c r="B46" s="44" t="inlineStr">
@@ -23009,37 +23005,37 @@
       </c>
       <c r="C46" s="45" t="inlineStr">
         <is>
-          <t>태스크 → 액션 아이템 전개</t>
+          <t>평가 기준 생성 및 판정</t>
         </is>
       </c>
       <c r="D46" s="45" t="inlineStr">
         <is>
-          <t>검증을 통과한 태스크를 배정된 대상의 어댑터 프로파일에 따라 실제 명령값을 갖는 액션 아이템으로 전개한다. 기종 의존 값과 그 해석 규칙은 어댑터 프로파일에만 두고 상위 계층과 화면 코드에 기종별 표를 두지 않는다(VZ-D-03). 같은 태스크가 다른 대상에 배정되면 상위 정의는 그대로 두고 전개 결과만 달라져야 한다. 전개 중 새 태스크가 필요해지면 파생 출처를 유지한 채 상위로 되돌린다.</t>
+          <t>태스크마다 종료를 판정할 평가 기준을 생성하고, 실행 결과를 그 기준으로 판정한다. 태스크는 실행 완료가 아니라 평가 통과로만 종료되며 평가 전에는 별도 상태로 표시한다(VZ-D-06). 기준은 측정 가능한 항목과 임계로 표현하고, 판정에는 사용한 근거와 판정 주체를 함께 남긴다. 판정에 필요한 값이 도달하지 않으면 통과로 승격하지 않고 근거 부족을 드러낸다. 규칙으로 판정할 수 없는 항목은 사람 판정으로 넘긴다.</t>
         </is>
       </c>
       <c r="E46" s="45" t="inlineStr">
         <is>
-          <t>(내부 처리) / 발행은 VZ-O-01</t>
+          <t>(내부 처리) / 판정 입력은 상태·명령 결과 수신</t>
         </is>
       </c>
       <c r="F46" s="43" t="inlineStr">
         <is>
-          <t>태스크 검증 통과 후 1회 + 배정 변경 시 재전개</t>
+          <t>태스크 실행 종료 시 1회, 근거 미도달 시 대기</t>
         </is>
       </c>
       <c r="G46" s="45" t="inlineStr">
         <is>
-          <t>전개는 검증 결과와 배정에 종속되어 주기가 없다. 실행 직전이 아니라 검증 직후에 전개하는 이유는, 전개 결과를 사용자가 승인 화면에서 미리 볼 수 있어야 하고(VZ-U-07) 전개 단계에서 드러나는 불가능(예: 대상이 지원하지 않는 동작)을 실행 전에 잡아야 하기 때문이다. 실제 디바이스 명령으로의 번역은 여전히 백엔드가 수행한다(VZ-O-01).</t>
+          <t>판정은 실행 종료 이벤트에 종속되어 주기가 없다. 근거가 도달하지 않았을 때 대기하는 이유는, 시간이 지났다는 이유로 통과시키면 '평가가 끝나야 태스크가 끝난다'는 회의 합의가 무의미해지기 때문이다. 판정 주체를 남기는 이유는 규칙 판정과 사람 판정이 섞일 때 사후에 둘을 갈라야 하기 때문이며, 이는 VZ-D-02의 산출 주체 기록과 같은 이유다.</t>
         </is>
       </c>
       <c r="H46" s="45" t="inlineStr">
         <is>
-          <t>백엔드 서버, 하드웨어</t>
+          <t>AI, 백엔드 서버, 하드웨어</t>
         </is>
       </c>
       <c r="I46" s="45" t="inlineStr">
         <is>
-          <t>HW-R-05, HW-A-02, BE-A-01, BE-A-02, AI-C-15</t>
+          <t>HW-A-04, HW-R-05, AI-S-03, BE-X-03 [구 AI-D-02 삭제분 인수]</t>
         </is>
       </c>
       <c r="J46" s="43" t="inlineStr">
@@ -23053,64 +23049,6 @@
         </is>
       </c>
       <c r="L46" s="27" t="n"/>
-    </row>
-    <row r="47">
-      <c r="A47" s="43" t="inlineStr">
-        <is>
-          <t>VZ-G-05</t>
-        </is>
-      </c>
-      <c r="B47" s="44" t="inlineStr">
-        <is>
-          <t>생성</t>
-        </is>
-      </c>
-      <c r="C47" s="45" t="inlineStr">
-        <is>
-          <t>평가 기준 생성 및 판정</t>
-        </is>
-      </c>
-      <c r="D47" s="45" t="inlineStr">
-        <is>
-          <t>태스크마다 종료를 판정할 평가 기준을 생성하고, 실행 결과를 그 기준으로 판정한다. 태스크는 실행 완료가 아니라 평가 통과로만 종료되며 평가 전에는 별도 상태로 표시한다(VZ-D-06). 기준은 측정 가능한 항목과 임계로 표현하고, 판정에는 사용한 근거와 판정 주체를 함께 남긴다. 판정에 필요한 값이 도달하지 않으면 통과로 승격하지 않고 근거 부족을 드러낸다. 규칙으로 판정할 수 없는 항목은 사람 판정으로 넘긴다.</t>
-        </is>
-      </c>
-      <c r="E47" s="45" t="inlineStr">
-        <is>
-          <t>(내부 처리) / 판정 입력은 상태·명령 결과 수신</t>
-        </is>
-      </c>
-      <c r="F47" s="43" t="inlineStr">
-        <is>
-          <t>태스크 실행 종료 시 1회, 근거 미도달 시 대기</t>
-        </is>
-      </c>
-      <c r="G47" s="45" t="inlineStr">
-        <is>
-          <t>판정은 실행 종료 이벤트에 종속되어 주기가 없다. 근거가 도달하지 않았을 때 대기하는 이유는, 시간이 지났다는 이유로 통과시키면 '평가가 끝나야 태스크가 끝난다'는 회의 합의가 무의미해지기 때문이다. 판정 주체를 남기는 이유는 규칙 판정과 사람 판정이 섞일 때 사후에 둘을 갈라야 하기 때문이며, 이는 VZ-D-02의 산출 주체 기록과 같은 이유다.</t>
-        </is>
-      </c>
-      <c r="H47" s="45" t="inlineStr">
-        <is>
-          <t>AI, 백엔드 서버, 하드웨어</t>
-        </is>
-      </c>
-      <c r="I47" s="45" t="inlineStr">
-        <is>
-          <t>HW-A-04, HW-R-05, AI-S-03, BE-X-03 [구 AI-D-02 삭제분 인수]</t>
-        </is>
-      </c>
-      <c r="J47" s="43" t="inlineStr">
-        <is>
-          <t>김현우</t>
-        </is>
-      </c>
-      <c r="K47" s="27" t="inlineStr">
-        <is>
-          <t>탭① 임무 설계 및 디버깅</t>
-        </is>
-      </c>
-      <c r="L47" s="27" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/피지컬팀 프로젝트 mk2 요구사항 정의서.xlsx
+++ b/피지컬팀 프로젝트 mk2 요구사항 정의서.xlsx
@@ -20911,7 +20911,7 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O51"/>
+  <dimension ref="A1:O52"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="12.63" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
     <col width="43.38" customWidth="1" style="54" min="4" max="4"/>
@@ -22828,7 +22828,7 @@
       </c>
       <c r="L32" s="37" t="n"/>
     </row>
-    <row r="33">
+    <row r="33" s="54">
       <c r="A33" s="43" t="inlineStr">
         <is>
           <t>VZ-C-06</t>
@@ -22886,50 +22886,50 @@
       </c>
       <c r="L33" s="37" t="n"/>
     </row>
-    <row r="34">
+    <row r="34" s="54">
       <c r="A34" s="43" t="inlineStr">
         <is>
-          <t>VZ-D-01</t>
+          <t>VZ-C-07</t>
         </is>
       </c>
       <c r="B34" s="44" t="inlineStr">
         <is>
-          <t>디버깅</t>
+          <t>공통</t>
         </is>
       </c>
       <c r="C34" s="45" t="inlineStr">
         <is>
-          <t>3계층 임무 모델 표시</t>
+          <t>연결 대상 설정</t>
         </is>
       </c>
       <c r="D34" s="45" t="inlineStr">
         <is>
-          <t>임무를 마일스톤 → 태스크 → 액션 아이템 3계층으로 받아 계층을 따라 내려가며 표시한다. 마일스톤은 도메인 무관 추상 단위이고, 태스크는 수행 가능 단위이며 deps로 분기·합류를 표현하는 DAG다. 액션 아이템만이 대상 기종에 의존한다. 태스크 종료는 평가(Evaluation) 통과로만 성립하며 평가 전 상태는 별도 상태로 표시한다. 액션 아이템 전개 중 파생된 태스크는 파생 출처를 유지한다. 이 계층의 생산 주체는 가시화다 — 마일스톤은 VZ-G-01, 태스크는 VZ-G-02, 액션 아이템은 VZ-G-04가 만들고 평가는 VZ-G-05가 판정한다. 실행 중 파생 태스크는 VZ-G-04의 되돌림 경로로 생긴다. 사전조건이 깨졌을 때 남은 계획을 다시 만드는 재생성 판단(구 AI-D-04)은 확장 기능으로 분류해 이번 범위에서 제외한다(E9) — 필수 동작이 아니고, 넣으면 실행 중 그래프 크기가 변해 탐색 공간 측정의 분모가 흔들린다.</t>
+          <t>가시화가 붙을 대상(백엔드 WS 게이트웨이·STT 서비스·제어 노드·디지털 트윈)의 주소를 화면에서 설정하고 저장할 수 있어야 한다. 설정은 새로고침·재접속 후에도 유지되며, 기본값으로 되돌리는 수단을 화면에 둔다. 주소가 바뀌면 기존 연결을 끊고 새 주소로 다시 붙는다. 아직 상대가 없는 대상(제어 노드·디지털 트윈)은 자리만 두고 「연결 예정」으로 표시한다.</t>
         </is>
       </c>
       <c r="E34" s="45" t="inlineStr">
         <is>
-          <t>생산자→백엔드→가시화(WS)</t>
+          <t>(내부 처리) / 실제 연결은 VZ-I-01·I-02 경로</t>
         </is>
       </c>
       <c r="F34" s="43" t="inlineStr">
         <is>
-          <t>계층 생성·상태 변화 시(이벤트 기반)</t>
+          <t>사용자 조작 시(이벤트 기반). 저장은 변경 즉시, 로드는 기동 시 1회</t>
         </is>
       </c>
       <c r="G34" s="45" t="inlineStr">
         <is>
-          <t>계층 구조는 임무 하달 시 1회 생성되고 이후에는 상태만 바뀐다. 주기 조회는 같은 구조를 반복 수신할 뿐이다. 액션 아이템 전개 중 새 태스크가 파생될 수 있으므로 구조 변경도 이벤트로 받아야 하며, 초기 1회 조회만으로는 그래프가 실행 중 자라는 것을 표현할 수 없다.</t>
+          <t>접속 대상 변경은 사용자 조작이라 주기가 없다. 지금은 빌드 시점 환경변수(VITE_GATEWAY_WS 등)로 고정돼 있어 주소를 바꾸려면 다시 빌드해야 하는데, 현장에서 게이트웨이·제어 노드 주소가 바뀔 때마다 빌드할 수는 없다. VZ-C-02(외부 소스 부재 시 동작)의 짝이다 — C-02가 「안 붙어 있어도 화면은 뜬다」면 C-07은 「어디에 붙을지 사람이 정한다」이다.</t>
         </is>
       </c>
       <c r="H34" s="45" t="inlineStr">
         <is>
-          <t>AI, 백엔드 서버, 하드웨어</t>
+          <t>백엔드 서버, 백엔드 엣지노드</t>
         </is>
       </c>
       <c r="I34" s="45" t="inlineStr">
         <is>
-          <t>BE-X-04, AI-C-09 ← VZ-G-01·02·04·05가 생산</t>
+          <t>BE-T-03(가시화 클라이언트 실시간 채널 게이트웨이), BE-C-05 ← VZ-I-01·I-02 가 쓰는 주소</t>
         </is>
       </c>
       <c r="J34" s="43" t="inlineStr">
@@ -22939,15 +22939,19 @@
       </c>
       <c r="K34" s="37" t="inlineStr">
         <is>
-          <t>노드 캔버스 · 실행 노드</t>
-        </is>
-      </c>
-      <c r="L34" s="37" t="n"/>
+          <t>공유 계층 · 기동</t>
+        </is>
+      </c>
+      <c r="L34" s="37" t="inlineStr">
+        <is>
+          <t>v1.2 신설. 구독·명령 출구는 여전히 하나다(verify:one-gateway) — 바뀌는 것은 주소뿐이고 transport 싱글턴은 유지한 채 끊고 다시 붙는다. 저장은 VZ-N-04 와 같은 방식이되 키가 임무별이 아니라 앱 전역이다.</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="43" t="inlineStr">
         <is>
-          <t>VZ-D-02</t>
+          <t>VZ-D-01</t>
         </is>
       </c>
       <c r="B35" s="44" t="inlineStr">
@@ -22957,12 +22961,12 @@
       </c>
       <c r="C35" s="45" t="inlineStr">
         <is>
-          <t>실행 추적 기록 수신·보관</t>
+          <t>3계층 임무 모델 표시</t>
         </is>
       </c>
       <c r="D35" s="45" t="inlineStr">
         <is>
-          <t>임무 실행 중 발생한 사건을 순번·시각·계층·노드·사건 종류·산출 주체·상세로 이루어진 기록 열로 받아 보관한다. 기록은 덧붙이기만 하며 수정·삭제 경로를 두지 않는다. 산출 주체(AI·백엔드·사람)를 반드시 포함하며, 실패한 임무의 기록도 보존한다. 상태를 단일 값으로 뭉쳐 저장하지 않고 기록 열에서 표시값을 파생시킨다.</t>
+          <t>임무를 마일스톤 → 태스크 → 액션 아이템 3계층으로 받아 계층을 따라 내려가며 표시한다. 마일스톤은 도메인 무관 추상 단위이고, 태스크는 수행 가능 단위이며 deps로 분기·합류를 표현하는 DAG다. 액션 아이템만이 대상 기종에 의존한다. 태스크 종료는 평가(Evaluation) 통과로만 성립하며 평가 전 상태는 별도 상태로 표시한다. 액션 아이템 전개 중 파생된 태스크는 파생 출처를 유지한다. 이 계층의 생산 주체는 가시화다 — 마일스톤은 VZ-G-01, 태스크는 VZ-G-02, 액션 아이템은 VZ-G-04가 만들고 평가는 VZ-G-05가 판정한다. 실행 중 파생 태스크는 VZ-G-04의 되돌림 경로로 생긴다. 사전조건이 깨졌을 때 남은 계획을 다시 만드는 재생성 판단(구 AI-D-04)은 확장 기능으로 분류해 이번 범위에서 제외한다(E9) — 필수 동작이 아니고, 넣으면 실행 중 그래프 크기가 변해 탐색 공간 측정의 분모가 흔들린다.</t>
         </is>
       </c>
       <c r="E35" s="45" t="inlineStr">
@@ -22972,12 +22976,12 @@
       </c>
       <c r="F35" s="43" t="inlineStr">
         <is>
-          <t>사건 발생 시(이벤트 기반), 화면 반영은 100 ms 창으로 병합</t>
+          <t>계층 생성·상태 변화 시(이벤트 기반)</t>
         </is>
       </c>
       <c r="G35" s="45" t="inlineStr">
         <is>
-          <t>기록은 실행 사건에 종속되므로 주기가 없다. 임무 중 로봇 상태가 50 ms(HW-R-03), 액추에이터 진행이 50 ms(HW-A-04)로 올라오므로 사건 밀도가 초당 수십 건에 이를 수 있어, 수신은 전량 하되 화면 반영만 VZ-I-01과 같은 100 ms 창으로 병합한다. 기록을 요약해 받으면 되감기(VZ-D-04)와 경로 격리(VZ-D-05)가 성립하지 않으므로 수신 자체를 줄이지 않는다.</t>
+          <t>계층 구조는 임무 하달 시 1회 생성되고 이후에는 상태만 바뀐다. 주기 조회는 같은 구조를 반복 수신할 뿐이다. 액션 아이템 전개 중 새 태스크가 파생될 수 있으므로 구조 변경도 이벤트로 받아야 하며, 초기 1회 조회만으로는 그래프가 실행 중 자라는 것을 표현할 수 없다.</t>
         </is>
       </c>
       <c r="H35" s="45" t="inlineStr">
@@ -22987,7 +22991,7 @@
       </c>
       <c r="I35" s="45" t="inlineStr">
         <is>
-          <t>HW-R-03, HW-A-04, BE-S-01, BE-X-03 [기록 계약 미정]</t>
+          <t>BE-X-04, AI-C-09 ← VZ-G-01·02·04·05가 생산</t>
         </is>
       </c>
       <c r="J35" s="43" t="inlineStr">
@@ -23005,7 +23009,7 @@
     <row r="36">
       <c r="A36" s="43" t="inlineStr">
         <is>
-          <t>VZ-D-03</t>
+          <t>VZ-D-02</t>
         </is>
       </c>
       <c r="B36" s="44" t="inlineStr">
@@ -23015,37 +23019,37 @@
       </c>
       <c r="C36" s="45" t="inlineStr">
         <is>
-          <t>계층 경계 강제(범용/대상 의존)</t>
+          <t>실행 추적 기록 수신·보관</t>
         </is>
       </c>
       <c r="D36" s="45" t="inlineStr">
         <is>
-          <t>마일스톤·태스크 계층의 계약에 하드웨어 어휘가 필드로 들어가지 못하게 하고, 기종 의존 값은 액션 아이템의 파라미터 안에만 둔다. 파라미터 해석 규칙은 대상별 어댑터 프로파일 파일에 두고 화면·모델 코드에 기종 표를 다시 적지 않는다. 새 대상 프로파일을 추가할 때 상위 두 계층의 코드가 바뀌지 않아야 하며, 이를 검증 스크립트로 확인한다.</t>
+          <t>임무 실행 중 발생한 사건을 순번·시각·계층·노드·사건 종류·산출 주체·상세로 이루어진 기록 열로 받아 보관한다. 기록은 덧붙이기만 하며 수정·삭제 경로를 두지 않는다. 산출 주체(AI·백엔드·사람)를 반드시 포함하며, 실패한 임무의 기록도 보존한다. 상태를 단일 값으로 뭉쳐 저장하지 않고 기록 열에서 표시값을 파생시킨다.</t>
         </is>
       </c>
       <c r="E36" s="45" t="inlineStr">
         <is>
-          <t>(내부 처리) / 계약 규약</t>
+          <t>생산자→백엔드→가시화(WS)</t>
         </is>
       </c>
       <c r="F36" s="43" t="inlineStr">
         <is>
-          <t>해당 없음(계약·검증 규약)</t>
+          <t>사건 발생 시(이벤트 기반), 화면 반영은 100 ms 창으로 병합</t>
         </is>
       </c>
       <c r="G36" s="45" t="inlineStr">
         <is>
-          <t>합의만으로는 경계가 무너진다. 기존 F4 계약이 좌표를 계약 본문 밖으로 막는 것과 같은 방식으로, 스키마의 추가 속성 금지와 회귀 검증으로 강제한다. 강제 장치가 없으면 편의상 태스크에 기종 필드가 하나씩 붙고, 그 순간 같은 임무 정의를 다른 기종에 재사용할 수 없게 된다.</t>
+          <t>기록은 실행 사건에 종속되므로 주기가 없다. 임무 중 로봇 상태가 50 ms(HW-R-03), 액추에이터 진행이 50 ms(HW-A-04)로 올라오므로 사건 밀도가 초당 수십 건에 이를 수 있어, 수신은 전량 하되 화면 반영만 VZ-I-01과 같은 100 ms 창으로 병합한다. 기록을 요약해 받으면 되감기(VZ-D-04)와 경로 격리(VZ-D-05)가 성립하지 않으므로 수신 자체를 줄이지 않는다.</t>
         </is>
       </c>
       <c r="H36" s="45" t="inlineStr">
         <is>
-          <t>AI, 백엔드 서버</t>
+          <t>AI, 백엔드 서버, 하드웨어</t>
         </is>
       </c>
       <c r="I36" s="45" t="inlineStr">
         <is>
-          <t>BE-C-01, AI-C-15</t>
+          <t>HW-R-03, HW-A-04, BE-S-01, BE-X-03 [기록 계약 미정]</t>
         </is>
       </c>
       <c r="J36" s="43" t="inlineStr">
@@ -23063,7 +23067,7 @@
     <row r="37">
       <c r="A37" s="43" t="inlineStr">
         <is>
-          <t>VZ-D-04</t>
+          <t>VZ-D-03</t>
         </is>
       </c>
       <c r="B37" s="44" t="inlineStr">
@@ -23073,37 +23077,37 @@
       </c>
       <c r="C37" s="45" t="inlineStr">
         <is>
-          <t>시점 복원(되감기)과 임무 이력</t>
+          <t>계층 경계 강제(범용/대상 의존)</t>
         </is>
       </c>
       <c r="D37" s="45" t="inlineStr">
         <is>
-          <t>보관된 기록을 앞에서부터 접어 임의 시점의 계층 상태를 복원하고, 시간 슬라이더로 그 시점 화면을 표시한다. 실패·재실행 등 사건이 있는 지점으로 바로 이동할 수 있어야 한다. 지난 임무를 이력에서 선택해 같은 방식으로 되감으며, 되감기 중에는 대상으로 나가는 명령을 차단한다. 되감기는 별도 화면이 아니라 3계층 표시 화면의 재생 모드다.</t>
+          <t>마일스톤·태스크 계층의 계약에 하드웨어 어휘가 필드로 들어가지 못하게 하고, 기종 의존 값은 액션 아이템의 파라미터 안에만 둔다. 파라미터 해석 규칙은 대상별 어댑터 프로파일 파일에 두고 화면·모델 코드에 기종 표를 다시 적지 않는다. 새 대상 프로파일을 추가할 때 상위 두 계층의 코드가 바뀌지 않아야 하며, 이를 검증 스크립트로 확인한다.</t>
         </is>
       </c>
       <c r="E37" s="45" t="inlineStr">
         <is>
-          <t>(내부 처리) / 이력 조회: 백엔드→가시화</t>
+          <t>(내부 처리) / 계약 규약</t>
         </is>
       </c>
       <c r="F37" s="43" t="inlineStr">
         <is>
-          <t>사용자 조작 시(이벤트 기반), 이력 목록은 열람 시 조회</t>
+          <t>해당 없음(계약·검증 규약)</t>
         </is>
       </c>
       <c r="G37" s="45" t="inlineStr">
         <is>
-          <t>되감기는 저장된 기록만 읽으므로 새 수신이 필요 없고 주기 개념이 없다. 이력도 확정된 과거라 폴링해도 새 값이 나오지 않아 열람 시 조회가 낭비가 적다. 되감기 중 명령을 차단하는 이유는, 과거 시점을 보고 있는 화면에서 낸 명령이 현재 상태에 적용되면 사람이 의도하지 않은 대상에 나가기 때문이다.</t>
+          <t>합의만으로는 경계가 무너진다. 기존 F4 계약이 좌표를 계약 본문 밖으로 막는 것과 같은 방식으로, 스키마의 추가 속성 금지와 회귀 검증으로 강제한다. 강제 장치가 없으면 편의상 태스크에 기종 필드가 하나씩 붙고, 그 순간 같은 임무 정의를 다른 기종에 재사용할 수 없게 된다.</t>
         </is>
       </c>
       <c r="H37" s="45" t="inlineStr">
         <is>
-          <t>백엔드 서버</t>
+          <t>AI, 백엔드 서버</t>
         </is>
       </c>
       <c r="I37" s="45" t="inlineStr">
         <is>
-          <t>BE-S-01, BE-Q-01</t>
+          <t>BE-C-01, AI-C-15</t>
         </is>
       </c>
       <c r="J37" s="43" t="inlineStr">
@@ -23121,7 +23125,7 @@
     <row r="38">
       <c r="A38" s="43" t="inlineStr">
         <is>
-          <t>VZ-D-05</t>
+          <t>VZ-D-04</t>
         </is>
       </c>
       <c r="B38" s="44" t="inlineStr">
@@ -23131,37 +23135,37 @@
       </c>
       <c r="C38" s="45" t="inlineStr">
         <is>
-          <t>실패 경로 격리</t>
+          <t>시점 복원(되감기)과 임무 이력</t>
         </is>
       </c>
       <c r="D38" s="45" t="inlineStr">
         <is>
-          <t>실패한 노드에서 의존 관계와 파생 관계를 역방향으로 따라가 실패에 관여한 노드 집합만 남기고 나머지를 접는다. 격리 집합에는 근본 원인이 반드시 포함되어야 하며, 축소 정도와 함께 근본 원인 포함 여부를 검증한다. 격리 결과에는 실패 단계와 사유, 판정 주체가 함께 표시된다.</t>
+          <t>보관된 기록을 앞에서부터 접어 임의 시점의 계층 상태를 복원하고, 시간 슬라이더로 그 시점 화면을 표시한다. 실패·재실행 등 사건이 있는 지점으로 바로 이동할 수 있어야 한다. 지난 임무를 이력에서 선택해 같은 방식으로 되감으며, 되감기 중에는 대상으로 나가는 명령을 차단한다. 되감기는 별도 화면이 아니라 3계층 표시 화면의 재생 모드다.</t>
         </is>
       </c>
       <c r="E38" s="45" t="inlineStr">
         <is>
-          <t>(내부 처리)</t>
+          <t>(내부 처리) / 이력 조회: 백엔드→가시화</t>
         </is>
       </c>
       <c r="F38" s="43" t="inlineStr">
         <is>
-          <t>실패 사건 도달 시 즉시 산출</t>
+          <t>사용자 조작 시(이벤트 기반), 이력 목록은 열람 시 조회</t>
         </is>
       </c>
       <c r="G38" s="45" t="inlineStr">
         <is>
-          <t>격리는 보관된 기록 위의 계산이라 외부 수신이 없다. 실패 도달 즉시 산출하는 이유는, 사람이 화면을 보는 시점에 이미 좁혀져 있어야 탐색 시간이 줄기 때문이다. 사후 배치 계산으로 미루면 실패 직후 대응 구간에서는 여전히 전체를 훑게 되어 목적을 잃는다.</t>
+          <t>되감기는 저장된 기록만 읽으므로 새 수신이 필요 없고 주기 개념이 없다. 이력도 확정된 과거라 폴링해도 새 값이 나오지 않아 열람 시 조회가 낭비가 적다. 되감기 중 명령을 차단하는 이유는, 과거 시점을 보고 있는 화면에서 낸 명령이 현재 상태에 적용되면 사람이 의도하지 않은 대상에 나가기 때문이다.</t>
         </is>
       </c>
       <c r="H38" s="45" t="inlineStr">
         <is>
-          <t>AI, 백엔드 서버</t>
+          <t>백엔드 서버</t>
         </is>
       </c>
       <c r="I38" s="45" t="inlineStr">
         <is>
-          <t>BE-X-04 [실패 단계 어휘 합의 필요]</t>
+          <t>BE-S-01, BE-Q-01</t>
         </is>
       </c>
       <c r="J38" s="43" t="inlineStr">
@@ -23179,7 +23183,7 @@
     <row r="39">
       <c r="A39" s="43" t="inlineStr">
         <is>
-          <t>VZ-D-06</t>
+          <t>VZ-D-05</t>
         </is>
       </c>
       <c r="B39" s="44" t="inlineStr">
@@ -23189,37 +23193,37 @@
       </c>
       <c r="C39" s="45" t="inlineStr">
         <is>
-          <t>실행 상태 8종 표시</t>
+          <t>실패 경로 격리</t>
         </is>
       </c>
       <c r="D39" s="45" t="inlineStr">
         <is>
-          <t>노드 상태를 대기·진행·완료·실패·건너뜀·평가 대기·미수행·재실행 8종으로 구분해 표시한다. 특히 조건상 의도적으로 넘긴 '건너뜀'과 선행 실패로 실행 자체가 일어나지 않은 '미수행'을 구분하며, 재실행은 회차를 함께 표시한다. 색만으로 8종을 구분하지 않고 테두리 형태·아이콘·회차 표기를 함께 사용한다.</t>
+          <t>실패한 노드에서 의존 관계와 파생 관계를 역방향으로 따라가 실패에 관여한 노드 집합만 남기고 나머지를 접는다. 격리 집합에는 근본 원인이 반드시 포함되어야 하며, 축소 정도와 함께 근본 원인 포함 여부를 검증한다. 격리 결과에는 실패 단계와 사유, 판정 주체가 함께 표시된다.</t>
         </is>
       </c>
       <c r="E39" s="45" t="inlineStr">
         <is>
-          <t>(내부 처리) / 상태는 VZ-D-02 기록에서 파생</t>
+          <t>(내부 처리)</t>
         </is>
       </c>
       <c r="F39" s="43" t="inlineStr">
         <is>
-          <t>기록 수신 시 갱신(100 ms 병합)</t>
+          <t>실패 사건 도달 시 즉시 산출</t>
         </is>
       </c>
       <c r="G39" s="45" t="inlineStr">
         <is>
-          <t>상태는 기록에서 파생되므로 별도 주기가 없다. 8종으로 나누는 이유는 디버깅에서 '안 돌렸다'와 '못 돌았다'가 완전히 다른 단서이기 때문이다. 둘을 한 색으로 합치면 사람이 실패 원인을 위쪽에서 찾을지 아래쪽에서 찾을지 판단할 근거를 잃는다. 색만으로 8종을 구분하려 하면 색각 접근성에서도 실패한다.</t>
+          <t>격리는 보관된 기록 위의 계산이라 외부 수신이 없다. 실패 도달 즉시 산출하는 이유는, 사람이 화면을 보는 시점에 이미 좁혀져 있어야 탐색 시간이 줄기 때문이다. 사후 배치 계산으로 미루면 실패 직후 대응 구간에서는 여전히 전체를 훑게 되어 목적을 잃는다.</t>
         </is>
       </c>
       <c r="H39" s="45" t="inlineStr">
         <is>
-          <t>백엔드 서버, 하드웨어</t>
+          <t>AI, 백엔드 서버</t>
         </is>
       </c>
       <c r="I39" s="45" t="inlineStr">
         <is>
-          <t>BE-X-03, BE-X-04</t>
+          <t>BE-X-04 [실패 단계 어휘 합의 필요]</t>
         </is>
       </c>
       <c r="J39" s="43" t="inlineStr">
@@ -23237,7 +23241,7 @@
     <row r="40">
       <c r="A40" s="43" t="inlineStr">
         <is>
-          <t>VZ-D-07</t>
+          <t>VZ-D-06</t>
         </is>
       </c>
       <c r="B40" s="44" t="inlineStr">
@@ -23247,37 +23251,37 @@
       </c>
       <c r="C40" s="45" t="inlineStr">
         <is>
-          <t>대상 배정과 대상 상태 조회</t>
+          <t>실행 상태 8종 표시</t>
         </is>
       </c>
       <c r="D40" s="45" t="inlineStr">
         <is>
-          <t>레지스트리의 대상 목록을 화면에 두고 마일스톤에 배정해 하위 태스크의 실행 대상을 정한다. 목록과 노드에는 연결 상태와 주요 지표(전원·링크 품질 등)를 함께 표시하고, 액션 아이템 상세에서는 대상의 상세 상태를 조회한다. 조회 항목은 대상별 어댑터 프로파일이 정의하며 화면 코드에 기종별 항목표를 두지 않는다. 배정된 대상이 실행 불가 상태이면 해당 태스크가 실행 전에도 위험으로 드러나야 한다.</t>
+          <t>노드 상태를 대기·진행·완료·실패·건너뜀·평가 대기·미수행·재실행 8종으로 구분해 표시한다. 특히 조건상 의도적으로 넘긴 '건너뜀'과 선행 실패로 실행 자체가 일어나지 않은 '미수행'을 구분하며, 재실행은 회차를 함께 표시한다. 색만으로 8종을 구분하지 않고 테두리 형태·아이콘·회차 표기를 함께 사용한다.</t>
         </is>
       </c>
       <c r="E40" s="45" t="inlineStr">
         <is>
-          <t>백엔드 레지스트리·상태→가시화</t>
+          <t>(내부 처리) / 상태는 VZ-D-02 기록에서 파생</t>
         </is>
       </c>
       <c r="F40" s="43" t="inlineStr">
         <is>
-          <t>레지스트리는 VZ-I-03과 동일, 상태는 VZ-I-01과 동일(100 ms 병합)</t>
+          <t>기록 수신 시 갱신(100 ms 병합)</t>
         </is>
       </c>
       <c r="G40" s="45" t="inlineStr">
         <is>
-          <t>배정은 사용자 조작이라 주기가 없고, 상태는 이미 구독 중인 값을 재사용하므로 추가 수신이 없다. 실행 전 위험 표시를 요구하는 이유는, 배정 대상이 오프라인인 태스크는 실행하면 반드시 실패하는데 그 사실이 실패 이후에야 드러나면 이 도구가 사후 추적으로만 쓰이기 때문이다.</t>
+          <t>상태는 기록에서 파생되므로 별도 주기가 없다. 8종으로 나누는 이유는 디버깅에서 '안 돌렸다'와 '못 돌았다'가 완전히 다른 단서이기 때문이다. 둘을 한 색으로 합치면 사람이 실패 원인을 위쪽에서 찾을지 아래쪽에서 찾을지 판단할 근거를 잃는다. 색만으로 8종을 구분하려 하면 색각 접근성에서도 실패한다.</t>
         </is>
       </c>
       <c r="H40" s="45" t="inlineStr">
         <is>
-          <t>백엔드 서버, 백엔드 엣지노드, 하드웨어</t>
+          <t>백엔드 서버, 하드웨어</t>
         </is>
       </c>
       <c r="I40" s="45" t="inlineStr">
         <is>
-          <t>HW-C-04, HW-S-07, HW-A-05, BE-C-02, AI-O-04</t>
+          <t>BE-X-03, BE-X-04</t>
         </is>
       </c>
       <c r="J40" s="43" t="inlineStr">
@@ -23295,7 +23299,7 @@
     <row r="41">
       <c r="A41" s="43" t="inlineStr">
         <is>
-          <t>VZ-D-08</t>
+          <t>VZ-D-07</t>
         </is>
       </c>
       <c r="B41" s="44" t="inlineStr">
@@ -23305,37 +23309,37 @@
       </c>
       <c r="C41" s="45" t="inlineStr">
         <is>
-          <t>화면에서의 실행 개입</t>
+          <t>대상 배정과 대상 상태 조회</t>
         </is>
       </c>
       <c r="D41" s="45" t="inlineStr">
         <is>
-          <t>임무 정지·재시작·중단, 실패한 태스크의 파라미터 수정 후 재실행, 액션 아이템 단독 실행, 결함 주입을 화면에서 발행한다. 정지는 하달 중인 액션 아이템까지 끝내고 멈추며 재시작은 멈춘 지점의 태스크부터 이어서 실행한다. 이 조작은 전부 산출 주체를 사람으로 기록에 남기고, 파라미터 수정은 회차를 누적한다. 실제 대상을 움직이지 않고 저장된 기록 위에서 결과만 확인하는 모드를 함께 제공한다.</t>
+          <t>레지스트리의 대상 목록을 화면에 두고 마일스톤에 배정해 하위 태스크의 실행 대상을 정한다. 목록과 노드에는 연결 상태와 주요 지표(전원·링크 품질 등)를 함께 표시하고, 액션 아이템 상세에서는 대상의 상세 상태를 조회한다. 조회 항목은 대상별 어댑터 프로파일이 정의하며 화면 코드에 기종별 항목표를 두지 않는다. 배정된 대상이 실행 불가 상태이면 해당 태스크가 실행 전에도 위험으로 드러나야 한다.</t>
         </is>
       </c>
       <c r="E41" s="45" t="inlineStr">
         <is>
-          <t>가시화→백엔드→대상</t>
+          <t>백엔드 레지스트리·상태→가시화</t>
         </is>
       </c>
       <c r="F41" s="43" t="inlineStr">
         <is>
-          <t>이벤트 기반(사용자 조작 시 즉시)</t>
+          <t>레지스트리는 VZ-I-03과 동일, 상태는 VZ-I-01과 동일(100 ms 병합)</t>
         </is>
       </c>
       <c r="G41" s="45" t="inlineStr">
         <is>
-          <t>사용자 조작은 비주기다. 정지를 액션 아이템 경계에서만 허용하는 이유는, 물리 동작 중간에 끊으면 대상이 어중간한 자세로 남고 그 상태가 기록으로 설명되지 않기 때문이다. 사람의 개입이 기록에 빠지면 되감기와 경로 격리가 잘못된 결론을 낸다 — 개입 기록은 성능이 아니라 도구의 신뢰성 문제라 예외를 두지 않는다.</t>
+          <t>배정은 사용자 조작이라 주기가 없고, 상태는 이미 구독 중인 값을 재사용하므로 추가 수신이 없다. 실행 전 위험 표시를 요구하는 이유는, 배정 대상이 오프라인인 태스크는 실행하면 반드시 실패하는데 그 사실이 실패 이후에야 드러나면 이 도구가 사후 추적으로만 쓰이기 때문이다.</t>
         </is>
       </c>
       <c r="H41" s="45" t="inlineStr">
         <is>
-          <t>백엔드 서버, 하드웨어</t>
+          <t>백엔드 서버, 백엔드 엣지노드, 하드웨어</t>
         </is>
       </c>
       <c r="I41" s="45" t="inlineStr">
         <is>
-          <t>HW-C-06, HW-R-05, BE-A-01, BE-X-01, BE-X-02</t>
+          <t>HW-C-04, HW-S-07, HW-A-05, BE-C-02, AI-O-04</t>
         </is>
       </c>
       <c r="J41" s="43" t="inlineStr">
@@ -23353,47 +23357,47 @@
     <row r="42">
       <c r="A42" s="43" t="inlineStr">
         <is>
-          <t>VZ-G-01</t>
+          <t>VZ-D-08</t>
         </is>
       </c>
       <c r="B42" s="44" t="inlineStr">
         <is>
-          <t>생성</t>
+          <t>디버깅</t>
         </is>
       </c>
       <c r="C42" s="45" t="inlineStr">
         <is>
-          <t>발화 텍스트 → 마일스톤 분리</t>
+          <t>화면에서의 실행 개입</t>
         </is>
       </c>
       <c r="D42" s="45" t="inlineStr">
         <is>
-          <t>STT로 변환된 발화 텍스트(VZ-L-01)를 임무 하나와 마일스톤 목록으로 분리한다. 마일스톤은 완전히 추상이며 하드웨어 어휘를 포함하지 않는다(VZ-D-03). 분리 결과는 제안 상태로 표시하고 사용자가 수락해야 하위 생성으로 넘어간다(VZ-L-02). 분리에 사용한 생성기 버전과 입력 텍스트를 근거로 함께 남겨 실패 시 이 단계까지 역추적할 수 있게 한다. 대상 호칭은 레지스트리의 표시 이름·별칭으로 해석한다. 로컬 LLM이 없거나 무응답이면 이 기능만 비활성화하고 수동 입력 경로를 남긴다(VZ-C-02).</t>
+          <t>임무 정지·재시작·중단, 실패한 태스크의 파라미터 수정 후 재실행, 액션 아이템 단독 실행, 결함 주입을 화면에서 발행한다. 정지는 하달 중인 액션 아이템까지 끝내고 멈추며 재시작은 멈춘 지점의 태스크부터 이어서 실행한다. 이 조작은 전부 산출 주체를 사람으로 기록에 남기고, 파라미터 수정은 회차를 누적한다. 실제 대상을 움직이지 않고 저장된 기록 위에서 결과만 확인하는 모드를 함께 제공한다.</t>
         </is>
       </c>
       <c r="E42" s="45" t="inlineStr">
         <is>
-          <t>가시화 내부(로컬 LLM)→가시화</t>
+          <t>가시화→백엔드→대상</t>
         </is>
       </c>
       <c r="F42" s="43" t="inlineStr">
         <is>
-          <t>발화 수락 시 1회(이벤트 기반), 응답은 스트리밍 표시</t>
+          <t>이벤트 기반(사용자 조작 시 즉시)</t>
         </is>
       </c>
       <c r="G42" s="45" t="inlineStr">
         <is>
-          <t>발화는 비주기이므로 생성도 비주기다. 스트리밍 표시하는 이유는 분리 결과를 전부 받은 뒤 한 번에 띄우면 체감 지연이 커지기 때문이다. 이 단계를 별도 요구사항으로 세우는 이유는, 마일스톤 분리 자체가 실패 지점이 될 수 있어서다 — 잘못 쪼갠 마일스톤은 하위 전체를 무너뜨리므로 생성 근거가 기록에 남아야 역추적이 최상위까지 닿는다.</t>
+          <t>사용자 조작은 비주기다. 정지를 액션 아이템 경계에서만 허용하는 이유는, 물리 동작 중간에 끊으면 대상이 어중간한 자세로 남고 그 상태가 기록으로 설명되지 않기 때문이다. 사람의 개입이 기록에 빠지면 되감기와 경로 격리가 잘못된 결론을 낸다 — 개입 기록은 성능이 아니라 도구의 신뢰성 문제라 예외를 두지 않는다.</t>
         </is>
       </c>
       <c r="H42" s="45" t="inlineStr">
         <is>
-          <t>AI, 백엔드 서버</t>
+          <t>백엔드 서버, 하드웨어</t>
         </is>
       </c>
       <c r="I42" s="45" t="inlineStr">
         <is>
-          <t>AI-C-09, AI-C-16, BE-Q-03 [구 AI-D-01 삭제분 인수]</t>
+          <t>HW-C-06, HW-R-05, BE-A-01, BE-X-01, BE-X-02</t>
         </is>
       </c>
       <c r="J42" s="43" t="inlineStr">
@@ -23411,7 +23415,7 @@
     <row r="43">
       <c r="A43" s="43" t="inlineStr">
         <is>
-          <t>VZ-G-02</t>
+          <t>VZ-G-01</t>
         </is>
       </c>
       <c r="B43" s="44" t="inlineStr">
@@ -23421,12 +23425,12 @@
       </c>
       <c r="C43" s="45" t="inlineStr">
         <is>
-          <t>마일스톤 → 태스크 생성</t>
+          <t>발화 텍스트 → 마일스톤 분리</t>
         </is>
       </c>
       <c r="D43" s="45" t="inlineStr">
         <is>
-          <t>수락된 마일스톤마다 수행 가능한 태스크를 생성한다. 태스크는 일렬이 아니라 deps로 분기·합류를 갖는 DAG이며, 하나의 마일스톤에 여러 태스크가 생길 수 있다. 태스크 계층까지는 적용 대상과 무관한 범용 단위이고 하드웨어 어휘를 포함하지 않는다. 생성 방식은 특정 LLM이나 계획 라이브러리를 필수로 하지 않으며, 검증 가능한 행동 단위와 조건 표현을 사용한다. 확인 가능한 정보 범위를 넘는 계획을 만들지 않고 부족한 근거를 명시한다.</t>
+          <t>STT로 변환된 발화 텍스트(VZ-L-01)를 임무 하나와 마일스톤 목록으로 분리한다. 마일스톤은 완전히 추상이며 하드웨어 어휘를 포함하지 않는다(VZ-D-03). 분리 결과는 제안 상태로 표시하고 사용자가 수락해야 하위 생성으로 넘어간다(VZ-L-02). 분리에 사용한 생성기 버전과 입력 텍스트를 근거로 함께 남겨 실패 시 이 단계까지 역추적할 수 있게 한다. 대상 호칭은 레지스트리의 표시 이름·별칭으로 해석한다. 로컬 LLM이 없거나 무응답이면 이 기능만 비활성화하고 수동 입력 경로를 남긴다(VZ-C-02).</t>
         </is>
       </c>
       <c r="E43" s="45" t="inlineStr">
@@ -23436,22 +23440,22 @@
       </c>
       <c r="F43" s="43" t="inlineStr">
         <is>
-          <t>마일스톤 수락 시 1회(이벤트 기반)</t>
+          <t>발화 수락 시 1회(이벤트 기반), 응답은 스트리밍 표시</t>
         </is>
       </c>
       <c r="G43" s="45" t="inlineStr">
         <is>
-          <t>마일스톤과 마찬가지로 사용자 수락에 종속되어 주기가 없다. DAG로 만드는 이유는 회의록 §4-3의 'flow → process — 여러 갈래가 다시 하나의 박스로 모이는 형태'를 표현해야 하기 때문이고, 일렬 인덱스로 두면 분기·합류가 사라져 실패 경로 역추적(VZ-D-05)이 성립하지 않는다.</t>
+          <t>발화는 비주기이므로 생성도 비주기다. 스트리밍 표시하는 이유는 분리 결과를 전부 받은 뒤 한 번에 띄우면 체감 지연이 커지기 때문이다. 이 단계를 별도 요구사항으로 세우는 이유는, 마일스톤 분리 자체가 실패 지점이 될 수 있어서다 — 잘못 쪼갠 마일스톤은 하위 전체를 무너뜨리므로 생성 근거가 기록에 남아야 역추적이 최상위까지 닿는다.</t>
         </is>
       </c>
       <c r="H43" s="45" t="inlineStr">
         <is>
-          <t>AI, 백엔드 서버, 하드웨어</t>
+          <t>AI, 백엔드 서버</t>
         </is>
       </c>
       <c r="I43" s="45" t="inlineStr">
         <is>
-          <t>AI-C-09, BE-X-04 [구 AI-D-01 삭제분 인수]</t>
+          <t>AI-C-09, AI-C-16, BE-Q-03 [구 AI-D-01 삭제분 인수]</t>
         </is>
       </c>
       <c r="J43" s="43" t="inlineStr">
@@ -23469,7 +23473,7 @@
     <row r="44">
       <c r="A44" s="43" t="inlineStr">
         <is>
-          <t>VZ-G-03</t>
+          <t>VZ-G-02</t>
         </is>
       </c>
       <c r="B44" s="44" t="inlineStr">
@@ -23479,37 +23483,37 @@
       </c>
       <c r="C44" s="45" t="inlineStr">
         <is>
-          <t>태스크 검증</t>
+          <t>마일스톤 → 태스크 생성</t>
         </is>
       </c>
       <c r="D44" s="45" t="inlineStr">
         <is>
-          <t>생성된 태스크를 실행 전에 검증한다. 구조, 순서, 의존 관계의 순환 여부, 사전조건, 자원 조건, 배정된 대상의 수행 가능성을 확인한다. 검증 기능은 생성 기능과 분리해 동일 입력에서 재현 가능한 결과를 제공한다. 확인할 수 없는 필수 조건이 있으면 해당 태스크만 실행 불가로 표시하고 부족한 근거를 명시한다. 검증 결과는 VZ-U-07의 승인 화면과 VZ-L-03의 2단 확인 ②단계 표시에 사용한다.</t>
+          <t>수락된 마일스톤마다 수행 가능한 태스크를 생성한다. 태스크는 일렬이 아니라 deps로 분기·합류를 갖는 DAG이며, 하나의 마일스톤에 여러 태스크가 생길 수 있다. 태스크 계층까지는 적용 대상과 무관한 범용 단위이고 하드웨어 어휘를 포함하지 않는다. 생성 방식은 특정 LLM이나 계획 라이브러리를 필수로 하지 않으며, 검증 가능한 행동 단위와 조건 표현을 사용한다. 확인 가능한 정보 범위를 넘는 계획을 만들지 않고 부족한 근거를 명시한다.</t>
         </is>
       </c>
       <c r="E44" s="45" t="inlineStr">
         <is>
-          <t>(내부 처리)</t>
+          <t>가시화 내부(로컬 LLM)→가시화</t>
         </is>
       </c>
       <c r="F44" s="43" t="inlineStr">
         <is>
-          <t>태스크 생성 직후 1회 + 배정 변경 시 재검증</t>
+          <t>마일스톤 수락 시 1회(이벤트 기반)</t>
         </is>
       </c>
       <c r="G44" s="45" t="inlineStr">
         <is>
-          <t>검증은 생성 결과에 종속되므로 주기가 없다. 배정이 바뀌면 다시 검증하는 이유는 대상이 달라지면 수행 가능성 판정이 달라지기 때문이다(VZ-D-07). 생성과 같은 사람이 만들더라도 모듈은 분리한다 — 생성기가 스스로를 검증하면 같은 오해를 두 번 반복할 뿐이고, 재현 가능한 검증이라야 실패했을 때 생성 탓인지 검증 탓인지 가를 수 있다.</t>
+          <t>마일스톤과 마찬가지로 사용자 수락에 종속되어 주기가 없다. DAG로 만드는 이유는 회의록 §4-3의 'flow → process — 여러 갈래가 다시 하나의 박스로 모이는 형태'를 표현해야 하기 때문이고, 일렬 인덱스로 두면 분기·합류가 사라져 실패 경로 역추적(VZ-D-05)이 성립하지 않는다.</t>
         </is>
       </c>
       <c r="H44" s="45" t="inlineStr">
         <is>
-          <t>백엔드 서버, 하드웨어</t>
+          <t>AI, 백엔드 서버, 하드웨어</t>
         </is>
       </c>
       <c r="I44" s="45" t="inlineStr">
         <is>
-          <t>BE-X-04, HW-A-05 [구 AI-D-02 삭제분 인수]</t>
+          <t>AI-C-09, BE-X-04 [구 AI-D-01 삭제분 인수]</t>
         </is>
       </c>
       <c r="J44" s="43" t="inlineStr">
@@ -23527,7 +23531,7 @@
     <row r="45">
       <c r="A45" s="43" t="inlineStr">
         <is>
-          <t>VZ-G-04</t>
+          <t>VZ-G-03</t>
         </is>
       </c>
       <c r="B45" s="44" t="inlineStr">
@@ -23537,27 +23541,27 @@
       </c>
       <c r="C45" s="45" t="inlineStr">
         <is>
-          <t>태스크 → 액션 아이템 전개</t>
+          <t>태스크 검증</t>
         </is>
       </c>
       <c r="D45" s="45" t="inlineStr">
         <is>
-          <t>검증을 통과한 태스크를 배정된 대상의 어댑터 프로파일에 따라 실제 명령값을 갖는 액션 아이템으로 전개한다. 기종 의존 값과 그 해석 규칙은 어댑터 프로파일에만 두고 상위 계층과 화면 코드에 기종별 표를 두지 않는다(VZ-D-03). 같은 태스크가 다른 대상에 배정되면 상위 정의는 그대로 두고 전개 결과만 달라져야 한다. 전개 중 새 태스크가 필요해지면 파생 출처를 유지한 채 상위로 되돌린다.</t>
+          <t>생성된 태스크를 실행 전에 검증한다. 구조, 순서, 의존 관계의 순환 여부, 사전조건, 자원 조건, 배정된 대상의 수행 가능성을 확인한다. 검증 기능은 생성 기능과 분리해 동일 입력에서 재현 가능한 결과를 제공한다. 확인할 수 없는 필수 조건이 있으면 해당 태스크만 실행 불가로 표시하고 부족한 근거를 명시한다. 검증 결과는 VZ-U-07의 승인 화면과 VZ-L-03의 2단 확인 ②단계 표시에 사용한다.</t>
         </is>
       </c>
       <c r="E45" s="45" t="inlineStr">
         <is>
-          <t>(내부 처리) / 발행은 VZ-O-01</t>
+          <t>(내부 처리)</t>
         </is>
       </c>
       <c r="F45" s="43" t="inlineStr">
         <is>
-          <t>태스크 검증 통과 후 1회 + 배정 변경 시 재전개</t>
+          <t>태스크 생성 직후 1회 + 배정 변경 시 재검증</t>
         </is>
       </c>
       <c r="G45" s="45" t="inlineStr">
         <is>
-          <t>전개는 검증 결과와 배정에 종속되어 주기가 없다. 실행 직전이 아니라 검증 직후에 전개하는 이유는, 전개 결과를 사용자가 승인 화면에서 미리 볼 수 있어야 하고(VZ-U-07) 전개 단계에서 드러나는 불가능(예: 대상이 지원하지 않는 동작)을 실행 전에 잡아야 하기 때문이다. 실제 디바이스 명령으로의 번역은 여전히 백엔드가 수행한다(VZ-O-01).</t>
+          <t>검증은 생성 결과에 종속되므로 주기가 없다. 배정이 바뀌면 다시 검증하는 이유는 대상이 달라지면 수행 가능성 판정이 달라지기 때문이다(VZ-D-07). 생성과 같은 사람이 만들더라도 모듈은 분리한다 — 생성기가 스스로를 검증하면 같은 오해를 두 번 반복할 뿐이고, 재현 가능한 검증이라야 실패했을 때 생성 탓인지 검증 탓인지 가를 수 있다.</t>
         </is>
       </c>
       <c r="H45" s="45" t="inlineStr">
@@ -23567,7 +23571,7 @@
       </c>
       <c r="I45" s="45" t="inlineStr">
         <is>
-          <t>HW-R-05, HW-A-02, BE-A-01, BE-A-02, AI-C-15</t>
+          <t>BE-X-04, HW-A-05 [구 AI-D-02 삭제분 인수]</t>
         </is>
       </c>
       <c r="J45" s="43" t="inlineStr">
@@ -23585,7 +23589,7 @@
     <row r="46" s="54">
       <c r="A46" s="43" t="inlineStr">
         <is>
-          <t>VZ-G-05</t>
+          <t>VZ-G-04</t>
         </is>
       </c>
       <c r="B46" s="44" t="inlineStr">
@@ -23595,37 +23599,37 @@
       </c>
       <c r="C46" s="45" t="inlineStr">
         <is>
-          <t>평가 기준 생성 및 판정</t>
+          <t>태스크 → 액션 아이템 전개</t>
         </is>
       </c>
       <c r="D46" s="45" t="inlineStr">
         <is>
-          <t>태스크마다 종료를 판정할 평가 기준을 생성하고, 실행 결과를 그 기준으로 판정한다. 태스크는 실행 완료가 아니라 평가 통과로만 종료되며 평가 전에는 별도 상태로 표시한다(VZ-D-06). 기준은 측정 가능한 항목과 임계로 표현하고, 판정에는 사용한 근거와 판정 주체를 함께 남긴다. 판정에 필요한 값이 도달하지 않으면 통과로 승격하지 않고 근거 부족을 드러낸다. 규칙으로 판정할 수 없는 항목은 사람 판정으로 넘긴다.</t>
+          <t>검증을 통과한 태스크를 배정된 대상의 어댑터 프로파일에 따라 실제 명령값을 갖는 액션 아이템으로 전개한다. 기종 의존 값과 그 해석 규칙은 어댑터 프로파일에만 두고 상위 계층과 화면 코드에 기종별 표를 두지 않는다(VZ-D-03). 같은 태스크가 다른 대상에 배정되면 상위 정의는 그대로 두고 전개 결과만 달라져야 한다. 전개 중 새 태스크가 필요해지면 파생 출처를 유지한 채 상위로 되돌린다.</t>
         </is>
       </c>
       <c r="E46" s="45" t="inlineStr">
         <is>
-          <t>(내부 처리) / 판정 입력은 상태·명령 결과 수신</t>
+          <t>(내부 처리) / 발행은 VZ-O-01</t>
         </is>
       </c>
       <c r="F46" s="43" t="inlineStr">
         <is>
-          <t>태스크 실행 종료 시 1회, 근거 미도달 시 대기</t>
+          <t>태스크 검증 통과 후 1회 + 배정 변경 시 재전개</t>
         </is>
       </c>
       <c r="G46" s="45" t="inlineStr">
         <is>
-          <t>판정은 실행 종료 이벤트에 종속되어 주기가 없다. 근거가 도달하지 않았을 때 대기하는 이유는, 시간이 지났다는 이유로 통과시키면 '평가가 끝나야 태스크가 끝난다'는 회의 합의가 무의미해지기 때문이다. 판정 주체를 남기는 이유는 규칙 판정과 사람 판정이 섞일 때 사후에 둘을 갈라야 하기 때문이며, 이는 VZ-D-02의 산출 주체 기록과 같은 이유다.</t>
+          <t>전개는 검증 결과와 배정에 종속되어 주기가 없다. 실행 직전이 아니라 검증 직후에 전개하는 이유는, 전개 결과를 사용자가 승인 화면에서 미리 볼 수 있어야 하고(VZ-U-07) 전개 단계에서 드러나는 불가능(예: 대상이 지원하지 않는 동작)을 실행 전에 잡아야 하기 때문이다. 실제 디바이스 명령으로의 번역은 여전히 백엔드가 수행한다(VZ-O-01).</t>
         </is>
       </c>
       <c r="H46" s="45" t="inlineStr">
         <is>
-          <t>AI, 백엔드 서버, 하드웨어</t>
+          <t>백엔드 서버, 하드웨어</t>
         </is>
       </c>
       <c r="I46" s="45" t="inlineStr">
         <is>
-          <t>HW-A-04, HW-R-05, AI-S-03, BE-X-03 [구 AI-D-02 삭제분 인수]</t>
+          <t>HW-R-05, HW-A-02, BE-A-01, BE-A-02, AI-C-15</t>
         </is>
       </c>
       <c r="J46" s="43" t="inlineStr">
@@ -23643,47 +23647,47 @@
     <row r="47">
       <c r="A47" s="43" t="inlineStr">
         <is>
-          <t>VZ-N-01</t>
+          <t>VZ-G-05</t>
         </is>
       </c>
       <c r="B47" s="44" t="inlineStr">
         <is>
-          <t>캔버스</t>
+          <t>생성</t>
         </is>
       </c>
       <c r="C47" s="45" t="inlineStr">
         <is>
-          <t>뷰 노드 팔레트</t>
+          <t>평가 기준 생성 및 판정</t>
         </is>
       </c>
       <c r="D47" s="45" t="inlineStr">
         <is>
-          <t>사용자는 노드 캔버스 상단 팔레트에서 뷰 노드(장치·위험 / 제어 / 지표 / 영상)를 선택해 캔버스에 생성할 수 있어야 한다. 팔레트 목록은 등록된 뷰 노드 렌더러에서 자동 구성되며, 개발자가 팔레트 코드를 고쳐 노드를 추가하는 일이 없어야 한다.</t>
+          <t>태스크마다 종료를 판정할 평가 기준을 생성하고, 실행 결과를 그 기준으로 판정한다. 태스크는 실행 완료가 아니라 평가 통과로만 종료되며 평가 전에는 별도 상태로 표시한다(VZ-D-06). 기준은 측정 가능한 항목과 임계로 표현하고, 판정에는 사용한 근거와 판정 주체를 함께 남긴다. 판정에 필요한 값이 도달하지 않으면 통과로 승격하지 않고 근거 부족을 드러낸다. 규칙으로 판정할 수 없는 항목은 사람 판정으로 넘긴다.</t>
         </is>
       </c>
       <c r="E47" s="45" t="inlineStr">
         <is>
-          <t>(내부 처리)</t>
+          <t>(내부 처리) / 판정 입력은 상태·명령 결과 수신</t>
         </is>
       </c>
       <c r="F47" s="43" t="inlineStr">
         <is>
-          <t>사용자 조작 시(이벤트 기반)</t>
+          <t>태스크 실행 종료 시 1회, 근거 미도달 시 대기</t>
         </is>
       </c>
       <c r="G47" s="45" t="inlineStr">
         <is>
-          <t>노드 생성은 사용자 조작에 종속되어 주기 개념이 없다. 팔레트 목록을 렌더러 등록에서 유도하는 이유는, 손으로 적은 목록과 실제 렌더러가 갈라지면 눌러도 아무것도 안 나오는 버튼이 생기기 때문이다(F10 REQ-1003과 같은 이유).</t>
+          <t>판정은 실행 종료 이벤트에 종속되어 주기가 없다. 근거가 도달하지 않았을 때 대기하는 이유는, 시간이 지났다는 이유로 통과시키면 '평가가 끝나야 태스크가 끝난다'는 회의 합의가 무의미해지기 때문이다. 판정 주체를 남기는 이유는 규칙 판정과 사람 판정이 섞일 때 사후에 둘을 갈라야 하기 때문이며, 이는 VZ-D-02의 산출 주체 기록과 같은 이유다.</t>
         </is>
       </c>
       <c r="H47" s="45" t="inlineStr">
         <is>
-          <t>(가시화 내부)</t>
+          <t>AI, 백엔드 서버, 하드웨어</t>
         </is>
       </c>
       <c r="I47" s="45" t="inlineStr">
         <is>
-          <t>상대 파트 없음 — 화면 구성이라 정상</t>
+          <t>HW-A-04, HW-R-05, AI-S-03, BE-X-03 [구 AI-D-02 삭제분 인수]</t>
         </is>
       </c>
       <c r="J47" s="43" t="inlineStr">
@@ -23693,19 +23697,15 @@
       </c>
       <c r="K47" s="37" t="inlineStr">
         <is>
-          <t>노드 캔버스 · 팔레트</t>
-        </is>
-      </c>
-      <c r="L47" s="37" t="inlineStr">
-        <is>
-          <t>v1.1 신설. 가시화 내부 화면 구성이라 상대 파트가 없는 것이 정상이다 — 삭제된 VZ-U-04(상대 없음)와 달리 실행에 개입하지 않으므로 상대가 필요 없다.</t>
-        </is>
-      </c>
+          <t>노드 캔버스 · 실행 노드</t>
+        </is>
+      </c>
+      <c r="L47" s="37" t="n"/>
     </row>
     <row r="48">
       <c r="A48" s="43" t="inlineStr">
         <is>
-          <t>VZ-N-02</t>
+          <t>VZ-N-01</t>
         </is>
       </c>
       <c r="B48" s="44" t="inlineStr">
@@ -23715,37 +23715,37 @@
       </c>
       <c r="C48" s="45" t="inlineStr">
         <is>
-          <t>뷰 노드 연결(범위 지정)</t>
+          <t>뷰 노드 팔레트</t>
         </is>
       </c>
       <c r="D48" s="45" t="inlineStr">
         <is>
-          <t>뷰 노드를 태스크 노드에 연결하면 그 태스크의 대상 장비·구역·실행 구간이 자동으로 해당 뷰 노드의 조회 범위가 되어야 한다. 연결하지 않은 전역 노드도 허용하며, 연결된 노드와 전역 노드는 화면에서 구별되어야 한다.</t>
+          <t>사용자는 노드 캔버스 상단 팔레트에서 뷰 노드(장치·위험 / 제어 / 지표 / 영상)를 선택해 캔버스에 생성할 수 있어야 한다. 팔레트 목록은 등록된 뷰 노드 렌더러에서 자동 구성되며, 개발자가 팔레트 코드를 고쳐 노드를 추가하는 일이 없어야 한다.</t>
         </is>
       </c>
       <c r="E48" s="45" t="inlineStr">
         <is>
-          <t>(내부 처리) / 실제 조회는 VZ-I-03·I-04·I-05·I-06 경로</t>
+          <t>(내부 처리)</t>
         </is>
       </c>
       <c r="F48" s="43" t="inlineStr">
         <is>
-          <t>연결·해제 시 1회(이벤트 기반). 이후 조회는 각 수신 요구사항의 주기를 따른다</t>
+          <t>사용자 조작 시(이벤트 기반)</t>
         </is>
       </c>
       <c r="G48" s="45" t="inlineStr">
         <is>
-          <t>연결 자체는 사용자 조작이라 주기가 없다. 범위를 연결에서 유도하는 이유는, 탭 시절 사용자가 대상과 시간을 화면마다 손으로 다시 고르던 일을 없애기 위해서다.</t>
+          <t>노드 생성은 사용자 조작에 종속되어 주기 개념이 없다. 팔레트 목록을 렌더러 등록에서 유도하는 이유는, 손으로 적은 목록과 실제 렌더러가 갈라지면 눌러도 아무것도 안 나오는 버튼이 생기기 때문이다(F10 REQ-1003과 같은 이유).</t>
         </is>
       </c>
       <c r="H48" s="45" t="inlineStr">
         <is>
-          <t>백엔드 서버</t>
+          <t>(가시화 내부)</t>
         </is>
       </c>
       <c r="I48" s="45" t="inlineStr">
         <is>
-          <t>VZ-I-03(구역·대상), VZ-I-04·I-05·I-06(조회 경로)</t>
+          <t>상대 파트 없음 — 화면 구성이라 정상</t>
         </is>
       </c>
       <c r="J48" s="43" t="inlineStr">
@@ -23755,19 +23755,19 @@
       </c>
       <c r="K48" s="37" t="inlineStr">
         <is>
-          <t>노드 캔버스 · 연결</t>
+          <t>노드 캔버스 · 팔레트</t>
         </is>
       </c>
       <c r="L48" s="37" t="inlineStr">
         <is>
-          <t>v1.1 신설. 뷰 노드 연결은 deps 가 아니다 — 실행 순서 엣지와 섞으면 깊이 계산에 순환이 생겨 배치가 깨진다(정의서 3.1 「구조상 지켜야 하는 것」 4).</t>
+          <t>v1.1 신설. 가시화 내부 화면 구성이라 상대 파트가 없는 것이 정상이다 — 삭제된 VZ-U-04(상대 없음)와 달리 실행에 개입하지 않으므로 상대가 필요 없다.</t>
         </is>
       </c>
     </row>
     <row r="49" s="54">
       <c r="A49" s="43" t="inlineStr">
         <is>
-          <t>VZ-N-03</t>
+          <t>VZ-N-02</t>
         </is>
       </c>
       <c r="B49" s="44" t="inlineStr">
@@ -23777,27 +23777,27 @@
       </c>
       <c r="C49" s="45" t="inlineStr">
         <is>
-          <t>뷰 노드 시간 범위 일치</t>
+          <t>뷰 노드 연결(범위 지정)</t>
         </is>
       </c>
       <c r="D49" s="45" t="inlineStr">
         <is>
-          <t>노드 캔버스의 모든 뷰 노드는 같은 재생 머리(VZ-D-04 되감기)를 기준으로 값을 표시해야 한다. 한 화면 안에서 어떤 노드는 과거를, 어떤 노드는 현재를 보이면 안 된다.</t>
+          <t>뷰 노드를 태스크 노드에 연결하면 그 태스크의 대상 장비·구역·실행 구간이 자동으로 해당 뷰 노드의 조회 범위가 되어야 한다. 연결하지 않은 전역 노드도 허용하며, 연결된 노드와 전역 노드는 화면에서 구별되어야 한다.</t>
         </is>
       </c>
       <c r="E49" s="45" t="inlineStr">
         <is>
-          <t>(내부 처리) / 재생 머리는 VZ-D-04에서 파생</t>
+          <t>(내부 처리) / 실제 조회는 VZ-I-03·I-04·I-05·I-06 경로</t>
         </is>
       </c>
       <c r="F49" s="43" t="inlineStr">
         <is>
-          <t>재생 머리 이동 시 갱신(이벤트 기반)</t>
+          <t>연결·해제 시 1회(이벤트 기반). 이후 조회는 각 수신 요구사항의 주기를 따른다</t>
         </is>
       </c>
       <c r="G49" s="45" t="inlineStr">
         <is>
-          <t>재생 머리는 사용자 조작과 기록 수신에 종속되므로 별도 주기가 없다. 노드마다 기준 시각이 다르면 「지금 무엇이 어디서 일어나는지」를 한 화면에서 읽을 수 없어, 탭을 없앤 이유 자체가 무너진다.</t>
+          <t>연결 자체는 사용자 조작이라 주기가 없다. 범위를 연결에서 유도하는 이유는, 탭 시절 사용자가 대상과 시간을 화면마다 손으로 다시 고르던 일을 없애기 위해서다.</t>
         </is>
       </c>
       <c r="H49" s="45" t="inlineStr">
@@ -23807,7 +23807,7 @@
       </c>
       <c r="I49" s="45" t="inlineStr">
         <is>
-          <t>VZ-D-02(기록), VZ-D-04(되감기)</t>
+          <t>VZ-I-03(구역·대상), VZ-I-04·I-05·I-06(조회 경로)</t>
         </is>
       </c>
       <c r="J49" s="43" t="inlineStr">
@@ -23817,19 +23817,19 @@
       </c>
       <c r="K49" s="37" t="inlineStr">
         <is>
-          <t>노드 캔버스 · 공통</t>
+          <t>노드 캔버스 · 연결</t>
         </is>
       </c>
       <c r="L49" s="37" t="inlineStr">
         <is>
-          <t>v1.1 신설. 되감기 중 명령 차단(REQ-1405)은 뷰 노드에도 그대로 적용된다.</t>
+          <t>v1.1 신설. 뷰 노드 연결은 deps 가 아니다 — 실행 순서 엣지와 섞으면 깊이 계산에 순환이 생겨 배치가 깨진다(정의서 3.1 「구조상 지켜야 하는 것」 4).</t>
         </is>
       </c>
     </row>
     <row r="50" s="54">
       <c r="A50" s="43" t="inlineStr">
         <is>
-          <t>VZ-N-04</t>
+          <t>VZ-N-03</t>
         </is>
       </c>
       <c r="B50" s="44" t="inlineStr">
@@ -23839,37 +23839,37 @@
       </c>
       <c r="C50" s="45" t="inlineStr">
         <is>
-          <t>캔버스 구성 보존</t>
+          <t>뷰 노드 시간 범위 일치</t>
         </is>
       </c>
       <c r="D50" s="45" t="inlineStr">
         <is>
-          <t>캔버스 구성(놓인 뷰 노드·위치·연결)은 마일스톤별로 보존되며 새로고침·재접속 후에도 유지되어야 한다. 대본이 기본 구성을 제공하면 첫 진입 시 그것으로 시작하고, 사용자가 바꾼 뒤에는 사용자 구성이 우선한다. 기본 구성으로 되돌리는 수단을 화면에 두어야 한다.</t>
+          <t>노드 캔버스의 모든 뷰 노드는 같은 재생 머리(VZ-D-04 되감기)를 기준으로 값을 표시해야 한다. 한 화면 안에서 어떤 노드는 과거를, 어떤 노드는 현재를 보이면 안 된다.</t>
         </is>
       </c>
       <c r="E50" s="45" t="inlineStr">
         <is>
-          <t>(내부 처리) / 기본 구성은 대본 사이드카에서 로드</t>
+          <t>(내부 처리) / 재생 머리는 VZ-D-04에서 파생</t>
         </is>
       </c>
       <c r="F50" s="43" t="inlineStr">
         <is>
-          <t>구성 변경 시 즉시 저장(이벤트 기반), 로드는 진입 시 1회</t>
+          <t>재생 머리 이동 시 갱신(이벤트 기반)</t>
         </is>
       </c>
       <c r="G50" s="45" t="inlineStr">
         <is>
-          <t>구성 변경은 사용자 조작이라 주기가 없다. 새로고침에 날아가면 사용자가 짜 놓은 화면을 매번 다시 만들어야 한다 — VZ-I-02(재접속 시 현재값 복원)가 데이터에 대해 세운 원칙을 화면 구성에도 적용한다.</t>
+          <t>재생 머리는 사용자 조작과 기록 수신에 종속되므로 별도 주기가 없다. 노드마다 기준 시각이 다르면 「지금 무엇이 어디서 일어나는지」를 한 화면에서 읽을 수 없어, 탭을 없앤 이유 자체가 무너진다.</t>
         </is>
       </c>
       <c r="H50" s="45" t="inlineStr">
         <is>
-          <t>(가시화 내부)</t>
+          <t>백엔드 서버</t>
         </is>
       </c>
       <c r="I50" s="45" t="inlineStr">
         <is>
-          <t>상대 파트 없음 — 화면 구성이라 정상</t>
+          <t>VZ-D-02(기록), VZ-D-04(되감기)</t>
         </is>
       </c>
       <c r="J50" s="43" t="inlineStr">
@@ -23884,73 +23884,134 @@
       </c>
       <c r="L50" s="37" t="inlineStr">
         <is>
-          <t>v1.1 신설. 3층(기본 구성=대본 사이드카 / 사용자 구성=localStorage / 되돌리기 버튼). 좌표는 대본 계약이 아니라 사이드카에 둔다 — F10 REQ-1002와 같은 원칙. 임무 전체 보기는 __mission__ 별도 슬롯.</t>
+          <t>v1.1 신설. 되감기 중 명령 차단(REQ-1405)은 뷰 노드에도 그대로 적용된다.</t>
         </is>
       </c>
     </row>
     <row r="51" s="54">
       <c r="A51" s="43" t="inlineStr">
         <is>
+          <t>VZ-N-04</t>
+        </is>
+      </c>
+      <c r="B51" s="44" t="inlineStr">
+        <is>
+          <t>캔버스</t>
+        </is>
+      </c>
+      <c r="C51" s="45" t="inlineStr">
+        <is>
+          <t>캔버스 구성 보존</t>
+        </is>
+      </c>
+      <c r="D51" s="45" t="inlineStr">
+        <is>
+          <t>캔버스 구성(놓인 뷰 노드·위치·연결)은 마일스톤별로 보존되며 새로고침·재접속 후에도 유지되어야 한다. 대본이 기본 구성을 제공하면 첫 진입 시 그것으로 시작하고, 사용자가 바꾼 뒤에는 사용자 구성이 우선한다. 기본 구성으로 되돌리는 수단을 화면에 두어야 한다.</t>
+        </is>
+      </c>
+      <c r="E51" s="45" t="inlineStr">
+        <is>
+          <t>(내부 처리) / 기본 구성은 대본 사이드카에서 로드</t>
+        </is>
+      </c>
+      <c r="F51" s="43" t="inlineStr">
+        <is>
+          <t>구성 변경 시 즉시 저장(이벤트 기반), 로드는 진입 시 1회</t>
+        </is>
+      </c>
+      <c r="G51" s="45" t="inlineStr">
+        <is>
+          <t>구성 변경은 사용자 조작이라 주기가 없다. 새로고침에 날아가면 사용자가 짜 놓은 화면을 매번 다시 만들어야 한다 — VZ-I-02(재접속 시 현재값 복원)가 데이터에 대해 세운 원칙을 화면 구성에도 적용한다.</t>
+        </is>
+      </c>
+      <c r="H51" s="45" t="inlineStr">
+        <is>
+          <t>(가시화 내부)</t>
+        </is>
+      </c>
+      <c r="I51" s="45" t="inlineStr">
+        <is>
+          <t>상대 파트 없음 — 화면 구성이라 정상</t>
+        </is>
+      </c>
+      <c r="J51" s="43" t="inlineStr">
+        <is>
+          <t>김현우</t>
+        </is>
+      </c>
+      <c r="K51" s="37" t="inlineStr">
+        <is>
+          <t>노드 캔버스 · 공통</t>
+        </is>
+      </c>
+      <c r="L51" s="37" t="inlineStr">
+        <is>
+          <t>v1.1 신설. 3층(기본 구성=대본 사이드카 / 사용자 구성=localStorage / 되돌리기 버튼). 좌표는 대본 계약이 아니라 사이드카에 둔다 — F10 REQ-1002와 같은 원칙. 임무 전체 보기는 __mission__ 별도 슬롯.</t>
+        </is>
+      </c>
+    </row>
+    <row r="52" s="54">
+      <c r="A52" s="43" t="inlineStr">
+        <is>
           <t>VZ-N-05</t>
         </is>
       </c>
-      <c r="B51" s="44" t="inlineStr">
+      <c r="B52" s="44" t="inlineStr">
         <is>
           <t>캔버스</t>
         </is>
       </c>
-      <c r="C51" s="45" t="inlineStr">
+      <c r="C52" s="45" t="inlineStr">
         <is>
           <t>뷰 노드 요약 카드와 확대</t>
         </is>
       </c>
-      <c r="D51" s="45" t="inlineStr">
+      <c r="D52" s="45" t="inlineStr">
         <is>
           <t>뷰 노드는 접힌 상태에서 핵심 값을 요약해 보이고, 확대하면 전체 화면을 제공해야 한다. 확대는 캔버스를 교체하지 않는 오버레이여야 하며, 동시에 하나만 열린다.</t>
         </is>
       </c>
-      <c r="E51" s="45" t="inlineStr">
+      <c r="E52" s="45" t="inlineStr">
         <is>
           <t>(내부 처리)</t>
         </is>
       </c>
-      <c r="F51" s="43" t="inlineStr">
+      <c r="F52" s="43" t="inlineStr">
         <is>
           <t>사용자 조작 시(이벤트 기반). 표시 값의 주기는 각 수신 요구사항을 따른다</t>
         </is>
       </c>
-      <c r="G51" s="45" t="inlineStr">
+      <c r="G52" s="45" t="inlineStr">
         <is>
           <t>확대·축소는 사용자 조작이라 주기가 없다. 오버레이로 못박는 이유는, 화면을 교체하는 순간 그것이 이름만 바꾼 탭이 되어 이번 개편이 원점으로 돌아가기 때문이다.</t>
         </is>
       </c>
-      <c r="H51" s="45" t="inlineStr">
+      <c r="H52" s="45" t="inlineStr">
         <is>
           <t>(가시화 내부)</t>
         </is>
       </c>
-      <c r="I51" s="45" t="inlineStr">
+      <c r="I52" s="45" t="inlineStr">
         <is>
           <t>상대 파트 없음 — 화면 구성이라 정상</t>
         </is>
       </c>
-      <c r="J51" s="43" t="inlineStr">
+      <c r="J52" s="43" t="inlineStr">
         <is>
           <t>김현우</t>
         </is>
       </c>
-      <c r="K51" s="37" t="inlineStr">
+      <c r="K52" s="37" t="inlineStr">
         <is>
           <t>노드 캔버스 · 공통</t>
         </is>
       </c>
-      <c r="L51" s="37" t="inlineStr">
+      <c r="L52" s="37" t="inlineStr">
         <is>
           <t>v1.1 신설. 「탭으로 되돌아가지 않는다」의 요구사항 근거. VZ-U-03(계층 뷰)의 표시 깊이를 이 요약↔확대가 실현한다. 영상 노드는 접힘=정지 프레임 / 확대=재생(VZ-I-06 프레임 루프).</t>
         </is>
       </c>
     </row>
-    <row r="52" s="54"/>
     <row r="53" s="54"/>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
